--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="11940"/>
+    <workbookView windowWidth="28125" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>sku</t>
   </si>
@@ -38,9 +38,6 @@
   </si>
   <si>
     <t>品名</t>
-  </si>
-  <si>
-    <t>属性</t>
   </si>
   <si>
     <t>品牌</t>
@@ -165,8 +162,16 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="23">
-    <font>
+  <fonts count="24">
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
@@ -659,51 +664,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -713,111 +715,117 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1139,200 +1147,197 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AU1"/>
+  <dimension ref="A1:AT1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="15" max="15" width="11.5" customWidth="1"/>
-    <col min="16" max="16" width="13" customWidth="1"/>
-    <col min="17" max="17" width="11" customWidth="1"/>
-    <col min="18" max="18" width="13.25" customWidth="1"/>
-    <col min="19" max="19" width="9.625" customWidth="1"/>
-    <col min="20" max="20" width="9.375" customWidth="1"/>
-    <col min="21" max="21" width="16" customWidth="1"/>
-    <col min="22" max="22" width="14.875" customWidth="1"/>
-    <col min="23" max="23" width="12" customWidth="1"/>
-    <col min="24" max="24" width="12.375" customWidth="1"/>
-    <col min="25" max="25" width="12.125" customWidth="1"/>
-    <col min="26" max="26" width="12.25" customWidth="1"/>
-    <col min="28" max="28" width="11.5" style="1"/>
-    <col min="29" max="29" width="10.375" style="1"/>
-    <col min="30" max="30" width="12.25" customWidth="1"/>
-    <col min="31" max="31" width="11.125" customWidth="1"/>
-    <col min="32" max="33" width="8.125" customWidth="1"/>
-    <col min="34" max="35" width="9.25" customWidth="1"/>
-    <col min="36" max="36" width="10.875" customWidth="1"/>
+    <col min="14" max="14" width="11.5" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="16" max="16" width="11" customWidth="1"/>
+    <col min="17" max="17" width="13.25" customWidth="1"/>
+    <col min="18" max="18" width="9.625" customWidth="1"/>
+    <col min="19" max="19" width="9.375" customWidth="1"/>
+    <col min="20" max="20" width="16" customWidth="1"/>
+    <col min="21" max="21" width="14.875" customWidth="1"/>
+    <col min="22" max="22" width="12" customWidth="1"/>
+    <col min="23" max="23" width="12.375" customWidth="1"/>
+    <col min="24" max="24" width="12.125" customWidth="1"/>
+    <col min="25" max="25" width="12.25" customWidth="1"/>
+    <col min="27" max="27" width="11.5" style="2"/>
+    <col min="28" max="28" width="10.375" style="2"/>
+    <col min="29" max="29" width="12.25" customWidth="1"/>
+    <col min="30" max="30" width="11.125" customWidth="1"/>
+    <col min="31" max="32" width="8.125" customWidth="1"/>
+    <col min="33" max="34" width="9.25" customWidth="1"/>
+    <col min="35" max="35" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:46">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="4" t="s">
         <v>27</v>
       </c>
       <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AI1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AO1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AP1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AR1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AS1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AT1" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="AU1" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 W2:W1048576 X2:X1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576 V2:V1048576 W2:W1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 S2:S1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576 R2:R1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q1048576 T2:T1048576 Y2:Y1048576 Z2:Z1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576 S2:S1048576 X2:X1048576 Y2:Y1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576 AP2:AP1048576 AQ$1:AQ$1048576 AS2:AS1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 AO2:AO1048576 AP$1:AP$1048576 AR2:AR1048576">
       <formula1>0</formula1>
       <formula2>9999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT2:AT1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
@@ -1340,7 +1345,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AP$1:AP$1048576" listDataValidation="1"/>
+    <ignoredError sqref="AO$1:AO$1048576" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>sku</t>
   </si>
@@ -107,6 +107,10 @@
   </si>
   <si>
     <t>销售状态</t>
+  </si>
+  <si>
+    <t xml:space="preserve">报关产品属性
+</t>
   </si>
   <si>
     <t>报关中文名</t>
@@ -809,7 +813,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -827,6 +831,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1147,8 +1154,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AT1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AT2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="14" max="14" width="11.5" customWidth="1"/>
     <col min="15" max="15" width="13" customWidth="1"/>
@@ -1169,6 +1176,7 @@
     <col min="31" max="32" width="8.125" customWidth="1"/>
     <col min="33" max="34" width="9.25" customWidth="1"/>
     <col min="35" max="35" width="10.875" customWidth="1"/>
+    <col min="46" max="46" width="33.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:46">
@@ -1266,53 +1274,65 @@
         <v>30</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AT1" s="5" t="s">
-        <v>44</v>
-      </c>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="11:46">
+      <c r="K2" s="2"/>
+      <c r="AT2" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="7">
+  <dataValidations count="8">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS1048576">
+      <formula1>0</formula1>
+      <formula2>99999999</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2">
+      <formula1>1</formula1>
+      <formula2>2958101</formula2>
+    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576 V2:V1048576 W2:W1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
@@ -1337,10 +1357,6 @@
       <formula1>0</formula1>
       <formula2>9999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS1048576">
-      <formula1>0</formula1>
-      <formula2>99999999</formula2>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>sku</t>
   </si>
@@ -150,6 +150,39 @@
   </si>
   <si>
     <t>单箱数量</t>
+  </si>
+  <si>
+    <t>ean码</t>
+  </si>
+  <si>
+    <t>计划首批下单量</t>
+  </si>
+  <si>
+    <t>首批下单时间</t>
+  </si>
+  <si>
+    <t>MOQ(最小起订量)</t>
+  </si>
+  <si>
+    <t>交货周期(天)</t>
+  </si>
+  <si>
+    <t>实际首批到货时间</t>
+  </si>
+  <si>
+    <t>实际首批到货量</t>
+  </si>
+  <si>
+    <t>首批到货状态</t>
+  </si>
+  <si>
+    <t>采购员</t>
+  </si>
+  <si>
+    <t>一级供应商</t>
+  </si>
+  <si>
+    <t>二级供应商</t>
   </si>
   <si>
     <t>错误信息</t>
@@ -813,7 +846,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -829,11 +862,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1154,7 +1190,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AT2"/>
+  <dimension ref="A1:BE2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="14" max="14" width="11.5" customWidth="1"/>
@@ -1176,10 +1212,20 @@
     <col min="31" max="32" width="8.125" customWidth="1"/>
     <col min="33" max="34" width="9.25" customWidth="1"/>
     <col min="35" max="35" width="10.875" customWidth="1"/>
-    <col min="46" max="46" width="33.125" customWidth="1"/>
+    <col min="46" max="46" width="9.125" customWidth="1"/>
+    <col min="47" max="47" width="13.25" customWidth="1"/>
+    <col min="48" max="48" width="13.375" customWidth="1"/>
+    <col min="49" max="49" width="14" customWidth="1"/>
+    <col min="50" max="50" width="12.75" customWidth="1"/>
+    <col min="51" max="51" width="14.125" customWidth="1"/>
+    <col min="52" max="52" width="13.75" customWidth="1"/>
+    <col min="53" max="53" width="13.375" customWidth="1"/>
+    <col min="55" max="55" width="9.875" customWidth="1"/>
+    <col min="56" max="56" width="10" customWidth="1"/>
+    <col min="57" max="57" width="27.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:46">
+    <row r="1" s="1" customFormat="1" spans="1:57">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1318,24 +1364,72 @@
       <c r="AT1" s="5" t="s">
         <v>45</v>
       </c>
+      <c r="AU1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="7" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="2" spans="11:46">
+    <row r="2" spans="11:51">
       <c r="K2" s="2"/>
       <c r="AT2" s="6"/>
+      <c r="AU2"/>
+      <c r="AV2" s="2"/>
+      <c r="AY2" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="8">
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS1048576">
+  <dataValidations count="11">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 AV2 AY2">
+      <formula1>1</formula1>
+      <formula2>2958101</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2">
-      <formula1>1</formula1>
-      <formula2>2958101</formula2>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2 AZ2">
+      <formula1>0</formula1>
+      <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576 V2:V1048576 W2:W1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576 S2:S1048576 X2:X1048576 Y2:Y1048576">
+      <formula1>0</formula1>
+      <formula2>999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 AO2:AO1048576 AP1:AP7 AP9:AP1048576 AR2:AR1048576">
+      <formula1>0</formula1>
+      <formula2>9999999</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q1048576">
       <formula1>0</formula1>
@@ -1345,17 +1439,17 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576 V2:V1048576 W2:W1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576 S2:S1048576 X2:X1048576 Y2:Y1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS1048576">
       <formula1>0</formula1>
-      <formula2>999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 AO2:AO1048576 AP$1:AP$1048576 AR2:AR1048576">
-      <formula1>0</formula1>
-      <formula2>9999999</formula2>
+      <formula2>99999999</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>sku</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t>首批下单时间</t>
+  </si>
+  <si>
+    <t>预计首批到货时间</t>
   </si>
   <si>
     <t>MOQ(最小起订量)</t>
@@ -846,7 +849,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -860,9 +863,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1190,7 +1190,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BE2"/>
+  <dimension ref="A1:BF2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="14" max="14" width="11.5" customWidth="1"/>
@@ -1220,12 +1220,13 @@
     <col min="51" max="51" width="14.125" customWidth="1"/>
     <col min="52" max="52" width="13.75" customWidth="1"/>
     <col min="53" max="53" width="13.375" customWidth="1"/>
+    <col min="54" max="54" width="11.75" customWidth="1"/>
     <col min="55" max="55" width="9.875" customWidth="1"/>
     <col min="56" max="56" width="10" customWidth="1"/>
     <col min="57" max="57" width="27.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:57">
+    <row r="1" s="1" customFormat="1" spans="1:58">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1361,101 +1362,104 @@
       <c r="AS1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="5" t="s">
+      <c r="AT1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="5" t="s">
+      <c r="AU1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="5" t="s">
+      <c r="AV1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="5" t="s">
+      <c r="AW1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="5" t="s">
+      <c r="AX1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="5" t="s">
+      <c r="AY1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="5" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="5" t="s">
+      <c r="BA1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="5" t="s">
+      <c r="BB1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="5" t="s">
+      <c r="BC1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="5" t="s">
+      <c r="BD1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="7" t="s">
+      <c r="BE1" s="3" t="s">
         <v>56</v>
       </c>
+      <c r="BF1" s="6" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="2" spans="11:51">
+    <row r="2" spans="11:52">
       <c r="K2" s="2"/>
-      <c r="AT2" s="6"/>
-      <c r="AU2"/>
+      <c r="AT2" s="5"/>
       <c r="AV2" s="2"/>
       <c r="AY2" s="2"/>
+      <c r="AZ2" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="11">
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 AV2 AY2">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2 AS2:AS4 AS5:AS1048576">
+      <formula1>0</formula1>
+      <formula2>99999999</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 AV2">
       <formula1>1</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2 AZ2">
+      <formula1>32874</formula1>
+      <formula2>2958101</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2 BA2">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P4 P5:P1048576 S2:S4 S5:S1048576 X2:X4 X5:X1048576 Y2:Y4 Y5:Y1048576">
+      <formula1>0</formula1>
+      <formula2>999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O4 O5:O1048576 AO2:AO4 AO5:AO1048576 AP1:AP4 AP5:AP6 AP8:AP1048576 AR2:AR4 AR5:AR1048576">
+      <formula1>0</formula1>
+      <formula2>9999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N4 N5:N1048576 R2:R4 R5:R1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q5:Q1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2 AZ2">
-      <formula1>0</formula1>
-      <formula2>999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T4 T5:T1048576 V2:V4 V5:V1048576 W2:W4 W5:W1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576 S2:S1048576 X2:X1048576 Y2:Y1048576">
-      <formula1>0</formula1>
-      <formula2>999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 AO2:AO1048576 AP1:AP7 AP9:AP1048576 AR2:AR1048576">
-      <formula1>0</formula1>
-      <formula2>9999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q1048576">
-      <formula1>0</formula1>
-      <formula2>99999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576 R2:R1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576 V2:V1048576 W2:W1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U4 U5:U1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS1048576">
-      <formula1>0</formula1>
-      <formula2>99999999</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AO$1:AO$1048576" listDataValidation="1"/>
+    <ignoredError sqref="AO1:AO1048575" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -1209,7 +1209,8 @@
     <col min="28" max="28" width="10.375" style="2"/>
     <col min="29" max="29" width="12.25" customWidth="1"/>
     <col min="30" max="30" width="11.125" customWidth="1"/>
-    <col min="31" max="32" width="8.125" customWidth="1"/>
+    <col min="31" max="31" width="8.125" customWidth="1"/>
+    <col min="32" max="32" width="10.5" customWidth="1"/>
     <col min="33" max="34" width="9.25" customWidth="1"/>
     <col min="35" max="35" width="10.875" customWidth="1"/>
     <col min="46" max="46" width="9.125" customWidth="1"/>
@@ -1223,7 +1224,8 @@
     <col min="54" max="54" width="11.75" customWidth="1"/>
     <col min="55" max="55" width="9.875" customWidth="1"/>
     <col min="56" max="56" width="10" customWidth="1"/>
-    <col min="57" max="57" width="27.25" customWidth="1"/>
+    <col min="57" max="57" width="11" customWidth="1"/>
+    <col min="58" max="58" width="28.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:58">
@@ -1410,7 +1412,7 @@
       <c r="AZ2" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="11">
+  <dataValidations count="10">
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2 AS2:AS4 AS5:AS1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
@@ -1423,11 +1425,15 @@
       <formula1>32874</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2 BA2">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N4 N5:N1048576 R2:R4 R5:R1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2 T2:T4 T5:T1048576 V2:V4 V5:V1048576 W2:W4 W5:W1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2 BA2">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
@@ -1439,17 +1445,9 @@
       <formula1>0</formula1>
       <formula2>9999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N4 N5:N1048576 R2:R4 R5:R1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q5:Q1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T4 T5:T1048576 V2:V4 V5:V1048576 W2:W4 W5:W1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U4 U5:U1048576">
       <formula1>0</formula1>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="28125" windowHeight="11940"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>sku</t>
   </si>
@@ -186,9 +186,6 @@
   </si>
   <si>
     <t>二级供应商</t>
-  </si>
-  <si>
-    <t>错误信息</t>
   </si>
 </sst>
 </file>
@@ -202,7 +199,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -221,13 +218,6 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -704,48 +694,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -755,101 +748,98 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -867,9 +857,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1190,7 +1177,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BF2"/>
+  <dimension ref="A1:BE2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="14" max="14" width="11.5" customWidth="1"/>
@@ -1225,10 +1212,9 @@
     <col min="55" max="55" width="9.875" customWidth="1"/>
     <col min="56" max="56" width="10" customWidth="1"/>
     <col min="57" max="57" width="11" customWidth="1"/>
-    <col min="58" max="58" width="28.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:58">
+    <row r="1" s="1" customFormat="1" spans="1:57">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1399,9 +1385,6 @@
       </c>
       <c r="BE1" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="BF1" s="6" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2" spans="11:52">

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="11940"/>
+    <workbookView windowWidth="28125" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -14,9 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>sku</t>
+  </si>
+  <si>
+    <t>产品分类</t>
   </si>
   <si>
     <t>销售方式</t>
@@ -1177,44 +1180,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BE2"/>
+  <dimension ref="A1:BF2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="14" max="14" width="11.5" customWidth="1"/>
-    <col min="15" max="15" width="13" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="13.25" customWidth="1"/>
-    <col min="18" max="18" width="9.625" customWidth="1"/>
-    <col min="19" max="19" width="9.375" customWidth="1"/>
-    <col min="20" max="20" width="16" customWidth="1"/>
-    <col min="21" max="21" width="14.875" customWidth="1"/>
-    <col min="22" max="22" width="12" customWidth="1"/>
-    <col min="23" max="23" width="12.375" customWidth="1"/>
-    <col min="24" max="24" width="12.125" customWidth="1"/>
-    <col min="25" max="25" width="12.25" customWidth="1"/>
-    <col min="27" max="27" width="11.5" style="2"/>
-    <col min="28" max="28" width="10.375" style="2"/>
-    <col min="29" max="29" width="12.25" customWidth="1"/>
-    <col min="30" max="30" width="11.125" customWidth="1"/>
-    <col min="31" max="31" width="8.125" customWidth="1"/>
-    <col min="32" max="32" width="10.5" customWidth="1"/>
-    <col min="33" max="34" width="9.25" customWidth="1"/>
-    <col min="35" max="35" width="10.875" customWidth="1"/>
-    <col min="46" max="46" width="9.125" customWidth="1"/>
-    <col min="47" max="47" width="13.25" customWidth="1"/>
-    <col min="48" max="48" width="13.375" customWidth="1"/>
-    <col min="49" max="49" width="14" customWidth="1"/>
-    <col min="50" max="50" width="12.75" customWidth="1"/>
-    <col min="51" max="51" width="14.125" customWidth="1"/>
-    <col min="52" max="52" width="13.75" customWidth="1"/>
-    <col min="53" max="53" width="13.375" customWidth="1"/>
-    <col min="54" max="54" width="11.75" customWidth="1"/>
-    <col min="55" max="55" width="9.875" customWidth="1"/>
-    <col min="56" max="56" width="10" customWidth="1"/>
-    <col min="57" max="57" width="11" customWidth="1"/>
+    <col min="15" max="15" width="11.5" customWidth="1"/>
+    <col min="16" max="16" width="13" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
+    <col min="18" max="18" width="13.25" customWidth="1"/>
+    <col min="19" max="19" width="9.625" customWidth="1"/>
+    <col min="20" max="20" width="9.375" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
+    <col min="22" max="22" width="14.875" customWidth="1"/>
+    <col min="23" max="23" width="12" customWidth="1"/>
+    <col min="24" max="24" width="12.375" customWidth="1"/>
+    <col min="25" max="25" width="12.125" customWidth="1"/>
+    <col min="26" max="26" width="12.25" customWidth="1"/>
+    <col min="28" max="28" width="11.5" style="2"/>
+    <col min="29" max="29" width="10.375" style="2"/>
+    <col min="30" max="30" width="12.25" customWidth="1"/>
+    <col min="31" max="31" width="11.125" customWidth="1"/>
+    <col min="32" max="32" width="8.125" customWidth="1"/>
+    <col min="33" max="33" width="10.5" customWidth="1"/>
+    <col min="34" max="35" width="9.25" customWidth="1"/>
+    <col min="36" max="36" width="10.875" customWidth="1"/>
+    <col min="47" max="47" width="9.125" customWidth="1"/>
+    <col min="48" max="48" width="13.25" customWidth="1"/>
+    <col min="49" max="49" width="13.375" customWidth="1"/>
+    <col min="50" max="50" width="14" customWidth="1"/>
+    <col min="51" max="51" width="12.75" customWidth="1"/>
+    <col min="52" max="52" width="14.125" customWidth="1"/>
+    <col min="53" max="53" width="13.75" customWidth="1"/>
+    <col min="54" max="54" width="13.375" customWidth="1"/>
+    <col min="55" max="55" width="11.75" customWidth="1"/>
+    <col min="56" max="56" width="9.875" customWidth="1"/>
+    <col min="57" max="57" width="10" customWidth="1"/>
+    <col min="58" max="58" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:57">
+    <row r="1" s="1" customFormat="1" spans="1:58">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1293,13 +1296,13 @@
       <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
       <c r="AB1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="4" t="s">
         <v>28</v>
       </c>
       <c r="AD1" s="3" t="s">
@@ -1386,53 +1389,56 @@
       <c r="BE1" s="3" t="s">
         <v>56</v>
       </c>
+      <c r="BF1" s="3" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="2" spans="11:52">
-      <c r="K2" s="2"/>
-      <c r="AT2" s="5"/>
-      <c r="AV2" s="2"/>
-      <c r="AY2" s="2"/>
+    <row r="2" spans="12:53">
+      <c r="L2" s="2"/>
+      <c r="AU2" s="5"/>
+      <c r="AW2" s="2"/>
       <c r="AZ2" s="2"/>
+      <c r="BA2" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="10">
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2 AS2:AS4 AS5:AS1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2 AT2:AT4 AT5:AT1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 AV2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2 AW2">
       <formula1>1</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2 AZ2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2 BA2">
       <formula1>32874</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N4 N5:N1048576 R2:R4 R5:R1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O4 O5:O1048576 S2:S4 S5:S1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2 T2:T4 T5:T1048576 V2:V4 V5:V1048576 W2:W4 W5:W1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2 U2:U4 U5:U1048576 W2:W4 W5:W1048576 X2:X4 X5:X1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2 BA2">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2 BB2">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P4 P5:P1048576 S2:S4 S5:S1048576 X2:X4 X5:X1048576 Y2:Y4 Y5:Y1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q5:Q1048576 T2:T4 T5:T1048576 Y2:Y4 Y5:Y1048576 Z2:Z4 Z5:Z1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O4 O5:O1048576 AO2:AO4 AO5:AO1048576 AP1:AP4 AP5:AP6 AP8:AP1048576 AR2:AR4 AR5:AR1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P4 P5:P1048576 AP2:AP4 AP5:AP1048576 AQ1:AQ4 AQ5:AQ6 AQ8:AQ1048576 AS2:AS4 AS5:AS1048576">
       <formula1>0</formula1>
       <formula2>9999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q5:Q1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R4 R5:R1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U4 U5:U1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V4 V5:V1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
@@ -1440,7 +1446,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AO1:AO1048575" listDataValidation="1"/>
+    <ignoredError sqref="AP1:AP1048575" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>sku</t>
   </si>
@@ -189,6 +189,12 @@
   </si>
   <si>
     <t>二级供应商</t>
+  </si>
+  <si>
+    <t>量产入库时间</t>
+  </si>
+  <si>
+    <t>产品开发状态</t>
   </si>
 </sst>
 </file>
@@ -842,7 +848,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -860,6 +866,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1180,7 +1189,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BF2"/>
+  <dimension ref="A1:BH2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="15" max="15" width="11.5" customWidth="1"/>
@@ -1215,9 +1224,10 @@
     <col min="56" max="56" width="9.875" customWidth="1"/>
     <col min="57" max="57" width="10" customWidth="1"/>
     <col min="58" max="58" width="11" customWidth="1"/>
+    <col min="59" max="59" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:58">
+    <row r="1" s="1" customFormat="1" spans="1:60">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1392,16 +1402,23 @@
       <c r="BF1" s="3" t="s">
         <v>57</v>
       </c>
+      <c r="BG1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="3" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="2" spans="12:53">
+    <row r="2" spans="12:59">
       <c r="L2" s="2"/>
       <c r="AU2" s="5"/>
       <c r="AW2" s="2"/>
       <c r="AZ2" s="2"/>
       <c r="BA2" s="2"/>
+      <c r="BG2" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="10">
+  <dataValidations count="12">
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2 AT2:AT4 AT5:AT1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
@@ -1442,6 +1459,13 @@
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG2:BG1048576">
+      <formula1>25569</formula1>
+      <formula2>72686</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH1048576">
+      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>sku</t>
   </si>
@@ -137,7 +137,13 @@
     <t>英文用途</t>
   </si>
   <si>
-    <t>产品尺寸</t>
+    <t>产品尺寸(长)</t>
+  </si>
+  <si>
+    <t>产品尺寸(宽)</t>
+  </si>
+  <si>
+    <t>产品尺寸(高)</t>
   </si>
   <si>
     <t>毛重</t>
@@ -146,7 +152,13 @@
     <t>净重</t>
   </si>
   <si>
-    <t>箱规</t>
+    <t>箱规(长)</t>
+  </si>
+  <si>
+    <t>箱规(宽)</t>
+  </si>
+  <si>
+    <t>箱规(高)</t>
   </si>
   <si>
     <t>单箱重量</t>
@@ -1189,7 +1201,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BH2"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="15" max="15" width="11.5" customWidth="1"/>
@@ -1212,22 +1224,25 @@
     <col min="33" max="33" width="10.5" customWidth="1"/>
     <col min="34" max="35" width="9.25" customWidth="1"/>
     <col min="36" max="36" width="10.875" customWidth="1"/>
-    <col min="47" max="47" width="9.125" customWidth="1"/>
-    <col min="48" max="48" width="13.25" customWidth="1"/>
-    <col min="49" max="49" width="13.375" customWidth="1"/>
-    <col min="50" max="50" width="14" customWidth="1"/>
-    <col min="51" max="51" width="12.75" customWidth="1"/>
-    <col min="52" max="52" width="14.125" customWidth="1"/>
-    <col min="53" max="53" width="13.75" customWidth="1"/>
-    <col min="54" max="54" width="13.375" customWidth="1"/>
-    <col min="55" max="55" width="11.75" customWidth="1"/>
-    <col min="56" max="56" width="9.875" customWidth="1"/>
-    <col min="57" max="57" width="10" customWidth="1"/>
-    <col min="58" max="58" width="11" customWidth="1"/>
-    <col min="59" max="59" width="9.375"/>
+    <col min="41" max="41" width="12.375" customWidth="1"/>
+    <col min="42" max="42" width="11.5" customWidth="1"/>
+    <col min="43" max="43" width="11" customWidth="1"/>
+    <col min="51" max="51" width="9.125" customWidth="1"/>
+    <col min="52" max="52" width="13.25" customWidth="1"/>
+    <col min="53" max="53" width="13.375" customWidth="1"/>
+    <col min="54" max="54" width="14" customWidth="1"/>
+    <col min="55" max="55" width="12.75" customWidth="1"/>
+    <col min="56" max="56" width="14.125" customWidth="1"/>
+    <col min="57" max="57" width="13.75" customWidth="1"/>
+    <col min="58" max="58" width="13.375" customWidth="1"/>
+    <col min="59" max="59" width="11.75" customWidth="1"/>
+    <col min="60" max="60" width="9.875" customWidth="1"/>
+    <col min="61" max="61" width="10" customWidth="1"/>
+    <col min="62" max="62" width="11" customWidth="1"/>
+    <col min="63" max="63" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:60">
+    <row r="1" s="1" customFormat="1" spans="1:64">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1408,26 +1423,41 @@
       <c r="BH1" s="3" t="s">
         <v>59</v>
       </c>
+      <c r="BI1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="3" t="s">
+        <v>63</v>
+      </c>
     </row>
-    <row r="2" spans="12:59">
+    <row r="2" spans="12:63">
       <c r="L2" s="2"/>
-      <c r="AU2" s="5"/>
-      <c r="AW2" s="2"/>
-      <c r="AZ2" s="2"/>
+      <c r="AY2" s="5"/>
       <c r="BA2" s="2"/>
-      <c r="BG2" s="6"/>
+      <c r="BD2" s="2"/>
+      <c r="BE2" s="2"/>
+      <c r="BK2" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="12">
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2 AT2:AT4 AT5:AT1048576">
+  <dataValidations count="13">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL1048576">
+      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2 AX2:AX4 AX5:AX1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2 AW2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2 BA2">
       <formula1>1</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2 BA2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BB2 BE2">
       <formula1>32874</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
@@ -1435,11 +1465,11 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2 U2:U4 U5:U1048576 W2:W4 W5:W1048576 X2:X4 X5:X1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD2 U2:U4 U5:U1048576 W2:W4 W5:W1048576 X2:X4 X5:X1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2 BB2">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2 BF2">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
@@ -1447,7 +1477,7 @@
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P4 P5:P1048576 AP2:AP4 AP5:AP1048576 AQ1:AQ4 AQ5:AQ6 AQ8:AQ1048576 AS2:AS4 AS5:AS1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P4 P5:P1048576 AR2:AR4 AR5:AR1048576 AS2:AS4 AS5:AS6 AS8:AS1048576 AW2:AW4 AW5:AW1048576">
       <formula1>0</formula1>
       <formula2>9999999</formula2>
     </dataValidation>
@@ -1459,18 +1489,19 @@
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG2:BG1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO2:AO1048576 AP2:AP1048576 AQ2:AQ1048576 AT2:AT1048576 AU2:AU1048576 AV2:AV1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK2:BK1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH1048576">
-      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AP1:AP1048575" listDataValidation="1"/>
+    <ignoredError sqref="AR1:AR1048575" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -1445,14 +1445,7 @@
       <c r="BK2" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="13">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL1048576">
-      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2 AX2:AX4 AX5:AX1048576">
-      <formula1>0</formula1>
-      <formula2>99999999</formula2>
-    </dataValidation>
+  <dataValidations count="16">
     <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2 BA2">
       <formula1>1</formula1>
       <formula2>2958101</formula2>
@@ -1461,37 +1454,56 @@
       <formula1>32874</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O4 O5:O1048576 S2:S4 S5:S1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R4 R5:R1048576">
+      <formula1>0</formula1>
+      <formula2>99999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O4 O5:O1048576 S2:S4 S5:S1048576 AO2:AO1048576 AP2:AP1048576 AQ2:AQ1048576 AT2:AT1048576 AU2:AU1048576 AV2:AV1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD2 U2:U4 U5:U1048576 W2:W4 W5:W1048576 X2:X4 X5:X1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD2 U2:U4 U5:U1048576 X2:X4 X5:X1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2 BF2">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V4 V5:V1048576">
       <formula1>0</formula1>
-      <formula2>99999999999</formula2>
+      <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q5:Q1048576 T2:T4 T5:T1048576 Y2:Y4 Y5:Y1048576 Z2:Z4 Z5:Z1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q5:Q1048576 T2:T4 T5:T1048576 Z2:Z4 Z5:Z1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL1048576">
+      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999900000</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P4 P5:P1048576 AR2:AR4 AR5:AR1048576 AS2:AS4 AS5:AS6 AS8:AS1048576 AW2:AW4 AW5:AW1048576">
       <formula1>0</formula1>
       <formula2>9999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R4 R5:R1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999999000</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999900</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX4 AX5:AX1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V4 V5:V1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576">
       <formula1>0</formula1>
-      <formula2>999999999999</formula2>
+      <formula2>9.99999999999999E+23</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO2:AO1048576 AP2:AP1048576 AQ2:AQ1048576 AT2:AT1048576 AU2:AU1048576 AV2:AV1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BC1048576">
       <formula1>0</formula1>
-      <formula2>9999999999</formula2>
+      <formula2>9.99999999999999E+21</formula2>
     </dataValidation>
     <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK2:BK1048576">
       <formula1>25569</formula1>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -1231,8 +1231,7 @@
     <col min="52" max="52" width="13.25" customWidth="1"/>
     <col min="53" max="53" width="13.375" customWidth="1"/>
     <col min="54" max="54" width="14" customWidth="1"/>
-    <col min="55" max="55" width="12.75" customWidth="1"/>
-    <col min="56" max="56" width="14.125" customWidth="1"/>
+    <col min="55" max="56" width="12.75" customWidth="1"/>
     <col min="57" max="57" width="13.75" customWidth="1"/>
     <col min="58" max="58" width="13.375" customWidth="1"/>
     <col min="59" max="59" width="11.75" customWidth="1"/>
@@ -1439,21 +1438,29 @@
     <row r="2" spans="12:63">
       <c r="L2" s="2"/>
       <c r="AY2" s="5"/>
+      <c r="AZ2"/>
       <c r="BA2" s="2"/>
-      <c r="BD2" s="2"/>
       <c r="BE2" s="2"/>
       <c r="BK2" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="16">
+  <dataValidations count="17">
     <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2 BA2">
       <formula1>1</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD2:BD1048576">
+      <formula1>0</formula1>
+      <formula2>99999999</formula2>
+    </dataValidation>
     <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BB2 BE2">
       <formula1>32874</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U4 U5:U1048576 X2:X4 X5:X1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R4 R5:R1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
@@ -1462,9 +1469,8 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD2 U2:U4 U5:U1048576 X2:X4 X5:X1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL1048576">
+      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V4 V5:V1048576">
       <formula1>0</formula1>
@@ -1474,36 +1480,33 @@
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL1048576">
-      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P4 P5:P1048576 AR2:AR4 AR5:AR1048576 AS2:AS4 AS5:AS6 AS8:AS1048576 AW2:AW4 AW5:AW1048576">
+      <formula1>0</formula1>
+      <formula2>9999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999999000</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999900</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX4 AX5:AX1048576">
+      <formula1>0</formula1>
+      <formula2>99999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576">
+      <formula1>0</formula1>
+      <formula2>9.99999999999999E+23</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BC1048576">
+      <formula1>0</formula1>
+      <formula2>9.99999999999999E+21</formula2>
     </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P4 P5:P1048576 AR2:AR4 AR5:AR1048576 AS2:AS4 AS5:AS6 AS8:AS1048576 AW2:AW4 AW5:AW1048576">
-      <formula1>0</formula1>
-      <formula2>9999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999999000</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999900</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX4 AX5:AX1048576">
-      <formula1>0</formula1>
-      <formula2>99999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576">
-      <formula1>0</formula1>
-      <formula2>9.99999999999999E+23</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BC1048576">
-      <formula1>0</formula1>
-      <formula2>9.99999999999999E+21</formula2>
     </dataValidation>
     <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK2:BK1048576">
       <formula1>25569</formula1>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>sku</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>品名</t>
+  </si>
+  <si>
+    <t>品名（英文）</t>
   </si>
   <si>
     <t>品牌</t>
@@ -1201,47 +1204,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BL2"/>
+  <dimension ref="A1:BM2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="15" max="15" width="11.5" customWidth="1"/>
-    <col min="16" max="16" width="13" customWidth="1"/>
-    <col min="17" max="17" width="11" customWidth="1"/>
-    <col min="18" max="18" width="13.25" customWidth="1"/>
-    <col min="19" max="19" width="9.625" customWidth="1"/>
-    <col min="20" max="20" width="9.375" customWidth="1"/>
-    <col min="21" max="21" width="16" customWidth="1"/>
-    <col min="22" max="22" width="14.875" customWidth="1"/>
-    <col min="23" max="23" width="12" customWidth="1"/>
-    <col min="24" max="24" width="12.375" customWidth="1"/>
-    <col min="25" max="25" width="12.125" customWidth="1"/>
-    <col min="26" max="26" width="12.25" customWidth="1"/>
-    <col min="28" max="28" width="11.5" style="2"/>
-    <col min="29" max="29" width="10.375" style="2"/>
-    <col min="30" max="30" width="12.25" customWidth="1"/>
-    <col min="31" max="31" width="11.125" customWidth="1"/>
-    <col min="32" max="32" width="8.125" customWidth="1"/>
-    <col min="33" max="33" width="10.5" customWidth="1"/>
-    <col min="34" max="35" width="9.25" customWidth="1"/>
-    <col min="36" max="36" width="10.875" customWidth="1"/>
-    <col min="41" max="41" width="12.375" customWidth="1"/>
-    <col min="42" max="42" width="11.5" customWidth="1"/>
-    <col min="43" max="43" width="11" customWidth="1"/>
-    <col min="51" max="51" width="9.125" customWidth="1"/>
-    <col min="52" max="52" width="13.25" customWidth="1"/>
-    <col min="53" max="53" width="13.375" customWidth="1"/>
-    <col min="54" max="54" width="14" customWidth="1"/>
-    <col min="55" max="56" width="12.75" customWidth="1"/>
-    <col min="57" max="57" width="13.75" customWidth="1"/>
-    <col min="58" max="58" width="13.375" customWidth="1"/>
-    <col min="59" max="59" width="11.75" customWidth="1"/>
-    <col min="60" max="60" width="9.875" customWidth="1"/>
-    <col min="61" max="61" width="10" customWidth="1"/>
-    <col min="62" max="62" width="11" customWidth="1"/>
-    <col min="63" max="63" width="9.375"/>
+    <col min="16" max="16" width="11.5" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
+    <col min="19" max="19" width="13.25" customWidth="1"/>
+    <col min="20" max="20" width="9.625" customWidth="1"/>
+    <col min="21" max="21" width="9.375" customWidth="1"/>
+    <col min="22" max="22" width="16" customWidth="1"/>
+    <col min="23" max="23" width="14.875" customWidth="1"/>
+    <col min="24" max="24" width="12" customWidth="1"/>
+    <col min="25" max="25" width="12.375" customWidth="1"/>
+    <col min="26" max="26" width="12.125" customWidth="1"/>
+    <col min="27" max="27" width="12.25" customWidth="1"/>
+    <col min="29" max="29" width="11.5" style="2"/>
+    <col min="30" max="30" width="10.375" style="2"/>
+    <col min="31" max="31" width="12.25" customWidth="1"/>
+    <col min="32" max="32" width="11.125" customWidth="1"/>
+    <col min="33" max="33" width="8.125" customWidth="1"/>
+    <col min="34" max="34" width="10.5" customWidth="1"/>
+    <col min="35" max="36" width="9.25" customWidth="1"/>
+    <col min="37" max="37" width="10.875" customWidth="1"/>
+    <col min="42" max="42" width="12.375" customWidth="1"/>
+    <col min="43" max="43" width="11.5" customWidth="1"/>
+    <col min="44" max="44" width="11" customWidth="1"/>
+    <col min="52" max="52" width="9.125" customWidth="1"/>
+    <col min="53" max="53" width="13.25" customWidth="1"/>
+    <col min="54" max="54" width="13.375" customWidth="1"/>
+    <col min="55" max="55" width="14" customWidth="1"/>
+    <col min="56" max="57" width="12.75" customWidth="1"/>
+    <col min="58" max="58" width="13.75" customWidth="1"/>
+    <col min="59" max="59" width="13.375" customWidth="1"/>
+    <col min="60" max="60" width="11.75" customWidth="1"/>
+    <col min="61" max="61" width="9.875" customWidth="1"/>
+    <col min="62" max="62" width="10" customWidth="1"/>
+    <col min="63" max="63" width="11" customWidth="1"/>
+    <col min="64" max="64" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:64">
+    <row r="1" s="1" customFormat="1" spans="1:65">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1323,13 +1326,13 @@
       <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AC1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="3" t="s">
@@ -1434,89 +1437,87 @@
       <c r="BL1" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="BM1" s="3" t="s">
+        <v>64</v>
+      </c>
     </row>
-    <row r="2" spans="12:63">
-      <c r="L2" s="2"/>
-      <c r="AY2" s="5"/>
-      <c r="AZ2"/>
-      <c r="BA2" s="2"/>
-      <c r="BE2" s="2"/>
-      <c r="BK2" s="6"/>
+    <row r="2" spans="13:64">
+      <c r="M2" s="2"/>
+      <c r="AZ2" s="5"/>
+      <c r="BB2" s="2"/>
+      <c r="BF2" s="2"/>
+      <c r="BL2" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="17">
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2 BA2">
+  <dataValidations count="16">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2 BB2">
       <formula1>1</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD2:BD1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2 BF2">
+      <formula1>32874</formula1>
+      <formula2>2958101</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V4 V5:V1048576 Y2:Y4 Y5:Y1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S4 S5:S1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BB2 BE2">
-      <formula1>32874</formula1>
-      <formula2>2958101</formula2>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P4 P5:P1048576 T2:T4 T5:T1048576 AP2:AP1048576 AQ2:AQ1048576 AR2:AR1048576 AU2:AU1048576 AV2:AV1048576 AW2:AW1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U4 U5:U1048576 X2:X4 X5:X1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W4 W5:W1048576">
       <formula1>0</formula1>
-      <formula2>99999999999</formula2>
+      <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R4 R5:R1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R4 R5:R1048576 U2:U4 U5:U1048576 AA2:AA4 AA5:AA1048576">
+      <formula1>0</formula1>
+      <formula2>999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q5:Q1048576 AS2:AS4 AS5:AS1048576 AT2:AT4 AT5:AT6 AT8:AT1048576 AX2:AX4 AX5:AX1048576">
+      <formula1>0</formula1>
+      <formula2>9999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999999000</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999900</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY4 AY5:AY1048576 BE2:BE1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O4 O5:O1048576 S2:S4 S5:S1048576 AO2:AO1048576 AP2:AP1048576 AQ2:AQ1048576 AT2:AT1048576 AU2:AU1048576 AV2:AV1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL1048576">
-      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V4 V5:V1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q5:Q1048576 T2:T4 T5:T1048576 Z2:Z4 Z5:Z1048576">
-      <formula1>0</formula1>
-      <formula2>999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P4 P5:P1048576 AR2:AR4 AR5:AR1048576 AS2:AS4 AS5:AS6 AS8:AS1048576 AW2:AW4 AW5:AW1048576">
-      <formula1>0</formula1>
-      <formula2>9999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999999000</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999900</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX4 AX5:AX1048576">
-      <formula1>0</formula1>
-      <formula2>99999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+23</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BC1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD2:BD1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+21</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG2:BG1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK2:BK1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM2:BM1048576">
+      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AR1:AR1048575" listDataValidation="1"/>
+    <ignoredError sqref="AS1:AS1048575" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -14,12 +14,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+  <si>
+    <t>spu</t>
+  </si>
   <si>
     <t>sku</t>
   </si>
   <si>
-    <t>产品分类</t>
+    <t>一级类目</t>
+  </si>
+  <si>
+    <t>二级类目</t>
   </si>
   <si>
     <t>销售方式</t>
@@ -1204,47 +1210,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BM2"/>
+  <dimension ref="A1:BO2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="16" max="16" width="11.5" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="11" customWidth="1"/>
-    <col min="19" max="19" width="13.25" customWidth="1"/>
-    <col min="20" max="20" width="9.625" customWidth="1"/>
-    <col min="21" max="21" width="9.375" customWidth="1"/>
-    <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="14.875" customWidth="1"/>
-    <col min="24" max="24" width="12" customWidth="1"/>
-    <col min="25" max="25" width="12.375" customWidth="1"/>
-    <col min="26" max="26" width="12.125" customWidth="1"/>
-    <col min="27" max="27" width="12.25" customWidth="1"/>
-    <col min="29" max="29" width="11.5" style="2"/>
-    <col min="30" max="30" width="10.375" style="2"/>
-    <col min="31" max="31" width="12.25" customWidth="1"/>
-    <col min="32" max="32" width="11.125" customWidth="1"/>
-    <col min="33" max="33" width="8.125" customWidth="1"/>
-    <col min="34" max="34" width="10.5" customWidth="1"/>
-    <col min="35" max="36" width="9.25" customWidth="1"/>
-    <col min="37" max="37" width="10.875" customWidth="1"/>
-    <col min="42" max="42" width="12.375" customWidth="1"/>
-    <col min="43" max="43" width="11.5" customWidth="1"/>
-    <col min="44" max="44" width="11" customWidth="1"/>
-    <col min="52" max="52" width="9.125" customWidth="1"/>
-    <col min="53" max="53" width="13.25" customWidth="1"/>
-    <col min="54" max="54" width="13.375" customWidth="1"/>
-    <col min="55" max="55" width="14" customWidth="1"/>
-    <col min="56" max="57" width="12.75" customWidth="1"/>
-    <col min="58" max="58" width="13.75" customWidth="1"/>
-    <col min="59" max="59" width="13.375" customWidth="1"/>
-    <col min="60" max="60" width="11.75" customWidth="1"/>
-    <col min="61" max="61" width="9.875" customWidth="1"/>
-    <col min="62" max="62" width="10" customWidth="1"/>
-    <col min="63" max="63" width="11" customWidth="1"/>
-    <col min="64" max="64" width="9.375"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
+    <col min="20" max="20" width="11" customWidth="1"/>
+    <col min="21" max="21" width="13.25" customWidth="1"/>
+    <col min="22" max="22" width="9.625" customWidth="1"/>
+    <col min="23" max="23" width="9.375" customWidth="1"/>
+    <col min="24" max="24" width="16" customWidth="1"/>
+    <col min="25" max="25" width="14.875" customWidth="1"/>
+    <col min="26" max="26" width="12" customWidth="1"/>
+    <col min="27" max="27" width="12.375" customWidth="1"/>
+    <col min="28" max="28" width="12.125" customWidth="1"/>
+    <col min="29" max="29" width="12.25" customWidth="1"/>
+    <col min="31" max="31" width="11.5" style="2"/>
+    <col min="32" max="32" width="10.375" style="2"/>
+    <col min="33" max="33" width="12.25" customWidth="1"/>
+    <col min="34" max="34" width="11.125" customWidth="1"/>
+    <col min="35" max="35" width="8.125" customWidth="1"/>
+    <col min="36" max="36" width="10.5" customWidth="1"/>
+    <col min="37" max="38" width="9.25" customWidth="1"/>
+    <col min="39" max="39" width="10.875" customWidth="1"/>
+    <col min="44" max="44" width="12.375" customWidth="1"/>
+    <col min="45" max="45" width="11.5" customWidth="1"/>
+    <col min="46" max="46" width="11" customWidth="1"/>
+    <col min="54" max="54" width="9.125" customWidth="1"/>
+    <col min="55" max="55" width="13.25" customWidth="1"/>
+    <col min="56" max="56" width="13.375" customWidth="1"/>
+    <col min="57" max="57" width="14" customWidth="1"/>
+    <col min="58" max="59" width="12.75" customWidth="1"/>
+    <col min="60" max="60" width="13.75" customWidth="1"/>
+    <col min="61" max="61" width="13.375" customWidth="1"/>
+    <col min="62" max="62" width="11.75" customWidth="1"/>
+    <col min="63" max="63" width="9.875" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="11" customWidth="1"/>
+    <col min="66" max="66" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:65">
+    <row r="1" s="1" customFormat="1" spans="1:67">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1329,16 +1335,16 @@
       <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="4" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="3" t="s">
@@ -1440,84 +1446,90 @@
       <c r="BM1" s="3" t="s">
         <v>64</v>
       </c>
+      <c r="BN1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="3" t="s">
+        <v>66</v>
+      </c>
     </row>
-    <row r="2" spans="13:64">
-      <c r="M2" s="2"/>
-      <c r="AZ2" s="5"/>
-      <c r="BB2" s="2"/>
-      <c r="BF2" s="2"/>
-      <c r="BL2" s="6"/>
+    <row r="2" spans="15:66">
+      <c r="O2" s="2"/>
+      <c r="BB2" s="5"/>
+      <c r="BD2" s="2"/>
+      <c r="BH2" s="2"/>
+      <c r="BN2" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="16">
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2 BB2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2 BD2">
       <formula1>1</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2 BF2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE2 BH2">
       <formula1>32874</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V4 V5:V1048576 Y2:Y4 Y5:Y1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X4 X5:X1048576 AA2:AA4 AA5:AA1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S4 S5:S1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U4 U5:U1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P4 P5:P1048576 T2:T4 T5:T1048576 AP2:AP1048576 AQ2:AQ1048576 AR2:AR1048576 AU2:AU1048576 AV2:AV1048576 AW2:AW1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R4 R5:R1048576 V2:V4 V5:V1048576 AR2:AR1048576 AS2:AS1048576 AT2:AT1048576 AW2:AW1048576 AX2:AX1048576 AY2:AY1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W4 W5:W1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y4 Y5:Y1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R4 R5:R1048576 U2:U4 U5:U1048576 AA2:AA4 AA5:AA1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T4 T5:T1048576 W2:W4 W5:W1048576 AC2:AC4 AC5:AC1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q5:Q1048576 AS2:AS4 AS5:AS1048576 AT2:AT4 AT5:AT6 AT8:AT1048576 AX2:AX4 AX5:AX1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S4 S5:S1048576 AU2:AU4 AU5:AU1048576 AV2:AV4 AV5:AV6 AV8:AV1048576 AZ2:AZ4 AZ5:AZ1048576">
       <formula1>0</formula1>
       <formula2>9999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
       <formula1>0</formula1>
       <formula2>999999999999999000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY4 AY5:AY1048576 BE2:BE1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA4 BA5:BA1048576 BG2:BG1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BC1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+23</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD2:BD1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+21</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG2:BG1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI2:BI1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN2:BN1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM2:BM1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BO2:BO1048576">
       <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AS1:AS1048575" listDataValidation="1"/>
+    <ignoredError sqref="AU1:AU1048575" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -14,18 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
-  <si>
-    <t>spu</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>sku</t>
   </si>
   <si>
-    <t>一级类目</t>
-  </si>
-  <si>
-    <t>二级类目</t>
+    <t>产品分类</t>
   </si>
   <si>
     <t>销售方式</t>
@@ -1210,47 +1204,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BO2"/>
+  <dimension ref="A1:BM2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="18" max="18" width="11.5" customWidth="1"/>
-    <col min="19" max="19" width="13" customWidth="1"/>
-    <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="13.25" customWidth="1"/>
-    <col min="22" max="22" width="9.625" customWidth="1"/>
-    <col min="23" max="23" width="9.375" customWidth="1"/>
-    <col min="24" max="24" width="16" customWidth="1"/>
-    <col min="25" max="25" width="14.875" customWidth="1"/>
-    <col min="26" max="26" width="12" customWidth="1"/>
-    <col min="27" max="27" width="12.375" customWidth="1"/>
-    <col min="28" max="28" width="12.125" customWidth="1"/>
-    <col min="29" max="29" width="12.25" customWidth="1"/>
-    <col min="31" max="31" width="11.5" style="2"/>
-    <col min="32" max="32" width="10.375" style="2"/>
-    <col min="33" max="33" width="12.25" customWidth="1"/>
-    <col min="34" max="34" width="11.125" customWidth="1"/>
-    <col min="35" max="35" width="8.125" customWidth="1"/>
-    <col min="36" max="36" width="10.5" customWidth="1"/>
-    <col min="37" max="38" width="9.25" customWidth="1"/>
-    <col min="39" max="39" width="10.875" customWidth="1"/>
-    <col min="44" max="44" width="12.375" customWidth="1"/>
-    <col min="45" max="45" width="11.5" customWidth="1"/>
-    <col min="46" max="46" width="11" customWidth="1"/>
-    <col min="54" max="54" width="9.125" customWidth="1"/>
-    <col min="55" max="55" width="13.25" customWidth="1"/>
-    <col min="56" max="56" width="13.375" customWidth="1"/>
-    <col min="57" max="57" width="14" customWidth="1"/>
-    <col min="58" max="59" width="12.75" customWidth="1"/>
-    <col min="60" max="60" width="13.75" customWidth="1"/>
-    <col min="61" max="61" width="13.375" customWidth="1"/>
-    <col min="62" max="62" width="11.75" customWidth="1"/>
-    <col min="63" max="63" width="9.875" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="11" customWidth="1"/>
-    <col min="66" max="66" width="9.375"/>
+    <col min="16" max="16" width="11.5" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
+    <col min="19" max="19" width="13.25" customWidth="1"/>
+    <col min="20" max="20" width="9.625" customWidth="1"/>
+    <col min="21" max="21" width="9.375" customWidth="1"/>
+    <col min="22" max="22" width="16" customWidth="1"/>
+    <col min="23" max="23" width="14.875" customWidth="1"/>
+    <col min="24" max="24" width="12" customWidth="1"/>
+    <col min="25" max="25" width="12.375" customWidth="1"/>
+    <col min="26" max="26" width="12.125" customWidth="1"/>
+    <col min="27" max="27" width="12.25" customWidth="1"/>
+    <col min="29" max="29" width="11.5" style="2"/>
+    <col min="30" max="30" width="10.375" style="2"/>
+    <col min="31" max="31" width="12.25" customWidth="1"/>
+    <col min="32" max="32" width="11.125" customWidth="1"/>
+    <col min="33" max="33" width="8.125" customWidth="1"/>
+    <col min="34" max="34" width="10.5" customWidth="1"/>
+    <col min="35" max="36" width="9.25" customWidth="1"/>
+    <col min="37" max="37" width="10.875" customWidth="1"/>
+    <col min="42" max="42" width="12.375" customWidth="1"/>
+    <col min="43" max="43" width="11.5" customWidth="1"/>
+    <col min="44" max="44" width="11" customWidth="1"/>
+    <col min="52" max="52" width="9.125" customWidth="1"/>
+    <col min="53" max="53" width="13.25" customWidth="1"/>
+    <col min="54" max="54" width="13.375" customWidth="1"/>
+    <col min="55" max="55" width="14" customWidth="1"/>
+    <col min="56" max="57" width="12.75" customWidth="1"/>
+    <col min="58" max="58" width="13.75" customWidth="1"/>
+    <col min="59" max="59" width="13.375" customWidth="1"/>
+    <col min="60" max="60" width="11.75" customWidth="1"/>
+    <col min="61" max="61" width="9.875" customWidth="1"/>
+    <col min="62" max="62" width="10" customWidth="1"/>
+    <col min="63" max="63" width="11" customWidth="1"/>
+    <col min="64" max="64" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:67">
+    <row r="1" s="1" customFormat="1" spans="1:65">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1335,16 +1329,16 @@
       <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AE1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AF1" s="3" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="3" t="s">
@@ -1446,90 +1440,84 @@
       <c r="BM1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="BO1" s="3" t="s">
-        <v>66</v>
-      </c>
     </row>
-    <row r="2" spans="15:66">
-      <c r="O2" s="2"/>
-      <c r="BB2" s="5"/>
-      <c r="BD2" s="2"/>
-      <c r="BH2" s="2"/>
-      <c r="BN2" s="6"/>
+    <row r="2" spans="13:64">
+      <c r="M2" s="2"/>
+      <c r="AZ2" s="5"/>
+      <c r="BB2" s="2"/>
+      <c r="BF2" s="2"/>
+      <c r="BL2" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="16">
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2 BD2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2 BB2">
       <formula1>1</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE2 BH2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2 BF2">
       <formula1>32874</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X4 X5:X1048576 AA2:AA4 AA5:AA1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V4 V5:V1048576 Y2:Y4 Y5:Y1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U4 U5:U1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S4 S5:S1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R4 R5:R1048576 V2:V4 V5:V1048576 AR2:AR1048576 AS2:AS1048576 AT2:AT1048576 AW2:AW1048576 AX2:AX1048576 AY2:AY1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P4 P5:P1048576 T2:T4 T5:T1048576 AP2:AP1048576 AQ2:AQ1048576 AR2:AR1048576 AU2:AU1048576 AV2:AV1048576 AW2:AW1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y4 Y5:Y1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W4 W5:W1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T4 T5:T1048576 W2:W4 W5:W1048576 AC2:AC4 AC5:AC1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R4 R5:R1048576 U2:U4 U5:U1048576 AA2:AA4 AA5:AA1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S4 S5:S1048576 AU2:AU4 AU5:AU1048576 AV2:AV4 AV5:AV6 AV8:AV1048576 AZ2:AZ4 AZ5:AZ1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q5:Q1048576 AS2:AS4 AS5:AS1048576 AT2:AT4 AT5:AT6 AT8:AT1048576 AX2:AX4 AX5:AX1048576">
       <formula1>0</formula1>
       <formula2>9999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X1048576">
       <formula1>0</formula1>
       <formula2>999999999999999000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA4 BA5:BA1048576 BG2:BG1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY4 AY5:AY1048576 BE2:BE1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BC1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+23</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD2:BD1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+21</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI2:BI1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG2:BG1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN2:BN1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BO2:BO1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM2:BM1048576">
       <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AU1:AU1048575" listDataValidation="1"/>
+    <ignoredError sqref="AS1:AS1048575" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -14,12 +14,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+  <si>
+    <t>spu</t>
+  </si>
   <si>
     <t>sku</t>
   </si>
   <si>
-    <t>产品分类</t>
+    <t>一级类目</t>
+  </si>
+  <si>
+    <t>二级类目</t>
   </si>
   <si>
     <t>销售方式</t>
@@ -1204,47 +1210,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BM2"/>
+  <dimension ref="A1:BO2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="16" max="16" width="11.5" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="11" customWidth="1"/>
-    <col min="19" max="19" width="13.25" customWidth="1"/>
-    <col min="20" max="20" width="9.625" customWidth="1"/>
-    <col min="21" max="21" width="9.375" customWidth="1"/>
-    <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="14.875" customWidth="1"/>
-    <col min="24" max="24" width="12" customWidth="1"/>
-    <col min="25" max="25" width="12.375" customWidth="1"/>
-    <col min="26" max="26" width="12.125" customWidth="1"/>
-    <col min="27" max="27" width="12.25" customWidth="1"/>
-    <col min="29" max="29" width="11.5" style="2"/>
-    <col min="30" max="30" width="10.375" style="2"/>
-    <col min="31" max="31" width="12.25" customWidth="1"/>
-    <col min="32" max="32" width="11.125" customWidth="1"/>
-    <col min="33" max="33" width="8.125" customWidth="1"/>
-    <col min="34" max="34" width="10.5" customWidth="1"/>
-    <col min="35" max="36" width="9.25" customWidth="1"/>
-    <col min="37" max="37" width="10.875" customWidth="1"/>
-    <col min="42" max="42" width="12.375" customWidth="1"/>
-    <col min="43" max="43" width="11.5" customWidth="1"/>
-    <col min="44" max="44" width="11" customWidth="1"/>
-    <col min="52" max="52" width="9.125" customWidth="1"/>
-    <col min="53" max="53" width="13.25" customWidth="1"/>
-    <col min="54" max="54" width="13.375" customWidth="1"/>
-    <col min="55" max="55" width="14" customWidth="1"/>
-    <col min="56" max="57" width="12.75" customWidth="1"/>
-    <col min="58" max="58" width="13.75" customWidth="1"/>
-    <col min="59" max="59" width="13.375" customWidth="1"/>
-    <col min="60" max="60" width="11.75" customWidth="1"/>
-    <col min="61" max="61" width="9.875" customWidth="1"/>
-    <col min="62" max="62" width="10" customWidth="1"/>
-    <col min="63" max="63" width="11" customWidth="1"/>
-    <col min="64" max="64" width="9.375"/>
+    <col min="3" max="3" width="14.125" customWidth="1"/>
+    <col min="4" max="4" width="12.875" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
+    <col min="20" max="20" width="11" customWidth="1"/>
+    <col min="21" max="21" width="13.25" customWidth="1"/>
+    <col min="22" max="22" width="9.625" customWidth="1"/>
+    <col min="23" max="23" width="9.375" customWidth="1"/>
+    <col min="24" max="24" width="16" customWidth="1"/>
+    <col min="25" max="25" width="14.875" customWidth="1"/>
+    <col min="26" max="26" width="12" customWidth="1"/>
+    <col min="27" max="27" width="12.375" customWidth="1"/>
+    <col min="28" max="28" width="12.125" customWidth="1"/>
+    <col min="29" max="29" width="12.25" customWidth="1"/>
+    <col min="31" max="31" width="11.5" style="2"/>
+    <col min="32" max="32" width="10.375" style="2"/>
+    <col min="33" max="33" width="12.25" customWidth="1"/>
+    <col min="34" max="34" width="11.125" customWidth="1"/>
+    <col min="35" max="35" width="8.125" customWidth="1"/>
+    <col min="36" max="36" width="10.5" customWidth="1"/>
+    <col min="37" max="38" width="9.25" customWidth="1"/>
+    <col min="39" max="39" width="10.875" customWidth="1"/>
+    <col min="44" max="44" width="12.375" customWidth="1"/>
+    <col min="45" max="45" width="11.5" customWidth="1"/>
+    <col min="46" max="46" width="11" customWidth="1"/>
+    <col min="54" max="54" width="9.125" customWidth="1"/>
+    <col min="55" max="55" width="13.25" customWidth="1"/>
+    <col min="56" max="56" width="13.375" customWidth="1"/>
+    <col min="57" max="57" width="14" customWidth="1"/>
+    <col min="58" max="59" width="12.75" customWidth="1"/>
+    <col min="60" max="60" width="13.75" customWidth="1"/>
+    <col min="61" max="61" width="13.375" customWidth="1"/>
+    <col min="62" max="62" width="11.75" customWidth="1"/>
+    <col min="63" max="63" width="9.875" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="11" customWidth="1"/>
+    <col min="66" max="66" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:65">
+    <row r="1" s="1" customFormat="1" spans="1:67">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1329,16 +1337,16 @@
       <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="4" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="3" t="s">
@@ -1440,84 +1448,90 @@
       <c r="BM1" s="3" t="s">
         <v>64</v>
       </c>
+      <c r="BN1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="3" t="s">
+        <v>66</v>
+      </c>
     </row>
-    <row r="2" spans="13:64">
-      <c r="M2" s="2"/>
-      <c r="AZ2" s="5"/>
-      <c r="BB2" s="2"/>
-      <c r="BF2" s="2"/>
-      <c r="BL2" s="6"/>
+    <row r="2" spans="15:66">
+      <c r="O2" s="2"/>
+      <c r="BB2" s="5"/>
+      <c r="BD2" s="2"/>
+      <c r="BH2" s="2"/>
+      <c r="BN2" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="16">
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2 BB2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2 BD2">
       <formula1>1</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2 BF2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE2 BH2">
       <formula1>32874</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V4 V5:V1048576 Y2:Y4 Y5:Y1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X4 X5:X1048576 AA2:AA4 AA5:AA1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S4 S5:S1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U4 U5:U1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P4 P5:P1048576 T2:T4 T5:T1048576 AP2:AP1048576 AQ2:AQ1048576 AR2:AR1048576 AU2:AU1048576 AV2:AV1048576 AW2:AW1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R4 R5:R1048576 V2:V4 V5:V1048576 AR2:AR1048576 AS2:AS1048576 AT2:AT1048576 AW2:AW1048576 AX2:AX1048576 AY2:AY1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W4 W5:W1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y4 Y5:Y1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R4 R5:R1048576 U2:U4 U5:U1048576 AA2:AA4 AA5:AA1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T4 T5:T1048576 W2:W4 W5:W1048576 AC2:AC4 AC5:AC1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q5:Q1048576 AS2:AS4 AS5:AS1048576 AT2:AT4 AT5:AT6 AT8:AT1048576 AX2:AX4 AX5:AX1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S4 S5:S1048576 AU2:AU4 AU5:AU1048576 AV2:AV4 AV5:AV6 AV8:AV1048576 AZ2:AZ4 AZ5:AZ1048576">
       <formula1>0</formula1>
       <formula2>9999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
       <formula1>0</formula1>
       <formula2>999999999999999000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY4 AY5:AY1048576 BE2:BE1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA4 BA5:BA1048576 BG2:BG1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BC1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+23</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD2:BD1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+21</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG2:BG1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI2:BI1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN2:BN1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM2:BM1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BO2:BO1048576">
       <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AS1:AS1048575" listDataValidation="1"/>
+    <ignoredError sqref="AU1:AU1048575" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -14,18 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
-  <si>
-    <t>spu</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>sku</t>
   </si>
   <si>
-    <t>一级类目</t>
-  </si>
-  <si>
-    <t>二级类目</t>
+    <t>产品分类</t>
   </si>
   <si>
     <t>销售方式</t>
@@ -1210,49 +1204,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BO2"/>
+  <dimension ref="A1:BM2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="3" max="3" width="14.125" customWidth="1"/>
-    <col min="4" max="4" width="12.875" customWidth="1"/>
-    <col min="18" max="18" width="11.5" customWidth="1"/>
-    <col min="19" max="19" width="13" customWidth="1"/>
-    <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="13.25" customWidth="1"/>
-    <col min="22" max="22" width="9.625" customWidth="1"/>
-    <col min="23" max="23" width="9.375" customWidth="1"/>
-    <col min="24" max="24" width="16" customWidth="1"/>
-    <col min="25" max="25" width="14.875" customWidth="1"/>
-    <col min="26" max="26" width="12" customWidth="1"/>
-    <col min="27" max="27" width="12.375" customWidth="1"/>
-    <col min="28" max="28" width="12.125" customWidth="1"/>
-    <col min="29" max="29" width="12.25" customWidth="1"/>
-    <col min="31" max="31" width="11.5" style="2"/>
-    <col min="32" max="32" width="10.375" style="2"/>
-    <col min="33" max="33" width="12.25" customWidth="1"/>
-    <col min="34" max="34" width="11.125" customWidth="1"/>
-    <col min="35" max="35" width="8.125" customWidth="1"/>
-    <col min="36" max="36" width="10.5" customWidth="1"/>
-    <col min="37" max="38" width="9.25" customWidth="1"/>
-    <col min="39" max="39" width="10.875" customWidth="1"/>
-    <col min="44" max="44" width="12.375" customWidth="1"/>
-    <col min="45" max="45" width="11.5" customWidth="1"/>
-    <col min="46" max="46" width="11" customWidth="1"/>
-    <col min="54" max="54" width="9.125" customWidth="1"/>
-    <col min="55" max="55" width="13.25" customWidth="1"/>
-    <col min="56" max="56" width="13.375" customWidth="1"/>
-    <col min="57" max="57" width="14" customWidth="1"/>
-    <col min="58" max="59" width="12.75" customWidth="1"/>
-    <col min="60" max="60" width="13.75" customWidth="1"/>
-    <col min="61" max="61" width="13.375" customWidth="1"/>
-    <col min="62" max="62" width="11.75" customWidth="1"/>
-    <col min="63" max="63" width="9.875" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="11" customWidth="1"/>
-    <col min="66" max="66" width="9.375"/>
+    <col min="16" max="16" width="11.5" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
+    <col min="19" max="19" width="13.25" customWidth="1"/>
+    <col min="20" max="20" width="9.625" customWidth="1"/>
+    <col min="21" max="21" width="9.375" customWidth="1"/>
+    <col min="22" max="22" width="16" customWidth="1"/>
+    <col min="23" max="23" width="14.875" customWidth="1"/>
+    <col min="24" max="24" width="12" customWidth="1"/>
+    <col min="25" max="25" width="12.375" customWidth="1"/>
+    <col min="26" max="26" width="12.125" customWidth="1"/>
+    <col min="27" max="27" width="12.25" customWidth="1"/>
+    <col min="29" max="29" width="11.5" style="2"/>
+    <col min="30" max="30" width="10.375" style="2"/>
+    <col min="31" max="31" width="12.25" customWidth="1"/>
+    <col min="32" max="32" width="11.125" customWidth="1"/>
+    <col min="33" max="33" width="8.125" customWidth="1"/>
+    <col min="34" max="34" width="10.5" customWidth="1"/>
+    <col min="35" max="36" width="9.25" customWidth="1"/>
+    <col min="37" max="37" width="10.875" customWidth="1"/>
+    <col min="42" max="42" width="12.375" customWidth="1"/>
+    <col min="43" max="43" width="11.5" customWidth="1"/>
+    <col min="44" max="44" width="11" customWidth="1"/>
+    <col min="52" max="52" width="9.125" customWidth="1"/>
+    <col min="53" max="53" width="13.25" customWidth="1"/>
+    <col min="54" max="54" width="13.375" customWidth="1"/>
+    <col min="55" max="55" width="14" customWidth="1"/>
+    <col min="56" max="57" width="12.75" customWidth="1"/>
+    <col min="58" max="58" width="13.75" customWidth="1"/>
+    <col min="59" max="59" width="13.375" customWidth="1"/>
+    <col min="60" max="60" width="11.75" customWidth="1"/>
+    <col min="61" max="61" width="9.875" customWidth="1"/>
+    <col min="62" max="62" width="10" customWidth="1"/>
+    <col min="63" max="63" width="11" customWidth="1"/>
+    <col min="64" max="64" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:67">
+    <row r="1" s="1" customFormat="1" spans="1:65">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1337,16 +1329,16 @@
       <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AE1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AF1" s="3" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="3" t="s">
@@ -1448,90 +1440,84 @@
       <c r="BM1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="BO1" s="3" t="s">
-        <v>66</v>
-      </c>
     </row>
-    <row r="2" spans="15:66">
-      <c r="O2" s="2"/>
-      <c r="BB2" s="5"/>
-      <c r="BD2" s="2"/>
-      <c r="BH2" s="2"/>
-      <c r="BN2" s="6"/>
+    <row r="2" spans="13:64">
+      <c r="M2" s="2"/>
+      <c r="AZ2" s="5"/>
+      <c r="BB2" s="2"/>
+      <c r="BF2" s="2"/>
+      <c r="BL2" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="16">
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2 BD2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2 BB2">
       <formula1>1</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE2 BH2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2 BF2">
       <formula1>32874</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X4 X5:X1048576 AA2:AA4 AA5:AA1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V4 V5:V1048576 Y2:Y4 Y5:Y1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U4 U5:U1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S4 S5:S1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R4 R5:R1048576 V2:V4 V5:V1048576 AR2:AR1048576 AS2:AS1048576 AT2:AT1048576 AW2:AW1048576 AX2:AX1048576 AY2:AY1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P4 P5:P1048576 T2:T4 T5:T1048576 AP2:AP1048576 AQ2:AQ1048576 AR2:AR1048576 AU2:AU1048576 AV2:AV1048576 AW2:AW1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y4 Y5:Y1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W4 W5:W1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T4 T5:T1048576 W2:W4 W5:W1048576 AC2:AC4 AC5:AC1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R4 R5:R1048576 U2:U4 U5:U1048576 AA2:AA4 AA5:AA1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S4 S5:S1048576 AU2:AU4 AU5:AU1048576 AV2:AV4 AV5:AV6 AV8:AV1048576 AZ2:AZ4 AZ5:AZ1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q5:Q1048576 AS2:AS4 AS5:AS1048576 AT2:AT4 AT5:AT6 AT8:AT1048576 AX2:AX4 AX5:AX1048576">
       <formula1>0</formula1>
       <formula2>9999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X1048576">
       <formula1>0</formula1>
       <formula2>999999999999999000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA4 BA5:BA1048576 BG2:BG1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY4 AY5:AY1048576 BE2:BE1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BC1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+23</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD2:BD1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+21</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI2:BI1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG2:BG1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN2:BN1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BO2:BO1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM2:BM1048576">
       <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AU1:AU1048575" listDataValidation="1"/>
+    <ignoredError sqref="AS1:AS1048575" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -14,12 +14,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+  <si>
+    <t>spu</t>
+  </si>
   <si>
     <t>sku</t>
   </si>
   <si>
-    <t>产品分类</t>
+    <t>一级分类</t>
+  </si>
+  <si>
+    <t>二级分类</t>
   </si>
   <si>
     <t>销售方式</t>
@@ -1204,47 +1210,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BM2"/>
+  <dimension ref="A1:BO2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="16" max="16" width="11.5" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="11" customWidth="1"/>
-    <col min="19" max="19" width="13.25" customWidth="1"/>
-    <col min="20" max="20" width="9.625" customWidth="1"/>
-    <col min="21" max="21" width="9.375" customWidth="1"/>
-    <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="14.875" customWidth="1"/>
-    <col min="24" max="24" width="12" customWidth="1"/>
-    <col min="25" max="25" width="12.375" customWidth="1"/>
-    <col min="26" max="26" width="12.125" customWidth="1"/>
-    <col min="27" max="27" width="12.25" customWidth="1"/>
-    <col min="29" max="29" width="11.5" style="2"/>
-    <col min="30" max="30" width="10.375" style="2"/>
-    <col min="31" max="31" width="12.25" customWidth="1"/>
-    <col min="32" max="32" width="11.125" customWidth="1"/>
-    <col min="33" max="33" width="8.125" customWidth="1"/>
-    <col min="34" max="34" width="10.5" customWidth="1"/>
-    <col min="35" max="36" width="9.25" customWidth="1"/>
-    <col min="37" max="37" width="10.875" customWidth="1"/>
-    <col min="42" max="42" width="12.375" customWidth="1"/>
-    <col min="43" max="43" width="11.5" customWidth="1"/>
-    <col min="44" max="44" width="11" customWidth="1"/>
-    <col min="52" max="52" width="9.125" customWidth="1"/>
-    <col min="53" max="53" width="13.25" customWidth="1"/>
-    <col min="54" max="54" width="13.375" customWidth="1"/>
-    <col min="55" max="55" width="14" customWidth="1"/>
-    <col min="56" max="57" width="12.75" customWidth="1"/>
-    <col min="58" max="58" width="13.75" customWidth="1"/>
-    <col min="59" max="59" width="13.375" customWidth="1"/>
-    <col min="60" max="60" width="11.75" customWidth="1"/>
-    <col min="61" max="61" width="9.875" customWidth="1"/>
-    <col min="62" max="62" width="10" customWidth="1"/>
-    <col min="63" max="63" width="11" customWidth="1"/>
-    <col min="64" max="64" width="9.375"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
+    <col min="20" max="20" width="11" customWidth="1"/>
+    <col min="21" max="21" width="13.25" customWidth="1"/>
+    <col min="22" max="22" width="9.625" customWidth="1"/>
+    <col min="23" max="23" width="9.375" customWidth="1"/>
+    <col min="24" max="24" width="16" customWidth="1"/>
+    <col min="25" max="25" width="14.875" customWidth="1"/>
+    <col min="26" max="26" width="12" customWidth="1"/>
+    <col min="27" max="27" width="12.375" customWidth="1"/>
+    <col min="28" max="28" width="12.125" customWidth="1"/>
+    <col min="29" max="29" width="12.25" customWidth="1"/>
+    <col min="31" max="31" width="11.5" style="2"/>
+    <col min="32" max="32" width="10.375" style="2"/>
+    <col min="33" max="33" width="12.25" customWidth="1"/>
+    <col min="34" max="34" width="11.125" customWidth="1"/>
+    <col min="35" max="35" width="8.125" customWidth="1"/>
+    <col min="36" max="36" width="10.5" customWidth="1"/>
+    <col min="37" max="38" width="9.25" customWidth="1"/>
+    <col min="39" max="39" width="10.875" customWidth="1"/>
+    <col min="44" max="44" width="12.375" customWidth="1"/>
+    <col min="45" max="45" width="11.5" customWidth="1"/>
+    <col min="46" max="46" width="11" customWidth="1"/>
+    <col min="54" max="54" width="9.125" customWidth="1"/>
+    <col min="55" max="55" width="13.25" customWidth="1"/>
+    <col min="56" max="56" width="13.375" customWidth="1"/>
+    <col min="57" max="57" width="14" customWidth="1"/>
+    <col min="58" max="59" width="12.75" customWidth="1"/>
+    <col min="60" max="60" width="13.75" customWidth="1"/>
+    <col min="61" max="61" width="13.375" customWidth="1"/>
+    <col min="62" max="62" width="11.75" customWidth="1"/>
+    <col min="63" max="63" width="9.875" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="11" customWidth="1"/>
+    <col min="66" max="66" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:65">
+    <row r="1" s="1" customFormat="1" spans="1:67">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1329,16 +1335,16 @@
       <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="4" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="3" t="s">
@@ -1440,84 +1446,90 @@
       <c r="BM1" s="3" t="s">
         <v>64</v>
       </c>
+      <c r="BN1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="3" t="s">
+        <v>66</v>
+      </c>
     </row>
-    <row r="2" spans="13:64">
-      <c r="M2" s="2"/>
-      <c r="AZ2" s="5"/>
-      <c r="BB2" s="2"/>
-      <c r="BF2" s="2"/>
-      <c r="BL2" s="6"/>
+    <row r="2" spans="15:66">
+      <c r="O2" s="2"/>
+      <c r="BB2" s="5"/>
+      <c r="BD2" s="2"/>
+      <c r="BH2" s="2"/>
+      <c r="BN2" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="16">
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2 BB2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2 BD2">
       <formula1>1</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2 BF2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE2 BH2">
       <formula1>32874</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V4 V5:V1048576 Y2:Y4 Y5:Y1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X4 X5:X1048576 AA2:AA4 AA5:AA1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S4 S5:S1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U4 U5:U1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P4 P5:P1048576 T2:T4 T5:T1048576 AP2:AP1048576 AQ2:AQ1048576 AR2:AR1048576 AU2:AU1048576 AV2:AV1048576 AW2:AW1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R4 R5:R1048576 V2:V4 V5:V1048576 AR2:AR1048576 AS2:AS1048576 AT2:AT1048576 AW2:AW1048576 AX2:AX1048576 AY2:AY1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W4 W5:W1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y4 Y5:Y1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R4 R5:R1048576 U2:U4 U5:U1048576 AA2:AA4 AA5:AA1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T4 T5:T1048576 W2:W4 W5:W1048576 AC2:AC4 AC5:AC1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q4 Q5:Q1048576 AS2:AS4 AS5:AS1048576 AT2:AT4 AT5:AT6 AT8:AT1048576 AX2:AX4 AX5:AX1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S4 S5:S1048576 AU2:AU4 AU5:AU1048576 AV2:AV4 AV5:AV6 AV8:AV1048576 AZ2:AZ4 AZ5:AZ1048576">
       <formula1>0</formula1>
       <formula2>9999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
       <formula1>0</formula1>
       <formula2>999999999999999000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY4 AY5:AY1048576 BE2:BE1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA4 BA5:BA1048576 BG2:BG1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BC1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+23</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD2:BD1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+21</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG2:BG1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI2:BI1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN2:BN1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM2:BM1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BO2:BO1048576">
       <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AS1:AS1048575" listDataValidation="1"/>
+    <ignoredError sqref="AU1:AU1048575" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -40,7 +40,7 @@
     <t>产品用途</t>
   </si>
   <si>
-    <t>存在侵权风险</t>
+    <t>存在侵权风险(是/否)</t>
   </si>
   <si>
     <t>主要材质</t>
@@ -82,13 +82,13 @@
     <t>标准零售价</t>
   </si>
   <si>
-    <t>目标毛利率</t>
-  </si>
-  <si>
-    <t>实际毛利率(人民币)</t>
-  </si>
-  <si>
-    <t>实际毛利率(美元)</t>
+    <t>目标毛利率%</t>
+  </si>
+  <si>
+    <t>实际毛利率%(人民币)</t>
+  </si>
+  <si>
+    <t>实际毛利率%(美元)</t>
   </si>
   <si>
     <t>年目标销售量</t>
@@ -134,7 +134,7 @@
     <t>报关申报价格</t>
   </si>
   <si>
-    <t>海关编码</t>
+    <t>中国海关编码</t>
   </si>
   <si>
     <t>申报要素</t>
@@ -1213,12 +1213,13 @@
   <dimension ref="A1:BO2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
+    <col min="9" max="9" width="16.875" customWidth="1"/>
     <col min="18" max="18" width="11.5" customWidth="1"/>
     <col min="19" max="19" width="13" customWidth="1"/>
     <col min="20" max="20" width="11" customWidth="1"/>
     <col min="21" max="21" width="13.25" customWidth="1"/>
     <col min="22" max="22" width="9.625" customWidth="1"/>
-    <col min="23" max="23" width="9.375" customWidth="1"/>
+    <col min="23" max="23" width="9.75" customWidth="1"/>
     <col min="24" max="24" width="16" customWidth="1"/>
     <col min="25" max="25" width="14.875" customWidth="1"/>
     <col min="26" max="26" width="12" customWidth="1"/>
@@ -1233,6 +1234,7 @@
     <col min="36" max="36" width="10.5" customWidth="1"/>
     <col min="37" max="38" width="9.25" customWidth="1"/>
     <col min="39" max="39" width="10.875" customWidth="1"/>
+    <col min="40" max="40" width="10.375" customWidth="1"/>
     <col min="44" max="44" width="12.375" customWidth="1"/>
     <col min="45" max="45" width="11.5" customWidth="1"/>
     <col min="46" max="46" width="11" customWidth="1"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="28125" windowHeight="11940"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -14,21 +14,222 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>spu</t>
   </si>
   <si>
-    <t>sku</t>
-  </si>
-  <si>
-    <t>一级分类</t>
-  </si>
-  <si>
-    <t>二级分类</t>
-  </si>
-  <si>
-    <t>销售方式</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sku编号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>一级分类</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>二级分类</t>
+    </r>
+  </si>
+  <si>
+    <t>产品经理</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>销售方式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>品名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>品名（英文）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>产品属性</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>品牌</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>产品开发状态</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>产品等级</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>销售渠道</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是否客户定制</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>模具成本(￥)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>委托开发成本(￥)</t>
+    </r>
   </si>
   <si>
     <t>产品卖点</t>
@@ -40,103 +241,481 @@
     <t>产品用途</t>
   </si>
   <si>
+    <t>计划上市时间</t>
+  </si>
+  <si>
     <t>存在侵权风险(是/否)</t>
   </si>
   <si>
+    <t>单位</t>
+  </si>
+  <si>
     <t>主要材质</t>
   </si>
   <si>
-    <t>品名</t>
-  </si>
-  <si>
-    <t>品名（英文）</t>
-  </si>
-  <si>
-    <t>品牌</t>
-  </si>
-  <si>
-    <t>产品属性</t>
-  </si>
-  <si>
-    <t>计划上市时间</t>
-  </si>
-  <si>
-    <t>单位</t>
-  </si>
-  <si>
-    <t>产品经理</t>
-  </si>
-  <si>
-    <t>目标含税成本</t>
-  </si>
-  <si>
-    <t>目标不含税成本</t>
-  </si>
-  <si>
-    <t>实际含税成本</t>
-  </si>
-  <si>
-    <t>实际不含税成本</t>
-  </si>
-  <si>
-    <t>标准零售价</t>
-  </si>
-  <si>
-    <t>目标毛利率%</t>
-  </si>
-  <si>
-    <t>实际毛利率%(人民币)</t>
-  </si>
-  <si>
-    <t>实际毛利率%(美元)</t>
-  </si>
-  <si>
-    <t>年目标销售量</t>
-  </si>
-  <si>
-    <t>年目标销售额</t>
-  </si>
-  <si>
-    <t>月目标销售量</t>
-  </si>
-  <si>
-    <t>月目标销售额</t>
-  </si>
-  <si>
-    <t>销售国家</t>
-  </si>
-  <si>
-    <t>上市时间</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>预计立项成本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>￥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>实际量产成本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>￥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>预计项目成本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>￥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>税率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>目标含税成本(￥)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>目标不含税成本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>￥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>标准零售价(￥)</t>
+    </r>
+  </si>
+  <si>
+    <t>ean码</t>
+  </si>
+  <si>
+    <t>MOQ(最小起订量)</t>
+  </si>
+  <si>
+    <t>试产数量</t>
+  </si>
+  <si>
+    <t>首批量产数量</t>
+  </si>
+  <si>
+    <t>计划首批下单量</t>
+  </si>
+  <si>
+    <t>实际首批到货量</t>
+  </si>
+  <si>
+    <t>预计首批到货时间</t>
+  </si>
+  <si>
+    <t>实际首批到货时间</t>
+  </si>
+  <si>
+    <t>首批下单时间</t>
+  </si>
+  <si>
+    <t>交货周期(天)</t>
+  </si>
+  <si>
+    <t>采购员</t>
+  </si>
+  <si>
+    <t>首批到货状态</t>
+  </si>
+  <si>
+    <t>一级供应商</t>
+  </si>
+  <si>
+    <t>二级供应商</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>年目标销量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>年目标销售额（￥）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>目标月销售量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>目标月销售额（￥）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>首季度目标销量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>销售国家</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>图片是否完成</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>视频是否完成</t>
+    </r>
   </si>
   <si>
     <t>退市时间</t>
   </si>
   <si>
-    <t>图片是否完成</t>
-  </si>
-  <si>
-    <t>视频是否完成</t>
-  </si>
-  <si>
-    <t>销售状态</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>销售状态</t>
+    </r>
+  </si>
+  <si>
+    <t>产品上市(含培训)资料链接</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是否可销售</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>销售平台</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">报关产品属性
 </t>
   </si>
   <si>
+    <r>
+      <t>报关申报价（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>$</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
     <t>报关中文名</t>
   </si>
   <si>
     <t>报关英文名</t>
   </si>
   <si>
-    <t>报关申报价格</t>
-  </si>
-  <si>
     <t>中国海关编码</t>
   </si>
   <si>
+    <t>报关型号</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>报关单位</t>
+    </r>
+  </si>
+  <si>
     <t>申报要素</t>
   </si>
   <si>
@@ -155,81 +734,44 @@
     <t>产品尺寸(高)</t>
   </si>
   <si>
+    <t>箱规(长)</t>
+  </si>
+  <si>
+    <t>箱规(宽)</t>
+  </si>
+  <si>
+    <t>箱规(高)</t>
+  </si>
+  <si>
     <t>毛重</t>
   </si>
   <si>
     <t>净重</t>
   </si>
   <si>
-    <t>箱规(长)</t>
-  </si>
-  <si>
-    <t>箱规(宽)</t>
-  </si>
-  <si>
-    <t>箱规(高)</t>
-  </si>
-  <si>
     <t>单箱重量</t>
   </si>
   <si>
     <t>单箱数量</t>
-  </si>
-  <si>
-    <t>ean码</t>
-  </si>
-  <si>
-    <t>计划首批下单量</t>
-  </si>
-  <si>
-    <t>首批下单时间</t>
-  </si>
-  <si>
-    <t>预计首批到货时间</t>
-  </si>
-  <si>
-    <t>MOQ(最小起订量)</t>
-  </si>
-  <si>
-    <t>交货周期(天)</t>
-  </si>
-  <si>
-    <t>实际首批到货时间</t>
-  </si>
-  <si>
-    <t>实际首批到货量</t>
-  </si>
-  <si>
-    <t>首批到货状态</t>
-  </si>
-  <si>
-    <t>采购员</t>
-  </si>
-  <si>
-    <t>一级供应商</t>
-  </si>
-  <si>
-    <t>二级供应商</t>
-  </si>
-  <si>
-    <t>量产入库时间</t>
-  </si>
-  <si>
-    <t>产品开发状态</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="10">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="176" formatCode="0.0000_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="178" formatCode="&quot;￥&quot;#,##0.0000;&quot;￥&quot;\-#,##0.0000"/>
+    <numFmt numFmtId="179" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="180" formatCode="0_ "/>
+    <numFmt numFmtId="181" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -238,16 +780,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -402,6 +943,28 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -869,26 +1432,56 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1210,39 +1803,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BO2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:BY1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="9" max="9" width="16.875" customWidth="1"/>
-    <col min="18" max="18" width="11.5" customWidth="1"/>
-    <col min="19" max="19" width="13" customWidth="1"/>
-    <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="13.25" customWidth="1"/>
-    <col min="22" max="22" width="9.625" customWidth="1"/>
+    <col min="1" max="1" width="4.875" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="8" max="8" width="12.375" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="7.75" customWidth="1"/>
+    <col min="11" max="11" width="12.75" customWidth="1"/>
+    <col min="14" max="14" width="11.5" customWidth="1"/>
+    <col min="15" max="15" width="12.125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="15.375" customWidth="1"/>
+    <col min="18" max="18" width="15.875" customWidth="1"/>
+    <col min="19" max="19" width="11" customWidth="1"/>
+    <col min="20" max="20" width="12" style="2" customWidth="1"/>
+    <col min="21" max="21" width="16.625" customWidth="1"/>
+    <col min="22" max="22" width="5.875" customWidth="1"/>
     <col min="23" max="23" width="9.75" customWidth="1"/>
-    <col min="24" max="24" width="16" customWidth="1"/>
-    <col min="25" max="25" width="14.875" customWidth="1"/>
-    <col min="26" max="26" width="12" customWidth="1"/>
-    <col min="27" max="27" width="12.375" customWidth="1"/>
-    <col min="28" max="28" width="12.125" customWidth="1"/>
-    <col min="29" max="29" width="12.25" customWidth="1"/>
-    <col min="31" max="31" width="11.5" style="2"/>
-    <col min="32" max="32" width="10.375" style="2"/>
-    <col min="33" max="33" width="12.25" customWidth="1"/>
-    <col min="34" max="34" width="11.125" customWidth="1"/>
-    <col min="35" max="35" width="8.125" customWidth="1"/>
-    <col min="36" max="36" width="10.5" customWidth="1"/>
-    <col min="37" max="38" width="9.25" customWidth="1"/>
-    <col min="39" max="39" width="10.875" customWidth="1"/>
-    <col min="40" max="40" width="10.375" customWidth="1"/>
+    <col min="24" max="24" width="15.125" style="3" customWidth="1"/>
+    <col min="25" max="25" width="15" style="1" customWidth="1"/>
+    <col min="26" max="26" width="14.875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="8.75" style="1" customWidth="1"/>
+    <col min="28" max="28" width="15.25" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16.75" style="1" customWidth="1"/>
+    <col min="30" max="30" width="14" style="1" customWidth="1"/>
+    <col min="31" max="31" width="11.5" style="4"/>
+    <col min="32" max="32" width="13" style="5" customWidth="1"/>
+    <col min="33" max="33" width="12.25" style="5" customWidth="1"/>
+    <col min="34" max="34" width="11.125" style="5" customWidth="1"/>
+    <col min="35" max="35" width="13.625" style="5" customWidth="1"/>
+    <col min="36" max="36" width="12.625" style="5" customWidth="1"/>
+    <col min="37" max="37" width="14.25" style="2" customWidth="1"/>
+    <col min="38" max="38" width="14.5" style="2" customWidth="1"/>
+    <col min="39" max="39" width="12" style="2" customWidth="1"/>
+    <col min="40" max="40" width="10.75" style="5" customWidth="1"/>
+    <col min="42" max="42" width="10.75" customWidth="1"/>
+    <col min="43" max="43" width="16.375" customWidth="1"/>
     <col min="44" max="44" width="12.375" customWidth="1"/>
-    <col min="45" max="45" width="11.5" customWidth="1"/>
-    <col min="46" max="46" width="11" customWidth="1"/>
+    <col min="45" max="45" width="11.5" style="5" customWidth="1"/>
+    <col min="46" max="46" width="15.875" style="1" customWidth="1"/>
+    <col min="47" max="47" width="11.625" style="5" customWidth="1"/>
+    <col min="48" max="48" width="15.875" style="1" customWidth="1"/>
+    <col min="49" max="49" width="13.5" style="5" customWidth="1"/>
+    <col min="51" max="51" width="11.75" customWidth="1"/>
+    <col min="52" max="52" width="12" customWidth="1"/>
+    <col min="53" max="53" width="11" style="2" customWidth="1"/>
     <col min="54" max="54" width="9.125" customWidth="1"/>
-    <col min="55" max="55" width="13.25" customWidth="1"/>
-    <col min="56" max="56" width="13.375" customWidth="1"/>
-    <col min="57" max="57" width="14" customWidth="1"/>
-    <col min="58" max="59" width="12.75" customWidth="1"/>
+    <col min="55" max="55" width="21.5" customWidth="1"/>
+    <col min="56" max="56" width="10.25" customWidth="1"/>
+    <col min="57" max="57" width="9.375" customWidth="1"/>
+    <col min="58" max="58" width="12.75" customWidth="1"/>
+    <col min="59" max="59" width="12.75" style="1" customWidth="1"/>
     <col min="60" max="60" width="13.75" customWidth="1"/>
     <col min="61" max="61" width="13.375" customWidth="1"/>
     <col min="62" max="62" width="11.75" customWidth="1"/>
@@ -1250,288 +1863,336 @@
     <col min="64" max="64" width="10" customWidth="1"/>
     <col min="65" max="65" width="11" customWidth="1"/>
     <col min="66" max="66" width="9.375"/>
+    <col min="68" max="68" width="11.875" style="6" customWidth="1"/>
+    <col min="69" max="69" width="12.5" style="6" customWidth="1"/>
+    <col min="70" max="70" width="12.125" style="6" customWidth="1"/>
+    <col min="71" max="76" width="9" style="6"/>
+    <col min="77" max="77" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:67">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:77">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AE1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AF1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AG1" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AI1" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AJ1" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AK1" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AL1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AM1" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AN1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AO1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AP1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AQ1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AR1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AS1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AT1" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AU1" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="AV1" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="3" t="s">
+      <c r="AW1" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="3" t="s">
+      <c r="AX1" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="3" t="s">
+      <c r="AY1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="3" t="s">
+      <c r="AZ1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="3" t="s">
+      <c r="BA1" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="3" t="s">
+      <c r="BB1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="3" t="s">
+      <c r="BC1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="3" t="s">
+      <c r="BD1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="3" t="s">
+      <c r="BE1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="3" t="s">
+      <c r="BF1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="3" t="s">
+      <c r="BG1" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="3" t="s">
+      <c r="BH1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="3" t="s">
+      <c r="BI1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="3" t="s">
+      <c r="BJ1" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="3" t="s">
+      <c r="BK1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="3" t="s">
+      <c r="BL1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="3" t="s">
+      <c r="BM1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="3" t="s">
+      <c r="BN1" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="3" t="s">
+      <c r="BO1" s="7" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="2" spans="15:66">
-      <c r="O2" s="2"/>
-      <c r="BB2" s="5"/>
-      <c r="BD2" s="2"/>
-      <c r="BH2" s="2"/>
-      <c r="BN2" s="6"/>
+      <c r="BP1" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="BX1" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="BY1" s="12" t="s">
+        <v>76</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="16">
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2 BD2">
-      <formula1>1</formula1>
-      <formula2>2958101</formula2>
+  <dataValidations count="21">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2 U3:U1048576">
+      <formula1>0</formula1>
+      <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE2 BH2">
-      <formula1>32874</formula1>
-      <formula2>2958101</formula2>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 V2 R3:R1048576 V3:V1048576 AR3:AR1048576 AX3:AX1048576 AY3:AY1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X4 X5:X1048576 AA2:AA4 AA5:AA1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 BP$1:BP$1048576 BQ$1:BQ$1048576 BT$1:BT$1048576 BW$1:BW$1048576 BX$1:BX$1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U4 U5:U1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2 W3:W1048576">
+      <formula1>0</formula1>
+      <formula2>999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2 S3:S1048576 AZ3:AZ1048576">
+      <formula1>0</formula1>
+      <formula2>9999999</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T$1:T$1048576 AM$1:AM$1048576 BA2:BA1048576">
+      <formula1>1</formula1>
+      <formula2>2958464</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT2:AT1048576 BU$1:BU$1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576 Z2:Z1048576 AA2:AA1048576">
+      <formula1>0</formula1>
+      <formula2>999999999</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK$1:AK$1048576 AL$1:AL$1048576">
+      <formula1>32874</formula1>
+      <formula2>2958464</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 AD2:AD1048576 AV2:AV1048576 BG$1:BG$1048576 BR$1:BR$1048576 BS$1:BS$1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X1048576 AB2:AB1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R4 R5:R1048576 V2:V4 V5:V1048576 AR2:AR1048576 AS2:AS1048576 AT2:AT1048576 AW2:AW1048576 AX2:AX1048576 AY2:AY1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576 BV$1:BV$1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y4 Y5:Y1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF$1:AF$1048576 AJ$1:AJ$1048576 AS2:AS1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG$1:AG$1048576 AH$1:AH$1048576 AI$1:AI$1048576 AN$1:AN$1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2:AU1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC3:BC1048576">
+      <formula1>0</formula1>
+      <formula2>9.99999999999999E+23</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY$1:BY$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T4 T5:T1048576 W2:W4 W5:W1048576 AC2:AC4 AC5:AC1048576">
-      <formula1>0</formula1>
-      <formula2>999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S4 S5:S1048576 AU2:AU4 AU5:AU1048576 AV2:AV4 AV5:AV6 AV8:AV1048576 AZ2:AZ4 AZ5:AZ1048576">
-      <formula1>0</formula1>
-      <formula2>9999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999999000</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999900</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA4 BA5:BA1048576 BG2:BG1048576">
-      <formula1>0</formula1>
-      <formula2>99999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BC1048576">
-      <formula1>0</formula1>
-      <formula2>9.99999999999999E+23</formula2>
     </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+21</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI2:BI1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI3:BI1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN2:BN1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN3:BN1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BO2:BO1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BO3:BO1048576">
       <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AU1:AU1048575" listDataValidation="1"/>
+    <ignoredError sqref="AU3:AU1048573" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="11940"/>
+    <workbookView windowWidth="28800" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -35,6 +42,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -50,6 +64,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -68,6 +89,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -83,6 +111,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -98,6 +133,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -113,6 +155,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -128,6 +177,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -143,6 +199,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -158,6 +221,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -173,6 +243,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -188,6 +265,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -203,6 +287,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -218,6 +309,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -254,6 +352,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -293,6 +398,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -332,6 +444,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -372,6 +491,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -387,6 +513,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -402,6 +535,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -441,6 +581,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -498,6 +645,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -513,6 +667,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -528,6 +689,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -543,6 +711,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -558,6 +733,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -573,6 +755,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -588,6 +777,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -603,6 +799,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -621,6 +824,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -639,6 +849,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -654,6 +871,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -673,6 +897,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>报关申报价（</t>
     </r>
     <r>
@@ -764,8 +995,8 @@
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0000_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="177" formatCode="0.0000_ "/>
     <numFmt numFmtId="178" formatCode="&quot;￥&quot;#,##0.0000;&quot;￥&quot;\-#,##0.0000"/>
     <numFmt numFmtId="179" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="180" formatCode="0_ "/>
@@ -1436,12 +1667,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1460,10 +1691,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1478,7 +1709,7 @@
     <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2104,22 +2335,37 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="21">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2 U3:U1048576">
+  <dataValidations count="18">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF$1:AF$1048576 AJ$1:AJ$1048576 AS2:AS1048576">
       <formula1>0</formula1>
-      <formula2>99999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 V2 R3:R1048576 V3:V1048576 AR3:AR1048576 AX3:AX1048576 AY3:AY1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
+      <formula2>99999999999</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 BP$1:BP$1048576 BQ$1:BQ$1048576 BT$1:BT$1048576 BW$1:BW$1048576 BX$1:BX$1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2 W3:W1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2 U3:U1048576 X2:X1048576 AB2:AB1048576">
+      <formula1>0</formula1>
+      <formula2>99999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY$1:BY$1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 V2 R3:R1048576 V3:V1048576 Y2:Y1048576 AR3:AR1048576 AX3:AX1048576 AY3:AY1048576 BV$1:BV$1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 AD2:AD1048576 AV2:AV1048576 BG$1:BG$1048576 BR$1:BR$1048576 BS$1:BS$1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2 P2:P1048576 W3:W1048576 Z2:Z1048576 AA2:AA1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BO3:BO1048576">
+      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2 S3:S1048576 AZ3:AZ1048576">
       <formula1>0</formula1>
@@ -2129,37 +2375,17 @@
       <formula1>1</formula1>
       <formula2>2958464</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT2:AT1048576 BU$1:BU$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG$1:AG$1048576 AH$1:AH$1048576 AI$1:AI$1048576 AN$1:AN$1048576">
       <formula1>0</formula1>
-      <formula2>9999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576 Z2:Z1048576 AA2:AA1048576">
-      <formula1>0</formula1>
-      <formula2>999999999</formula2>
+      <formula2>9999999999</formula2>
     </dataValidation>
     <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK$1:AK$1048576 AL$1:AL$1048576">
       <formula1>32874</formula1>
       <formula2>2958464</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 AD2:AD1048576 AV2:AV1048576 BG$1:BG$1048576 BR$1:BR$1048576 BS$1:BS$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT2:AT1048576 BU$1:BU$1048576">
       <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X1048576 AB2:AB1048576">
-      <formula1>0</formula1>
-      <formula2>99999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576 BV$1:BV$1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF$1:AF$1048576 AJ$1:AJ$1048576 AS2:AS1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG$1:AG$1048576 AH$1:AH$1048576 AI$1:AI$1048576 AN$1:AN$1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
+      <formula2>9999999999999</formula2>
     </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2:AU1048576">
       <formula1>0</formula1>
@@ -2168,10 +2394,6 @@
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC3:BC1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+23</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY$1:BY$1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
     </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF1048576">
       <formula1>0</formula1>
@@ -2185,9 +2407,6 @@
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BO3:BO1048576">
-      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12540"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -375,7 +375,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Helvetica"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -391,7 +391,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Helvetica"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -421,7 +421,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Helvetica"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -437,7 +437,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Helvetica"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -467,7 +467,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Helvetica"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -484,7 +484,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Helvetica"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -558,7 +558,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Helvetica"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -574,7 +574,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Helvetica"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -910,7 +910,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Helvetica"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>$</t>
     </r>
@@ -989,20 +989,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="177" formatCode="0.0000_ "/>
-    <numFmt numFmtId="178" formatCode="&quot;￥&quot;#,##0.0000;&quot;￥&quot;\-#,##0.0000"/>
-    <numFmt numFmtId="179" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="180" formatCode="0_ "/>
-    <numFmt numFmtId="181" formatCode="0.00_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="5">
+    <numFmt numFmtId="178" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="179" formatCode="0.0000_ "/>
+    <numFmt numFmtId="181" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="182" formatCode="0_ "/>
+    <numFmt numFmtId="183" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1025,160 +1020,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <name val="Helvetica"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -1197,202 +1041,23 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1415,251 +1080,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1667,22 +1090,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1691,82 +1111,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2028,14 +1404,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BY1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -2053,31 +1429,31 @@
     <col min="21" max="21" width="16.625" customWidth="1"/>
     <col min="22" max="22" width="5.875" customWidth="1"/>
     <col min="23" max="23" width="9.75" customWidth="1"/>
-    <col min="24" max="24" width="15.125" style="3" customWidth="1"/>
+    <col min="24" max="24" width="15.125" style="16" customWidth="1"/>
     <col min="25" max="25" width="15" style="1" customWidth="1"/>
     <col min="26" max="26" width="14.875" style="1" customWidth="1"/>
     <col min="27" max="27" width="8.75" style="1" customWidth="1"/>
     <col min="28" max="28" width="15.25" style="1" customWidth="1"/>
     <col min="29" max="29" width="16.75" style="1" customWidth="1"/>
     <col min="30" max="30" width="14" style="1" customWidth="1"/>
-    <col min="31" max="31" width="11.5" style="4"/>
-    <col min="32" max="32" width="13" style="5" customWidth="1"/>
-    <col min="33" max="33" width="12.25" style="5" customWidth="1"/>
-    <col min="34" max="34" width="11.125" style="5" customWidth="1"/>
-    <col min="35" max="35" width="13.625" style="5" customWidth="1"/>
-    <col min="36" max="36" width="12.625" style="5" customWidth="1"/>
+    <col min="31" max="31" width="11.5" style="3"/>
+    <col min="32" max="32" width="13" style="4" customWidth="1"/>
+    <col min="33" max="33" width="12.25" style="4" customWidth="1"/>
+    <col min="34" max="34" width="11.125" style="4" customWidth="1"/>
+    <col min="35" max="35" width="13.625" style="4" customWidth="1"/>
+    <col min="36" max="36" width="12.625" style="4" customWidth="1"/>
     <col min="37" max="37" width="14.25" style="2" customWidth="1"/>
     <col min="38" max="38" width="14.5" style="2" customWidth="1"/>
     <col min="39" max="39" width="12" style="2" customWidth="1"/>
-    <col min="40" max="40" width="10.75" style="5" customWidth="1"/>
+    <col min="40" max="40" width="10.75" style="4" customWidth="1"/>
     <col min="42" max="42" width="10.75" customWidth="1"/>
     <col min="43" max="43" width="16.375" customWidth="1"/>
     <col min="44" max="44" width="12.375" customWidth="1"/>
-    <col min="45" max="45" width="11.5" style="5" customWidth="1"/>
+    <col min="45" max="45" width="11.5" style="4" customWidth="1"/>
     <col min="46" max="46" width="15.875" style="1" customWidth="1"/>
-    <col min="47" max="47" width="11.625" style="5" customWidth="1"/>
+    <col min="47" max="47" width="11.625" style="4" customWidth="1"/>
     <col min="48" max="48" width="15.875" style="1" customWidth="1"/>
-    <col min="49" max="49" width="13.5" style="5" customWidth="1"/>
+    <col min="49" max="49" width="13.5" style="4" customWidth="1"/>
     <col min="51" max="51" width="11.75" customWidth="1"/>
     <col min="52" max="52" width="12" customWidth="1"/>
     <col min="53" max="53" width="11" style="2" customWidth="1"/>
@@ -2094,322 +1470,323 @@
     <col min="64" max="64" width="10" customWidth="1"/>
     <col min="65" max="65" width="11" customWidth="1"/>
     <col min="66" max="66" width="9.375"/>
-    <col min="68" max="68" width="11.875" style="6" customWidth="1"/>
-    <col min="69" max="69" width="12.5" style="6" customWidth="1"/>
-    <col min="70" max="70" width="12.125" style="6" customWidth="1"/>
-    <col min="71" max="76" width="9" style="6"/>
-    <col min="77" max="77" width="9" style="5"/>
+    <col min="68" max="68" width="11.875" style="5" customWidth="1"/>
+    <col min="69" max="69" width="12.5" style="5" customWidth="1"/>
+    <col min="70" max="70" width="12.125" style="5" customWidth="1"/>
+    <col min="71" max="76" width="9" style="5"/>
+    <col min="77" max="77" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:77" x14ac:dyDescent="0.15">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="T1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="7" t="s">
+      <c r="U1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="7" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="7" t="s">
+      <c r="W1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="11" t="s">
+      <c r="X1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="9" t="s">
+      <c r="Y1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="9" t="s">
+      <c r="Z1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="9" t="s">
+      <c r="AA1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="9" t="s">
+      <c r="AB1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="9" t="s">
+      <c r="AC1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AD1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="7" t="s">
+      <c r="AE1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="12" t="s">
+      <c r="AF1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="12" t="s">
+      <c r="AG1" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="12" t="s">
+      <c r="AH1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="12" t="s">
+      <c r="AI1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="13" t="s">
+      <c r="AJ1" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="10" t="s">
+      <c r="AK1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="10" t="s">
+      <c r="AL1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="10" t="s">
+      <c r="AM1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="12" t="s">
+      <c r="AN1" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="7" t="s">
+      <c r="AO1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="7" t="s">
+      <c r="AP1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="7" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="7" t="s">
+      <c r="AR1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="14" t="s">
+      <c r="AS1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="9" t="s">
+      <c r="AT1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="14" t="s">
+      <c r="AU1" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="9" t="s">
+      <c r="AV1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="14" t="s">
+      <c r="AW1" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="8" t="s">
+      <c r="AX1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="8" t="s">
+      <c r="AY1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="8" t="s">
+      <c r="AZ1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="10" t="s">
+      <c r="BA1" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="8" t="s">
+      <c r="BB1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="7" t="s">
+      <c r="BC1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="8" t="s">
+      <c r="BD1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="8" t="s">
+      <c r="BE1" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="7" t="s">
+      <c r="BF1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="15" t="s">
+      <c r="BG1" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="7" t="s">
+      <c r="BH1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="7" t="s">
+      <c r="BI1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="7" t="s">
+      <c r="BJ1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="7" t="s">
+      <c r="BK1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="7" t="s">
+      <c r="BL1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="7" t="s">
+      <c r="BM1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="7" t="s">
+      <c r="BN1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="7" t="s">
+      <c r="BO1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="16" t="s">
+      <c r="BP1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="16" t="s">
+      <c r="BQ1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="16" t="s">
+      <c r="BR1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="16" t="s">
+      <c r="BS1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="16" t="s">
+      <c r="BT1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="16" t="s">
+      <c r="BU1" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="16" t="s">
+      <c r="BV1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" s="16" t="s">
+      <c r="BW1" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" s="16" t="s">
+      <c r="BX1" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" s="12" t="s">
+      <c r="BY1" s="10" t="s">
         <v>76</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="18">
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF$1:AF$1048576 AJ$1:AJ$1048576 AS2:AS1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF1:AF1048576 AJ1:AJ1048576 AS2:AS1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 BP$1:BP$1048576 BQ$1:BQ$1048576 BT$1:BT$1048576 BW$1:BW$1048576 BX$1:BX$1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 BP1:BP1048576 BQ1:BQ1048576 BT1:BT1048576 BW1:BW1048576 BX1:BX1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2 U3:U1048576 X2:X1048576 AB2:AB1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2 U3:U1048576 X2:X1048576 AB2:AB1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY$1:BY$1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY1:BY1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 V2 R3:R1048576 V3:V1048576 Y2:Y1048576 AR3:AR1048576 AX3:AX1048576 AY3:AY1048576 BV$1:BV$1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 V2 R3:R1048576 V3:V1048576 Y2:Y1048576 AR3:AR1048576 AX3:AX1048576 AY3:AY1048576 BV1:BV1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 AD2:AD1048576 AV2:AV1048576 BG$1:BG$1048576 BR$1:BR$1048576 BS$1:BS$1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 AD2:AD1048576 AV2:AV1048576 BG1:BG1048576 BR1:BR1048576 BS1:BS1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2 P2:P1048576 W3:W1048576 Z2:Z1048576 AA2:AA1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2 P2:P1048576 W3:W1048576 Z2:Z1048576 AA2:AA1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BO3:BO1048576">
       <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2 S3:S1048576 AZ3:AZ1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2 S3:S1048576 AZ3:AZ1048576">
       <formula1>0</formula1>
       <formula2>9999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T$1:T$1048576 AM$1:AM$1048576 BA2:BA1048576">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T1:T1048576 AM1:AM1048576 BA2:BA1048576">
       <formula1>1</formula1>
       <formula2>2958464</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG$1:AG$1048576 AH$1:AH$1048576 AI$1:AI$1048576 AN$1:AN$1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG1:AG1048576 AH1:AH1048576 AI1:AI1048576 AN1:AN1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK$1:AK$1048576 AL$1:AL$1048576">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK1:AK1048576 AL1:AL1048576">
       <formula1>32874</formula1>
       <formula2>2958464</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT2:AT1048576 BU$1:BU$1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT2:AT1048576 BU1:BU1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2:AU1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2:AU1048576">
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC3:BC1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC3:BC1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+23</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+21</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI3:BI1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI3:BI1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN3:BN1048576">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN3:BN1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="AU3:AU1048573" listDataValidation="1"/>
   </ignoredErrors>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -1,20 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12540"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>spu</t>
   </si>
@@ -152,6 +165,23 @@
       </rPr>
       <t>品名（英文）</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>产品类型</t>
+    </r>
+  </si>
+  <si>
+    <t>迭代产品</t>
   </si>
   <si>
     <r>
@@ -375,7 +405,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Helvetica"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>(</t>
     </r>
@@ -391,7 +421,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Helvetica"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
@@ -421,7 +451,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Helvetica"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>(</t>
     </r>
@@ -437,7 +467,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Helvetica"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
@@ -467,7 +497,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Helvetica"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>(</t>
     </r>
@@ -484,7 +514,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Helvetica"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
@@ -558,7 +588,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Helvetica"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>(</t>
     </r>
@@ -574,7 +604,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Helvetica"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
@@ -910,7 +940,7 @@
       <rPr>
         <sz val="10.5"/>
         <rFont val="Helvetica"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>$</t>
     </r>
@@ -989,15 +1019,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="5">
-    <numFmt numFmtId="178" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="179" formatCode="0.0000_ "/>
-    <numFmt numFmtId="181" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="182" formatCode="0_ "/>
-    <numFmt numFmtId="183" formatCode="0.00_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="9">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.0000_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="179" formatCode="0_ "/>
+    <numFmt numFmtId="180" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1020,9 +1054,166 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <name val="Helvetica"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -1041,23 +1232,202 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1080,29 +1450,274 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1111,38 +1726,85 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1404,120 +2066,122 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BY1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:CA1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="8" max="8" width="12.375" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
-    <col min="10" max="10" width="7.75" customWidth="1"/>
-    <col min="11" max="11" width="12.75" customWidth="1"/>
-    <col min="14" max="14" width="11.5" customWidth="1"/>
-    <col min="15" max="15" width="12.125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="15.375" customWidth="1"/>
-    <col min="18" max="18" width="15.875" customWidth="1"/>
-    <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="12" style="2" customWidth="1"/>
-    <col min="21" max="21" width="16.625" customWidth="1"/>
-    <col min="22" max="22" width="5.875" customWidth="1"/>
-    <col min="23" max="23" width="9.75" customWidth="1"/>
-    <col min="24" max="24" width="15.125" style="16" customWidth="1"/>
-    <col min="25" max="25" width="15" style="1" customWidth="1"/>
-    <col min="26" max="26" width="14.875" style="1" customWidth="1"/>
-    <col min="27" max="27" width="8.75" style="1" customWidth="1"/>
-    <col min="28" max="28" width="15.25" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16.75" style="1" customWidth="1"/>
-    <col min="30" max="30" width="14" style="1" customWidth="1"/>
-    <col min="31" max="31" width="11.5" style="3"/>
-    <col min="32" max="32" width="13" style="4" customWidth="1"/>
-    <col min="33" max="33" width="12.25" style="4" customWidth="1"/>
-    <col min="34" max="34" width="11.125" style="4" customWidth="1"/>
-    <col min="35" max="35" width="13.625" style="4" customWidth="1"/>
-    <col min="36" max="36" width="12.625" style="4" customWidth="1"/>
-    <col min="37" max="37" width="14.25" style="2" customWidth="1"/>
-    <col min="38" max="38" width="14.5" style="2" customWidth="1"/>
-    <col min="39" max="39" width="12" style="2" customWidth="1"/>
-    <col min="40" max="40" width="10.75" style="4" customWidth="1"/>
-    <col min="42" max="42" width="10.75" customWidth="1"/>
-    <col min="43" max="43" width="16.375" customWidth="1"/>
-    <col min="44" max="44" width="12.375" customWidth="1"/>
-    <col min="45" max="45" width="11.5" style="4" customWidth="1"/>
-    <col min="46" max="46" width="15.875" style="1" customWidth="1"/>
-    <col min="47" max="47" width="11.625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="10.5" customWidth="1"/>
+    <col min="10" max="10" width="12.375" customWidth="1"/>
+    <col min="11" max="11" width="9" customWidth="1"/>
+    <col min="12" max="12" width="7.75" customWidth="1"/>
+    <col min="13" max="13" width="12.75" customWidth="1"/>
+    <col min="16" max="16" width="11.5" customWidth="1"/>
+    <col min="17" max="17" width="12.125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="14.375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="15.375" customWidth="1"/>
+    <col min="20" max="20" width="15.875" customWidth="1"/>
+    <col min="21" max="21" width="11" customWidth="1"/>
+    <col min="22" max="22" width="12" style="2" customWidth="1"/>
+    <col min="23" max="23" width="16.625" customWidth="1"/>
+    <col min="24" max="24" width="5.875" customWidth="1"/>
+    <col min="25" max="25" width="9.75" customWidth="1"/>
+    <col min="26" max="26" width="15.125" style="3" customWidth="1"/>
+    <col min="27" max="27" width="15" style="1" customWidth="1"/>
+    <col min="28" max="28" width="14.875" style="1" customWidth="1"/>
+    <col min="29" max="29" width="8.75" style="1" customWidth="1"/>
+    <col min="30" max="30" width="15.25" style="1" customWidth="1"/>
+    <col min="31" max="31" width="16.75" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14" style="1" customWidth="1"/>
+    <col min="33" max="33" width="11.5" style="4"/>
+    <col min="34" max="34" width="13" style="5" customWidth="1"/>
+    <col min="35" max="35" width="12.25" style="5" customWidth="1"/>
+    <col min="36" max="36" width="11.125" style="5" customWidth="1"/>
+    <col min="37" max="37" width="13.625" style="5" customWidth="1"/>
+    <col min="38" max="38" width="12.625" style="5" customWidth="1"/>
+    <col min="39" max="39" width="14.25" style="2" customWidth="1"/>
+    <col min="40" max="40" width="14.5" style="2" customWidth="1"/>
+    <col min="41" max="41" width="12" style="2" customWidth="1"/>
+    <col min="42" max="42" width="10.75" style="5" customWidth="1"/>
+    <col min="44" max="44" width="10.75" customWidth="1"/>
+    <col min="45" max="45" width="16.375" customWidth="1"/>
+    <col min="46" max="46" width="12.375" customWidth="1"/>
+    <col min="47" max="47" width="11.5" style="5" customWidth="1"/>
     <col min="48" max="48" width="15.875" style="1" customWidth="1"/>
-    <col min="49" max="49" width="13.5" style="4" customWidth="1"/>
-    <col min="51" max="51" width="11.75" customWidth="1"/>
-    <col min="52" max="52" width="12" customWidth="1"/>
-    <col min="53" max="53" width="11" style="2" customWidth="1"/>
-    <col min="54" max="54" width="9.125" customWidth="1"/>
-    <col min="55" max="55" width="21.5" customWidth="1"/>
-    <col min="56" max="56" width="10.25" customWidth="1"/>
-    <col min="57" max="57" width="9.375" customWidth="1"/>
-    <col min="58" max="58" width="12.75" customWidth="1"/>
-    <col min="59" max="59" width="12.75" style="1" customWidth="1"/>
-    <col min="60" max="60" width="13.75" customWidth="1"/>
-    <col min="61" max="61" width="13.375" customWidth="1"/>
-    <col min="62" max="62" width="11.75" customWidth="1"/>
-    <col min="63" max="63" width="9.875" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="11" customWidth="1"/>
-    <col min="66" max="66" width="9.375"/>
-    <col min="68" max="68" width="11.875" style="5" customWidth="1"/>
-    <col min="69" max="69" width="12.5" style="5" customWidth="1"/>
-    <col min="70" max="70" width="12.125" style="5" customWidth="1"/>
-    <col min="71" max="76" width="9" style="5"/>
-    <col min="77" max="77" width="9" style="4"/>
+    <col min="49" max="49" width="11.625" style="5" customWidth="1"/>
+    <col min="50" max="50" width="15.875" style="1" customWidth="1"/>
+    <col min="51" max="51" width="13.5" style="5" customWidth="1"/>
+    <col min="53" max="53" width="11.75" customWidth="1"/>
+    <col min="54" max="54" width="12" customWidth="1"/>
+    <col min="55" max="55" width="11" style="2" customWidth="1"/>
+    <col min="56" max="56" width="9.125" customWidth="1"/>
+    <col min="57" max="57" width="21.5" customWidth="1"/>
+    <col min="58" max="58" width="10.25" customWidth="1"/>
+    <col min="59" max="59" width="9.375" customWidth="1"/>
+    <col min="60" max="60" width="12.75" customWidth="1"/>
+    <col min="61" max="61" width="12.75" style="1" customWidth="1"/>
+    <col min="62" max="62" width="13.75" customWidth="1"/>
+    <col min="63" max="63" width="13.375" customWidth="1"/>
+    <col min="64" max="64" width="11.75" customWidth="1"/>
+    <col min="65" max="65" width="9.875" customWidth="1"/>
+    <col min="66" max="66" width="10" customWidth="1"/>
+    <col min="67" max="67" width="11" customWidth="1"/>
+    <col min="68" max="68" width="9.375"/>
+    <col min="70" max="70" width="11.875" style="6" customWidth="1"/>
+    <col min="71" max="71" width="12.5" style="6" customWidth="1"/>
+    <col min="72" max="72" width="12.125" style="6" customWidth="1"/>
+    <col min="73" max="78" width="9" style="6"/>
+    <col min="79" max="79" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" x14ac:dyDescent="0.15">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:79">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="8" t="s">
@@ -1526,269 +2190,278 @@
       <c r="P1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="T1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="15" t="s">
+      <c r="X1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Y1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="Z1" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AA1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="8" t="s">
+      <c r="AB1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="8" t="s">
+      <c r="AC1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="8" t="s">
+      <c r="AD1" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AE1" s="10" t="s">
         <v>30</v>
       </c>
       <c r="AF1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="10" t="s">
+      <c r="AG1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="10" t="s">
+      <c r="AH1" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="10" t="s">
+      <c r="AI1" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="11" t="s">
+      <c r="AJ1" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="9" t="s">
+      <c r="AK1" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="9" t="s">
+      <c r="AL1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="9" t="s">
+      <c r="AM1" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="10" t="s">
+      <c r="AN1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AO1" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AP1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AQ1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AR1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="12" t="s">
+      <c r="AS1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="8" t="s">
+      <c r="AT1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="12" t="s">
+      <c r="AU1" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="8" t="s">
+      <c r="AV1" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="12" t="s">
+      <c r="AW1" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="7" t="s">
+      <c r="AX1" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="7" t="s">
+      <c r="AY1" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="7" t="s">
+      <c r="AZ1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="9" t="s">
+      <c r="BA1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="7" t="s">
+      <c r="BB1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BC1" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="7" t="s">
+      <c r="BD1" s="8" t="s">
         <v>55</v>
       </c>
       <c r="BE1" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BF1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="13" t="s">
+      <c r="BG1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="6" t="s">
+      <c r="BH1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="6" t="s">
+      <c r="BI1" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="6" t="s">
+      <c r="BJ1" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="6" t="s">
+      <c r="BK1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="6" t="s">
+      <c r="BL1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="6" t="s">
+      <c r="BM1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="6" t="s">
+      <c r="BN1" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="6" t="s">
+      <c r="BO1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="14" t="s">
+      <c r="BP1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="14" t="s">
+      <c r="BQ1" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="14" t="s">
+      <c r="BR1" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="14" t="s">
+      <c r="BS1" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="14" t="s">
+      <c r="BT1" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="14" t="s">
+      <c r="BU1" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="14" t="s">
+      <c r="BV1" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" s="14" t="s">
+      <c r="BW1" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" s="14" t="s">
+      <c r="BX1" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" s="10" t="s">
+      <c r="BY1" s="17" t="s">
         <v>76</v>
+      </c>
+      <c r="BZ1" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="CA1" s="13" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <dataValidations count="18">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF1:AF1048576 AJ1:AJ1048576 AS2:AS1048576">
+  <dataValidations count="19">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2 X2 T3:T1048576 X3:X1048576 AA2:AA1048576 AT3:AT1048576 AZ3:AZ1048576 BA3:BA1048576 BX$1:BX$1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2 U3:U1048576 BB3:BB1048576">
+      <formula1>0</formula1>
+      <formula2>9999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2 W3:W1048576 Z2:Z1048576 AD2:AD1048576">
+      <formula1>0</formula1>
+      <formula2>99999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2 R2:R1048576 Y3:Y1048576 AB2:AB1048576 AC2:AC1048576">
+      <formula1>0</formula1>
+      <formula2>999999999</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I$1:I$1048576">
+      <formula1>"新产品,迭代产品"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q1048576 AF2:AF1048576 AX2:AX1048576 BI$1:BI$1048576 BT$1:BT$1048576 BU$1:BU$1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V$1:V$1048576 AO$1:AO$1048576 BC2:BC1048576">
+      <formula1>1</formula1>
+      <formula2>2958464</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE1048576 BR$1:BR$1048576 BS$1:BS$1048576 BV$1:BV$1048576 BY$1:BY$1048576 BZ$1:BZ$1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 BP1:BP1048576 BQ1:BQ1048576 BT1:BT1048576 BW1:BW1048576 BX1:BX1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH$1:AH$1048576 AL$1:AL$1048576 AU2:AU1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2 U3:U1048576 X2:X1048576 AB2:AB1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AJ$1:AJ$1048576 AK$1:AK$1048576 AP$1:AP$1048576">
       <formula1>0</formula1>
-      <formula2>99999999</formula2>
+      <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY1:BY1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM$1:AM$1048576 AN$1:AN$1048576">
+      <formula1>32874</formula1>
+      <formula2>2958464</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2:AV1048576 BW$1:BW$1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY1048576 CA$1:CA$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 V2 R3:R1048576 V3:V1048576 Y2:Y1048576 AR3:AR1048576 AX3:AX1048576 AY3:AY1048576 BV1:BV1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576 AD2:AD1048576 AV2:AV1048576 BG1:BG1048576 BR1:BR1048576 BS1:BS1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2 P2:P1048576 W3:W1048576 Z2:Z1048576 AA2:AA1048576">
-      <formula1>0</formula1>
-      <formula2>999999999</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BO3:BO1048576">
-      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2 S3:S1048576 AZ3:AZ1048576">
-      <formula1>0</formula1>
-      <formula2>9999999</formula2>
-    </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T1:T1048576 AM1:AM1048576 BA2:BA1048576">
-      <formula1>1</formula1>
-      <formula2>2958464</formula2>
-    </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG1:AG1048576 AH1:AH1048576 AI1:AI1048576 AN1:AN1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK1:AK1048576 AL1:AL1048576">
-      <formula1>32874</formula1>
-      <formula2>2958464</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT2:AT1048576 BU1:BU1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2:AU1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC3:BC1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE3:BE1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+23</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+21</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI3:BI1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK3:BK1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN3:BN1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BP3:BP1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BQ3:BQ1048576">
+      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AU3:AU1048573" listDataValidation="1"/>
+    <ignoredError sqref="AW3:AW1048573" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="23130" windowHeight="11850"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t>spu</t>
   </si>
@@ -168,6 +168,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1014,6 +1021,12 @@
   </si>
   <si>
     <t>单箱数量</t>
+  </si>
+  <si>
+    <t>推荐仓位(小货区)</t>
+  </si>
+  <si>
+    <t>推荐仓位(大货区)</t>
   </si>
 </sst>
 </file>
@@ -1698,7 +1711,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1718,6 +1731,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1751,6 +1767,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2072,8 +2094,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CA1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:CC2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -2139,246 +2161,258 @@
     <col min="72" max="72" width="12.125" style="6" customWidth="1"/>
     <col min="73" max="78" width="9" style="6"/>
     <col min="79" max="79" width="9" style="5"/>
+    <col min="80" max="81" width="11.125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:79">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:81">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="Q1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="R1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="S1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="T1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="7" t="s">
+      <c r="U1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="11" t="s">
+      <c r="V1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="7" t="s">
+      <c r="W1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="X1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="Y1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="12" t="s">
+      <c r="Z1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AA1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="10" t="s">
+      <c r="AB1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="10" t="s">
+      <c r="AC1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="10" t="s">
+      <c r="AD1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="10" t="s">
+      <c r="AE1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="10" t="s">
+      <c r="AF1" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="7" t="s">
+      <c r="AG1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="13" t="s">
+      <c r="AH1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="13" t="s">
+      <c r="AI1" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="13" t="s">
+      <c r="AJ1" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="13" t="s">
+      <c r="AK1" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="14" t="s">
+      <c r="AL1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="11" t="s">
+      <c r="AM1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="11" t="s">
+      <c r="AN1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="11" t="s">
+      <c r="AO1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="13" t="s">
+      <c r="AP1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="7" t="s">
+      <c r="AQ1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="7" t="s">
+      <c r="AR1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="7" t="s">
+      <c r="AS1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="7" t="s">
+      <c r="AT1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="15" t="s">
+      <c r="AU1" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="10" t="s">
+      <c r="AV1" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="15" t="s">
+      <c r="AW1" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="10" t="s">
+      <c r="AX1" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="15" t="s">
+      <c r="AY1" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="8" t="s">
+      <c r="AZ1" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="8" t="s">
+      <c r="BA1" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="8" t="s">
+      <c r="BB1" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="11" t="s">
+      <c r="BC1" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="8" t="s">
+      <c r="BD1" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="7" t="s">
+      <c r="BE1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="8" t="s">
+      <c r="BF1" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="8" t="s">
+      <c r="BG1" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="7" t="s">
+      <c r="BH1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="16" t="s">
+      <c r="BI1" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="7" t="s">
+      <c r="BJ1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="7" t="s">
+      <c r="BK1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="7" t="s">
+      <c r="BL1" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="7" t="s">
+      <c r="BM1" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="7" t="s">
+      <c r="BN1" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="7" t="s">
+      <c r="BO1" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="7" t="s">
+      <c r="BP1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="7" t="s">
+      <c r="BQ1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="17" t="s">
+      <c r="BR1" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="17" t="s">
+      <c r="BS1" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="17" t="s">
+      <c r="BT1" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="17" t="s">
+      <c r="BU1" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="17" t="s">
+      <c r="BV1" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" s="17" t="s">
+      <c r="BW1" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" s="17" t="s">
+      <c r="BX1" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" s="17" t="s">
+      <c r="BY1" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" s="17" t="s">
+      <c r="BZ1" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="CA1" s="13" t="s">
+      <c r="CA1" s="14" t="s">
         <v>78</v>
       </c>
+      <c r="CB1" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC1" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="79:81">
+      <c r="CA2" s="20"/>
+      <c r="CB2" s="20"/>
+      <c r="CC2" s="20"/>
     </row>
   </sheetData>
   <dataValidations count="19">

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowWidth="23130" windowHeight="11850"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
   <si>
     <t>spu</t>
   </si>
@@ -55,13 +55,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -76,25 +69,21 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>二级分类</t>
+    <t>二级分类</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>应用分类</t>
     </r>
   </si>
   <si>
@@ -102,13 +91,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1769,10 +1751,10 @@
     <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2094,77 +2076,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CC2"/>
+  <dimension ref="A1:CD2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="8" max="8" width="12.375" customWidth="1"/>
-    <col min="9" max="9" width="10.5" customWidth="1"/>
-    <col min="10" max="10" width="12.375" customWidth="1"/>
-    <col min="11" max="11" width="9" customWidth="1"/>
-    <col min="12" max="12" width="7.75" customWidth="1"/>
-    <col min="13" max="13" width="12.75" customWidth="1"/>
-    <col min="16" max="16" width="11.5" customWidth="1"/>
-    <col min="17" max="17" width="12.125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="14.375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="15.375" customWidth="1"/>
-    <col min="20" max="20" width="15.875" customWidth="1"/>
-    <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="12" style="2" customWidth="1"/>
-    <col min="23" max="23" width="16.625" customWidth="1"/>
-    <col min="24" max="24" width="5.875" customWidth="1"/>
-    <col min="25" max="25" width="9.75" customWidth="1"/>
-    <col min="26" max="26" width="15.125" style="3" customWidth="1"/>
-    <col min="27" max="27" width="15" style="1" customWidth="1"/>
-    <col min="28" max="28" width="14.875" style="1" customWidth="1"/>
-    <col min="29" max="29" width="8.75" style="1" customWidth="1"/>
-    <col min="30" max="30" width="15.25" style="1" customWidth="1"/>
-    <col min="31" max="31" width="16.75" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14" style="1" customWidth="1"/>
-    <col min="33" max="33" width="11.5" style="4"/>
-    <col min="34" max="34" width="13" style="5" customWidth="1"/>
-    <col min="35" max="35" width="12.25" style="5" customWidth="1"/>
-    <col min="36" max="36" width="11.125" style="5" customWidth="1"/>
-    <col min="37" max="37" width="13.625" style="5" customWidth="1"/>
-    <col min="38" max="38" width="12.625" style="5" customWidth="1"/>
-    <col min="39" max="39" width="14.25" style="2" customWidth="1"/>
-    <col min="40" max="40" width="14.5" style="2" customWidth="1"/>
-    <col min="41" max="41" width="12" style="2" customWidth="1"/>
-    <col min="42" max="42" width="10.75" style="5" customWidth="1"/>
-    <col min="44" max="44" width="10.75" customWidth="1"/>
-    <col min="45" max="45" width="16.375" customWidth="1"/>
-    <col min="46" max="46" width="12.375" customWidth="1"/>
-    <col min="47" max="47" width="11.5" style="5" customWidth="1"/>
-    <col min="48" max="48" width="15.875" style="1" customWidth="1"/>
-    <col min="49" max="49" width="11.625" style="5" customWidth="1"/>
-    <col min="50" max="50" width="15.875" style="1" customWidth="1"/>
-    <col min="51" max="51" width="13.5" style="5" customWidth="1"/>
-    <col min="53" max="53" width="11.75" customWidth="1"/>
-    <col min="54" max="54" width="12" customWidth="1"/>
-    <col min="55" max="55" width="11" style="2" customWidth="1"/>
-    <col min="56" max="56" width="9.125" customWidth="1"/>
-    <col min="57" max="57" width="21.5" customWidth="1"/>
-    <col min="58" max="58" width="10.25" customWidth="1"/>
-    <col min="59" max="59" width="9.375" customWidth="1"/>
-    <col min="60" max="60" width="12.75" customWidth="1"/>
-    <col min="61" max="61" width="12.75" style="1" customWidth="1"/>
-    <col min="62" max="62" width="13.75" customWidth="1"/>
-    <col min="63" max="63" width="13.375" customWidth="1"/>
-    <col min="64" max="64" width="11.75" customWidth="1"/>
-    <col min="65" max="65" width="9.875" customWidth="1"/>
-    <col min="66" max="66" width="10" customWidth="1"/>
-    <col min="67" max="67" width="11" customWidth="1"/>
-    <col min="68" max="68" width="9.375"/>
-    <col min="70" max="70" width="11.875" style="6" customWidth="1"/>
-    <col min="71" max="71" width="12.5" style="6" customWidth="1"/>
-    <col min="72" max="72" width="12.125" style="6" customWidth="1"/>
-    <col min="73" max="78" width="9" style="6"/>
-    <col min="79" max="79" width="9" style="5"/>
-    <col min="80" max="81" width="11.125" style="7" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="13" max="13" width="7.75" customWidth="1"/>
+    <col min="14" max="14" width="12.75" customWidth="1"/>
+    <col min="17" max="17" width="11.5" customWidth="1"/>
+    <col min="18" max="18" width="12.125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="14.375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="15.375" customWidth="1"/>
+    <col min="21" max="21" width="15.875" customWidth="1"/>
+    <col min="22" max="22" width="11" customWidth="1"/>
+    <col min="23" max="23" width="12" style="2" customWidth="1"/>
+    <col min="24" max="24" width="16.625" customWidth="1"/>
+    <col min="25" max="25" width="5.875" customWidth="1"/>
+    <col min="26" max="26" width="9.75" customWidth="1"/>
+    <col min="27" max="27" width="15.125" style="3" customWidth="1"/>
+    <col min="28" max="28" width="15" style="1" customWidth="1"/>
+    <col min="29" max="29" width="14.875" style="1" customWidth="1"/>
+    <col min="30" max="30" width="8.75" style="1" customWidth="1"/>
+    <col min="31" max="31" width="15.25" style="1" customWidth="1"/>
+    <col min="32" max="32" width="16.75" style="1" customWidth="1"/>
+    <col min="33" max="33" width="14" style="1" customWidth="1"/>
+    <col min="34" max="34" width="11.5" style="4"/>
+    <col min="35" max="35" width="13" style="5" customWidth="1"/>
+    <col min="36" max="36" width="12.25" style="5" customWidth="1"/>
+    <col min="37" max="37" width="11.125" style="5" customWidth="1"/>
+    <col min="38" max="38" width="13.625" style="5" customWidth="1"/>
+    <col min="39" max="39" width="12.625" style="5" customWidth="1"/>
+    <col min="40" max="40" width="14.25" style="2" customWidth="1"/>
+    <col min="41" max="41" width="14.5" style="2" customWidth="1"/>
+    <col min="42" max="42" width="12" style="2" customWidth="1"/>
+    <col min="43" max="43" width="10.75" style="5" customWidth="1"/>
+    <col min="45" max="45" width="10.75" customWidth="1"/>
+    <col min="46" max="46" width="16.375" customWidth="1"/>
+    <col min="47" max="47" width="12.375" customWidth="1"/>
+    <col min="48" max="48" width="11.5" style="5" customWidth="1"/>
+    <col min="49" max="49" width="15.875" style="1" customWidth="1"/>
+    <col min="50" max="50" width="11.625" style="5" customWidth="1"/>
+    <col min="51" max="51" width="15.875" style="1" customWidth="1"/>
+    <col min="52" max="52" width="13.5" style="5" customWidth="1"/>
+    <col min="54" max="54" width="11.75" customWidth="1"/>
+    <col min="55" max="55" width="12" customWidth="1"/>
+    <col min="56" max="56" width="11" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.125" customWidth="1"/>
+    <col min="58" max="58" width="21.5" customWidth="1"/>
+    <col min="59" max="59" width="10.25" customWidth="1"/>
+    <col min="60" max="60" width="9.375" customWidth="1"/>
+    <col min="61" max="61" width="12.75" customWidth="1"/>
+    <col min="62" max="62" width="12.75" style="1" customWidth="1"/>
+    <col min="63" max="63" width="13.75" customWidth="1"/>
+    <col min="64" max="64" width="13.375" customWidth="1"/>
+    <col min="65" max="65" width="11.75" customWidth="1"/>
+    <col min="66" max="66" width="9.875" customWidth="1"/>
+    <col min="67" max="67" width="10" customWidth="1"/>
+    <col min="68" max="68" width="11" customWidth="1"/>
+    <col min="69" max="69" width="9.375"/>
+    <col min="71" max="71" width="11.875" style="6" customWidth="1"/>
+    <col min="72" max="72" width="12.5" style="6" customWidth="1"/>
+    <col min="73" max="73" width="12.125" style="6" customWidth="1"/>
+    <col min="74" max="79" width="9" style="6"/>
+    <col min="80" max="80" width="9" style="5"/>
+    <col min="81" max="82" width="11.125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:81">
+    <row r="1" spans="1:82">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -2174,13 +2156,13 @@
       <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="9" t="s">
@@ -2192,10 +2174,10 @@
       <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="9" t="s">
@@ -2213,13 +2195,13 @@
       <c r="P1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="Q1" s="9" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="S1" s="11" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="8" t="s">
@@ -2228,10 +2210,10 @@
       <c r="U1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="12" t="s">
+      <c r="V1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="W1" s="12" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="8" t="s">
@@ -2240,10 +2222,10 @@
       <c r="Y1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="13" t="s">
+      <c r="Z1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="11" t="s">
+      <c r="AA1" s="13" t="s">
         <v>26</v>
       </c>
       <c r="AB1" s="11" t="s">
@@ -2261,10 +2243,10 @@
       <c r="AF1" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="8" t="s">
+      <c r="AG1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="14" t="s">
+      <c r="AH1" s="8" t="s">
         <v>33</v>
       </c>
       <c r="AI1" s="14" t="s">
@@ -2276,10 +2258,10 @@
       <c r="AK1" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="15" t="s">
+      <c r="AL1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="12" t="s">
+      <c r="AM1" s="15" t="s">
         <v>38</v>
       </c>
       <c r="AN1" s="12" t="s">
@@ -2288,10 +2270,10 @@
       <c r="AO1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="14" t="s">
+      <c r="AP1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="8" t="s">
+      <c r="AQ1" s="14" t="s">
         <v>42</v>
       </c>
       <c r="AR1" s="8" t="s">
@@ -2303,22 +2285,22 @@
       <c r="AT1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="16" t="s">
+      <c r="AU1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="11" t="s">
+      <c r="AV1" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="16" t="s">
+      <c r="AW1" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="11" t="s">
+      <c r="AX1" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="16" t="s">
+      <c r="AY1" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="9" t="s">
+      <c r="AZ1" s="16" t="s">
         <v>51</v>
       </c>
       <c r="BA1" s="9" t="s">
@@ -2327,28 +2309,28 @@
       <c r="BB1" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="12" t="s">
+      <c r="BC1" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="9" t="s">
+      <c r="BD1" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="8" t="s">
+      <c r="BE1" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="9" t="s">
+      <c r="BF1" s="8" t="s">
         <v>57</v>
       </c>
       <c r="BG1" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="8" t="s">
+      <c r="BH1" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="17" t="s">
+      <c r="BI1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="8" t="s">
+      <c r="BJ1" s="17" t="s">
         <v>61</v>
       </c>
       <c r="BK1" s="8" t="s">
@@ -2372,7 +2354,7 @@
       <c r="BQ1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="18" t="s">
+      <c r="BR1" s="8" t="s">
         <v>69</v>
       </c>
       <c r="BS1" s="18" t="s">
@@ -2399,103 +2381,106 @@
       <c r="BZ1" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="CA1" s="14" t="s">
+      <c r="CA1" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="CB1" s="19" t="s">
+      <c r="CB1" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" s="19" t="s">
+      <c r="CC1" s="20" t="s">
         <v>80</v>
       </c>
+      <c r="CD1" s="20" t="s">
+        <v>81</v>
+      </c>
     </row>
-    <row r="2" spans="79:81">
-      <c r="CA2" s="20"/>
-      <c r="CB2" s="20"/>
-      <c r="CC2" s="20"/>
+    <row r="2" spans="80:82">
+      <c r="CB2" s="19"/>
+      <c r="CC2" s="19"/>
+      <c r="CD2" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="19">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2 X2 T3:T1048576 X3:X1048576 AA2:AA1048576 AT3:AT1048576 AZ3:AZ1048576 BA3:BA1048576 BX$1:BX$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
+      <formula1>"新产品,迭代产品"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BJ$1:BJ$1048576 BU$1:BV$1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 Z2:Z1048576 AC2:AD1048576">
+      <formula1>0</formula1>
+      <formula2>999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 Y2:Y1048576 AB2:AB1048576 AU3:AU1048576 BY$1:BY$1048576 BA3:BB1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2 U3:U1048576 BB3:BB1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576 BC3:BC1048576">
       <formula1>0</formula1>
       <formula2>9999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2 W3:W1048576 Z2:Z1048576 AD2:AD1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W$1:W$1048576 AP$1:AP$1048576 BD2:BD1048576">
+      <formula1>1</formula1>
+      <formula2>2958464</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X1048576 AA2:AA1048576 AE2:AE1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2 R2:R1048576 Y3:Y1048576 AB2:AB1048576 AC2:AC1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BW$1:BW$1048576 BS$1:BT$1048576 BZ$1:CA$1048576">
       <formula1>0</formula1>
-      <formula2>999999999</formula2>
+      <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I$1:I$1048576">
-      <formula1>"新产品,迭代产品"</formula1>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AM$1:AM$1048576 AV2:AV1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q1048576 AF2:AF1048576 AX2:AX1048576 BI$1:BI$1048576 BT$1:BT$1048576 BU$1:BU$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ$1:AQ$1048576 AJ$1:AL$1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BX$1:BX$1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576 CB$1:CB$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V$1:V$1048576 AO$1:AO$1048576 BC2:BC1048576">
-      <formula1>1</formula1>
-      <formula2>2958464</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE1048576 BR$1:BR$1048576 BS$1:BS$1048576 BV$1:BV$1048576 BY$1:BY$1048576 BZ$1:BZ$1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH$1:AH$1048576 AL$1:AL$1048576 AU2:AU1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AJ$1:AJ$1048576 AK$1:AK$1048576 AP$1:AP$1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM$1:AM$1048576 AN$1:AN$1048576">
-      <formula1>32874</formula1>
-      <formula2>2958464</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV2:AV1048576 BW$1:BW$1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY1048576 CA$1:CA$1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE3:BE1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF3:BF1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+23</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2:BH1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI2:BI1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+21</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK3:BK1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL3:BL1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BP3:BP1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BQ3:BQ1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BQ3:BQ1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BR3:BR1048576">
       <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN$1:AO$1048576">
+      <formula1>32874</formula1>
+      <formula2>2958464</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AW3:AW1048573" listDataValidation="1"/>
+    <ignoredError sqref="AX3:AX1048573" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -55,6 +55,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -73,6 +80,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -91,6 +105,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1216,16 +1237,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2400,7 +2421,7 @@
       <c r="CD2" s="19"/>
     </row>
   </sheetData>
-  <dataValidations count="19">
+  <dataValidations count="18">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
@@ -2456,10 +2477,6 @@
       <formula1>0</formula1>
       <formula2>9.99999999999999E+23</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI2:BI1048576">
-      <formula1>0</formula1>
-      <formula2>9.99999999999999E+21</formula2>
-    </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL3:BL1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
     <t>spu</t>
   </si>
@@ -911,13 +911,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -934,6 +927,21 @@
   <si>
     <t xml:space="preserve">报关产品属性
 </t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>保险属性</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1237,16 +1245,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1772,10 +1780,10 @@
     <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2097,7 +2105,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CD2"/>
+  <dimension ref="A1:CE2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
@@ -2151,23 +2159,23 @@
     <col min="59" max="59" width="10.25" customWidth="1"/>
     <col min="60" max="60" width="9.375" customWidth="1"/>
     <col min="61" max="61" width="12.75" customWidth="1"/>
-    <col min="62" max="62" width="12.75" style="1" customWidth="1"/>
-    <col min="63" max="63" width="13.75" customWidth="1"/>
-    <col min="64" max="64" width="13.375" customWidth="1"/>
-    <col min="65" max="65" width="11.75" customWidth="1"/>
-    <col min="66" max="66" width="9.875" customWidth="1"/>
-    <col min="67" max="67" width="10" customWidth="1"/>
-    <col min="68" max="68" width="11" customWidth="1"/>
-    <col min="69" max="69" width="9.375"/>
-    <col min="71" max="71" width="11.875" style="6" customWidth="1"/>
-    <col min="72" max="72" width="12.5" style="6" customWidth="1"/>
-    <col min="73" max="73" width="12.125" style="6" customWidth="1"/>
-    <col min="74" max="79" width="9" style="6"/>
-    <col min="80" max="80" width="9" style="5"/>
-    <col min="81" max="82" width="11.125" style="7" customWidth="1"/>
+    <col min="62" max="63" width="12.75" style="1" customWidth="1"/>
+    <col min="64" max="64" width="13.75" customWidth="1"/>
+    <col min="65" max="65" width="13.375" customWidth="1"/>
+    <col min="66" max="66" width="11.75" customWidth="1"/>
+    <col min="67" max="67" width="9.875" customWidth="1"/>
+    <col min="68" max="68" width="10" customWidth="1"/>
+    <col min="69" max="69" width="11" customWidth="1"/>
+    <col min="70" max="70" width="9.375"/>
+    <col min="72" max="72" width="11.875" style="6" customWidth="1"/>
+    <col min="73" max="73" width="12.5" style="6" customWidth="1"/>
+    <col min="74" max="74" width="12.125" style="6" customWidth="1"/>
+    <col min="75" max="80" width="9" style="6"/>
+    <col min="81" max="81" width="9" style="5"/>
+    <col min="82" max="83" width="11.125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:82">
+    <row r="1" spans="1:83">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -2351,10 +2359,10 @@
       <c r="BI1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="17" t="s">
+      <c r="BJ1" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="8" t="s">
+      <c r="BK1" s="17" t="s">
         <v>62</v>
       </c>
       <c r="BL1" s="8" t="s">
@@ -2378,7 +2386,7 @@
       <c r="BR1" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="18" t="s">
+      <c r="BS1" s="8" t="s">
         <v>70</v>
       </c>
       <c r="BT1" s="18" t="s">
@@ -2405,27 +2413,30 @@
       <c r="CA1" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="CB1" s="14" t="s">
+      <c r="CB1" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" s="20" t="s">
+      <c r="CC1" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="20" t="s">
+      <c r="CD1" s="19" t="s">
         <v>81</v>
       </c>
+      <c r="CE1" s="19" t="s">
+        <v>82</v>
+      </c>
     </row>
-    <row r="2" spans="80:82">
-      <c r="CB2" s="19"/>
-      <c r="CC2" s="19"/>
-      <c r="CD2" s="19"/>
+    <row r="2" spans="81:83">
+      <c r="CC2" s="20"/>
+      <c r="CD2" s="20"/>
+      <c r="CE2" s="20"/>
     </row>
   </sheetData>
   <dataValidations count="18">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BJ$1:BJ$1048576 BU$1:BV$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK$1:BK$1048576 BV$1:BW$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
@@ -2433,7 +2444,7 @@
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 Y2:Y1048576 AB2:AB1048576 AU3:AU1048576 BY$1:BY$1048576 BA3:BB1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 Y2:Y1048576 AB2:AB1048576 AU3:AU1048576 BZ$1:BZ$1048576 BA3:BB1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
@@ -2449,7 +2460,7 @@
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BW$1:BW$1048576 BS$1:BT$1048576 BZ$1:CA$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX$1:BX$1048576 BT$1:BU$1048576 CA$1:CB$1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
@@ -2461,7 +2472,7 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BX$1:BX$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY$1:BY$1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
@@ -2469,7 +2480,7 @@
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576 CB$1:CB$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576 CC$1:CC$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
@@ -2477,15 +2488,15 @@
       <formula1>0</formula1>
       <formula2>9.99999999999999E+23</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL3:BL1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM3:BM1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900000</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BQ3:BQ1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BR3:BR1048576">
       <formula1>25569</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BR3:BR1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BS3:BS1048576">
       <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
     </dataValidation>
     <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN$1:AO$1048576">

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
@@ -911,6 +911,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -930,6 +937,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1004,22 +1018,22 @@
     <t>英文用途</t>
   </si>
   <si>
-    <t>产品尺寸(长)</t>
-  </si>
-  <si>
-    <t>产品尺寸(宽)</t>
-  </si>
-  <si>
-    <t>产品尺寸(高)</t>
-  </si>
-  <si>
-    <t>箱规(长)</t>
-  </si>
-  <si>
-    <t>箱规(宽)</t>
-  </si>
-  <si>
-    <t>箱规(高)</t>
+    <t>产品尺寸(长)(cm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(宽)(cm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(高)(cm)</t>
+  </si>
+  <si>
+    <t>箱规(长)(cm)</t>
+  </si>
+  <si>
+    <t>箱规(宽)(cm)</t>
+  </si>
+  <si>
+    <t>箱规(高)(cm)</t>
   </si>
   <si>
     <t>毛重</t>
@@ -1245,16 +1259,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2436,7 +2450,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK$1:BK$1048576 BV$1:BW$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK$1:BK$1048576 BV2:BW1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
@@ -2460,7 +2474,7 @@
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX$1:BX$1048576 BT$1:BU$1048576 CA$1:CB$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX2:BX1048576 CA$1:CB$1048576 BT2:BU1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
@@ -2472,7 +2486,7 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY$1:BY$1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY2:BY1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
@@ -911,13 +911,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -937,13 +930,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1018,22 +1004,22 @@
     <t>英文用途</t>
   </si>
   <si>
-    <t>产品尺寸(长)(cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(宽)(cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(高)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(长)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(宽)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(高)(cm)</t>
+    <t>产品尺寸(长)</t>
+  </si>
+  <si>
+    <t>产品尺寸(宽)</t>
+  </si>
+  <si>
+    <t>产品尺寸(高)</t>
+  </si>
+  <si>
+    <t>箱规(长)</t>
+  </si>
+  <si>
+    <t>箱规(宽)</t>
+  </si>
+  <si>
+    <t>箱规(高)</t>
   </si>
   <si>
     <t>毛重</t>
@@ -1259,16 +1245,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2450,7 +2436,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK$1:BK$1048576 BV2:BW1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK$1:BK$1048576 BV$1:BW$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
@@ -2474,7 +2460,7 @@
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX2:BX1048576 CA$1:CB$1048576 BT2:BU1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX$1:BX$1048576 BT$1:BU$1048576 CA$1:CB$1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
@@ -2486,7 +2472,7 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY2:BY1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY$1:BY$1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -1036,13 +1036,13 @@
     <t>箱规(高)(cm)</t>
   </si>
   <si>
-    <t>毛重</t>
-  </si>
-  <si>
-    <t>净重</t>
-  </si>
-  <si>
-    <t>单箱重量</t>
+    <t>毛重(g)</t>
+  </si>
+  <si>
+    <t>净重(g)</t>
+  </si>
+  <si>
+    <t>单箱重量(kg)</t>
   </si>
   <si>
     <t>单箱数量</t>
@@ -1257,18 +1257,18 @@
       <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2458,7 +2458,7 @@
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 Y2:Y1048576 AB2:AB1048576 AU3:AU1048576 BZ$1:BZ$1048576 BA3:BB1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 Y2:Y1048576 AB2:AB1048576 AU3:AU1048576 BZ2:BZ1048576 BA3:BB1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
@@ -2474,7 +2474,7 @@
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX2:BX1048576 CA$1:CB$1048576 BT2:BU1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX2:BX1048576 BT2:BU1048576 CA2:CB1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -239,13 +239,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -305,13 +298,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1249,6 +1235,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <name val="Helvetica"/>
       <charset val="134"/>
@@ -1257,18 +1249,12 @@
       <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1736,7 +1722,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1795,9 +1781,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2119,8 +2102,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CE2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:CE1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -2440,51 +2423,53 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="81:83">
-      <c r="CC2" s="20"/>
-      <c r="CD2" s="20"/>
-      <c r="CE2" s="20"/>
-    </row>
   </sheetData>
-  <dataValidations count="18">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
+  <dataValidations count="15">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1 J2:J1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK$1:BK$1048576 BV2:BW1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1 AP1 W2:W1048576 AP2:AP1048576 BD2:BD1048576">
+      <formula1>1</formula1>
+      <formula2>2958464</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1 AM1 AI2:AI1048576 AM2:AM1048576 AV2:AV1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ1:AL1 AQ1 AQ2:AQ1048576 AJ2:AL1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN1:AO1 AN2:AO1048576">
+      <formula1>32874</formula1>
+      <formula2>2958464</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK1 R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK2:BK1048576 BV2:BW1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 Z2:Z1048576 AC2:AD1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC1 AZ2:AZ1048576 CC2:CC1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 AC2:AD1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 Y2:Y1048576 AB2:AB1048576 AU3:AU1048576 BZ2:BZ1048576 BA3:BB1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:X$1048576">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576 AB2:AB1048576 BZ2:BZ1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576 BC3:BC1048576">
-      <formula1>0</formula1>
-      <formula2>9999999</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W$1:W$1048576 AP$1:AP$1048576 BD2:BD1048576">
-      <formula1>1</formula1>
-      <formula2>2958464</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X1048576 AA2:AA1048576 AE2:AE1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA1048576 AE2:AE1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX2:BX1048576 BT2:BU1048576 CA2:CB1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX2:BX1048576 CA2:CB1048576 BT2:BU1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AM$1:AM$1048576 AV2:AV1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ$1:AQ$1048576 AJ$1:AL$1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY2:BY1048576">
       <formula1>0</formula1>
@@ -2494,35 +2479,16 @@
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576 CC$1:CC$1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF3:BF1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+23</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM3:BM1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999900000</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BR3:BR1048576">
-      <formula1>25569</formula1>
-      <formula2>72686</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BS3:BS1048576">
-      <formula1>"未开发,开发中,开发完成,中止开发,暂停开发"</formula1>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN$1:AO$1048576">
-      <formula1>32874</formula1>
-      <formula2>2958464</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AX3:AX1048573" listDataValidation="1"/>
+    <ignoredError sqref="AX2:AX1048572" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -239,6 +239,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -298,6 +305,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1044,16 +1058,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
     <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="178" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="179" formatCode="0_ "/>
-    <numFmt numFmtId="180" formatCode="0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0_ "/>
+    <numFmt numFmtId="179" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -1235,12 +1248,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <name val="Helvetica"/>
       <charset val="134"/>
@@ -1255,6 +1262,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1722,7 +1735,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1735,18 +1748,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1765,22 +1775,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2169,110 +2179,110 @@
     <col min="74" max="74" width="12.125" style="6" customWidth="1"/>
     <col min="75" max="80" width="9" style="6"/>
     <col min="81" max="81" width="9" style="5"/>
-    <col min="82" max="83" width="11.125" style="7" customWidth="1"/>
+    <col min="82" max="83" width="11.125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:83">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="R1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="S1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="T1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="U1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="V1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="W1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="X1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Y1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="Z1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="13" t="s">
+      <c r="AA1" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="11" t="s">
+      <c r="AB1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="11" t="s">
+      <c r="AC1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="11" t="s">
+      <c r="AD1" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="11" t="s">
+      <c r="AE1" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="11" t="s">
+      <c r="AF1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="11" t="s">
+      <c r="AG1" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="8" t="s">
+      <c r="AH1" s="13" t="s">
         <v>33</v>
       </c>
       <c r="AI1" s="14" t="s">
@@ -2290,100 +2300,100 @@
       <c r="AM1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="12" t="s">
+      <c r="AN1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="12" t="s">
+      <c r="AO1" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="12" t="s">
+      <c r="AP1" s="11" t="s">
         <v>41</v>
       </c>
       <c r="AQ1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="8" t="s">
+      <c r="AR1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="8" t="s">
+      <c r="AS1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="8" t="s">
+      <c r="AT1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="8" t="s">
+      <c r="AU1" s="7" t="s">
         <v>46</v>
       </c>
       <c r="AV1" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="11" t="s">
+      <c r="AW1" s="10" t="s">
         <v>48</v>
       </c>
       <c r="AX1" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="11" t="s">
+      <c r="AY1" s="10" t="s">
         <v>50</v>
       </c>
       <c r="AZ1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="9" t="s">
+      <c r="BA1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="9" t="s">
+      <c r="BB1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="9" t="s">
+      <c r="BC1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="12" t="s">
+      <c r="BD1" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="9" t="s">
+      <c r="BE1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="8" t="s">
+      <c r="BF1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="9" t="s">
+      <c r="BG1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="9" t="s">
+      <c r="BH1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="8" t="s">
+      <c r="BI1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="11" t="s">
+      <c r="BJ1" s="10" t="s">
         <v>61</v>
       </c>
       <c r="BK1" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="8" t="s">
+      <c r="BL1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="8" t="s">
+      <c r="BM1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="8" t="s">
+      <c r="BN1" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="8" t="s">
+      <c r="BO1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="8" t="s">
+      <c r="BP1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="8" t="s">
+      <c r="BQ1" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="8" t="s">
+      <c r="BR1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="8" t="s">
+      <c r="BS1" s="7" t="s">
         <v>70</v>
       </c>
       <c r="BT1" s="18" t="s">
@@ -2416,39 +2426,19 @@
       <c r="CC1" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="19" t="s">
+      <c r="CD1" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="19" t="s">
+      <c r="CE1" s="13" t="s">
         <v>82</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="15">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1 J2:J1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1 AP1 W2:W1048576 AP2:AP1048576 BD2:BD1048576">
-      <formula1>1</formula1>
-      <formula2>2958464</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1 AM1 AI2:AI1048576 AM2:AM1048576 AV2:AV1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ1:AL1 AQ1 AQ2:AQ1048576 AJ2:AL1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN1:AO1 AN2:AO1048576">
-      <formula1>32874</formula1>
-      <formula2>2958464</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK1 R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK2:BK1048576 BV2:BW1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC1 AZ2:AZ1048576 CC2:CC1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK$1:BK$1048576 BV2:BW1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
@@ -2456,20 +2446,32 @@
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W$1:W$1048576 AP$1:AP$1048576 BD2:BD1048576">
+      <formula1>1</formula1>
+      <formula2>2958464</formula2>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:X$1048576">
       <formula1>"是,否"</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576 AB2:AB1048576 BZ2:BZ1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA1048576 AE2:AE1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX2:BX1048576 CA2:CB1048576 BT2:BU1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576 BZ2:BZ1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX2:BX1048576 BT2:BU1048576 CA2:CB1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AM$1:AM$1048576 AV2:AV1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ$1:AQ$1048576 AJ$1:AL$1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY2:BY1048576">
       <formula1>0</formula1>
@@ -2479,9 +2481,17 @@
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576 CC$1:CC$1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF3:BF1048576">
       <formula1>0</formula1>
       <formula2>9.99999999999999E+23</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN$1:AO$1048576">
+      <formula1>32874</formula1>
+      <formula2>2958464</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -2434,24 +2434,40 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="15">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
+  <dataValidations count="14">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1 J2:J1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK$1:BK$1048576 BV2:BW1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1 AP1 W2:W1048576 AP2:AP1048576 BD2:BD1048576">
+      <formula1>1</formula1>
+      <formula2>2958464</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X1 X2:X1048576">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1 AM1 AI2:AI1048576 AM2:AM1048576 AV2:AV1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ1:AL1 AQ1 AQ2:AQ1048576 AJ2:AL1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN1:AO1 AN2:AO1048576">
+      <formula1>32874</formula1>
+      <formula2>2958464</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK1 R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK2:BK1048576 BV2:BW1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC1 AZ2:AZ1048576 CC2:CC1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 AC2:AD1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W$1:W$1048576 AP$1:AP$1048576 BD2:BD1048576">
-      <formula1>1</formula1>
-      <formula2>2958464</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:X$1048576">
-      <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA1048576 AE2:AE1048576">
       <formula1>0</formula1>
@@ -2465,14 +2481,6 @@
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AM$1:AM$1048576 AV2:AV1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ$1:AQ$1048576 AJ$1:AL$1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY2:BY1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
@@ -2481,24 +2489,12 @@
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576 CC$1:CC$1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF3:BF1048576">
-      <formula1>0</formula1>
-      <formula2>9.99999999999999E+23</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN$1:AO$1048576">
-      <formula1>32874</formula1>
-      <formula2>2958464</formula2>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AX2:AX1048572" listDataValidation="1"/>
+    <ignoredError sqref="AX2:AX1048555" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -385,7 +385,19 @@
     <t>存在侵权风险(是/否)</t>
   </si>
   <si>
-    <t>单位</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>单位</t>
+    </r>
   </si>
   <si>
     <t>主要材质</t>
@@ -1258,16 +1270,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2131,7 +2143,7 @@
     <col min="22" max="22" width="11" customWidth="1"/>
     <col min="23" max="23" width="12" style="2" customWidth="1"/>
     <col min="24" max="24" width="16.625" customWidth="1"/>
-    <col min="25" max="25" width="5.875" customWidth="1"/>
+    <col min="25" max="25" width="6.75" customWidth="1"/>
     <col min="26" max="26" width="9.75" customWidth="1"/>
     <col min="27" max="27" width="15.125" style="3" customWidth="1"/>
     <col min="28" max="28" width="15" style="1" customWidth="1"/>
@@ -2255,7 +2267,7 @@
       <c r="X1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="Y1" s="8" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="7" t="s">
@@ -2435,39 +2447,23 @@
     </row>
   </sheetData>
   <dataValidations count="14">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1 J2:J1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1 AP1 W2:W1048576 AP2:AP1048576 BD2:BD1048576">
-      <formula1>1</formula1>
-      <formula2>2958464</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X1 X2:X1048576">
-      <formula1>"是,否"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1 AM1 AI2:AI1048576 AM2:AM1048576 AV2:AV1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ1:AL1 AQ1 AQ2:AQ1048576 AJ2:AL1048576">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN1:AO1 AN2:AO1048576">
-      <formula1>32874</formula1>
-      <formula2>2958464</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK1 R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK2:BK1048576 BV2:BW1048576">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC1 AZ2:AZ1048576 CC2:CC1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK$1:BK$1048576 BV2:BW1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 AC2:AD1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W$1:W$1048576 AP$1:AP$1048576 BD2:BD1048576">
+      <formula1>1</formula1>
+      <formula2>2958464</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:X$1048576">
+      <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA1048576 AE2:AE1048576">
       <formula1>0</formula1>
@@ -2481,6 +2477,14 @@
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AM$1:AM$1048576 AV2:AV1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ$1:AQ$1048576 AJ$1:AL$1048576">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY2:BY1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
@@ -2488,6 +2492,14 @@
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX1048576">
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576 CC$1:CC$1048576">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN$1:AO$1048576">
+      <formula1>32874</formula1>
+      <formula2>2958464</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t>spu</t>
   </si>
@@ -238,6 +238,9 @@
     </r>
   </si>
   <si>
+    <t>研发团队</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -386,6 +389,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1270,16 +1280,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2124,7 +2134,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CE1"/>
+  <dimension ref="A1:CF1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
@@ -2134,67 +2144,67 @@
     <col min="11" max="11" width="12.375" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="7.75" customWidth="1"/>
-    <col min="14" max="14" width="12.75" customWidth="1"/>
-    <col min="17" max="17" width="11.5" customWidth="1"/>
-    <col min="18" max="18" width="12.125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="14.375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="15.375" customWidth="1"/>
-    <col min="21" max="21" width="15.875" customWidth="1"/>
-    <col min="22" max="22" width="11" customWidth="1"/>
-    <col min="23" max="23" width="12" style="2" customWidth="1"/>
-    <col min="24" max="24" width="16.625" customWidth="1"/>
-    <col min="25" max="25" width="6.75" customWidth="1"/>
-    <col min="26" max="26" width="9.75" customWidth="1"/>
-    <col min="27" max="27" width="15.125" style="3" customWidth="1"/>
-    <col min="28" max="28" width="15" style="1" customWidth="1"/>
-    <col min="29" max="29" width="14.875" style="1" customWidth="1"/>
-    <col min="30" max="30" width="8.75" style="1" customWidth="1"/>
-    <col min="31" max="31" width="15.25" style="1" customWidth="1"/>
-    <col min="32" max="32" width="16.75" style="1" customWidth="1"/>
-    <col min="33" max="33" width="14" style="1" customWidth="1"/>
-    <col min="34" max="34" width="11.5" style="4"/>
-    <col min="35" max="35" width="13" style="5" customWidth="1"/>
-    <col min="36" max="36" width="12.25" style="5" customWidth="1"/>
-    <col min="37" max="37" width="11.125" style="5" customWidth="1"/>
-    <col min="38" max="38" width="13.625" style="5" customWidth="1"/>
-    <col min="39" max="39" width="12.625" style="5" customWidth="1"/>
-    <col min="40" max="40" width="14.25" style="2" customWidth="1"/>
-    <col min="41" max="41" width="14.5" style="2" customWidth="1"/>
-    <col min="42" max="42" width="12" style="2" customWidth="1"/>
-    <col min="43" max="43" width="10.75" style="5" customWidth="1"/>
-    <col min="45" max="45" width="10.75" customWidth="1"/>
-    <col min="46" max="46" width="16.375" customWidth="1"/>
-    <col min="47" max="47" width="12.375" customWidth="1"/>
-    <col min="48" max="48" width="11.5" style="5" customWidth="1"/>
-    <col min="49" max="49" width="15.875" style="1" customWidth="1"/>
-    <col min="50" max="50" width="11.625" style="5" customWidth="1"/>
-    <col min="51" max="51" width="15.875" style="1" customWidth="1"/>
-    <col min="52" max="52" width="13.5" style="5" customWidth="1"/>
-    <col min="54" max="54" width="11.75" customWidth="1"/>
-    <col min="55" max="55" width="12" customWidth="1"/>
-    <col min="56" max="56" width="11" style="2" customWidth="1"/>
-    <col min="57" max="57" width="9.125" customWidth="1"/>
-    <col min="58" max="58" width="21.5" customWidth="1"/>
-    <col min="59" max="59" width="10.25" customWidth="1"/>
-    <col min="60" max="60" width="9.375" customWidth="1"/>
-    <col min="61" max="61" width="12.75" customWidth="1"/>
-    <col min="62" max="63" width="12.75" style="1" customWidth="1"/>
-    <col min="64" max="64" width="13.75" customWidth="1"/>
-    <col min="65" max="65" width="13.375" customWidth="1"/>
-    <col min="66" max="66" width="11.75" customWidth="1"/>
-    <col min="67" max="67" width="9.875" customWidth="1"/>
-    <col min="68" max="68" width="10" customWidth="1"/>
-    <col min="69" max="69" width="11" customWidth="1"/>
-    <col min="70" max="70" width="9.375"/>
-    <col min="72" max="72" width="11.875" style="6" customWidth="1"/>
-    <col min="73" max="73" width="12.5" style="6" customWidth="1"/>
-    <col min="74" max="74" width="12.125" style="6" customWidth="1"/>
-    <col min="75" max="80" width="9" style="6"/>
-    <col min="81" max="81" width="9" style="5"/>
-    <col min="82" max="83" width="11.125" style="4" customWidth="1"/>
+    <col min="14" max="15" width="12.75" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
+    <col min="19" max="19" width="12.125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="14.375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="15.375" customWidth="1"/>
+    <col min="22" max="22" width="15.875" customWidth="1"/>
+    <col min="23" max="23" width="11" customWidth="1"/>
+    <col min="24" max="24" width="12" style="2" customWidth="1"/>
+    <col min="25" max="25" width="16.625" customWidth="1"/>
+    <col min="26" max="26" width="6.75" customWidth="1"/>
+    <col min="27" max="27" width="9.75" customWidth="1"/>
+    <col min="28" max="28" width="15.125" style="3" customWidth="1"/>
+    <col min="29" max="29" width="15" style="1" customWidth="1"/>
+    <col min="30" max="30" width="14.875" style="1" customWidth="1"/>
+    <col min="31" max="31" width="8.75" style="1" customWidth="1"/>
+    <col min="32" max="32" width="15.25" style="1" customWidth="1"/>
+    <col min="33" max="33" width="16.75" style="1" customWidth="1"/>
+    <col min="34" max="34" width="14" style="1" customWidth="1"/>
+    <col min="35" max="35" width="11.5" style="4"/>
+    <col min="36" max="36" width="13" style="5" customWidth="1"/>
+    <col min="37" max="37" width="12.25" style="5" customWidth="1"/>
+    <col min="38" max="38" width="11.125" style="5" customWidth="1"/>
+    <col min="39" max="39" width="13.625" style="5" customWidth="1"/>
+    <col min="40" max="40" width="12.625" style="5" customWidth="1"/>
+    <col min="41" max="41" width="14.25" style="2" customWidth="1"/>
+    <col min="42" max="42" width="14.5" style="2" customWidth="1"/>
+    <col min="43" max="43" width="12" style="2" customWidth="1"/>
+    <col min="44" max="44" width="10.75" style="5" customWidth="1"/>
+    <col min="46" max="46" width="10.75" customWidth="1"/>
+    <col min="47" max="47" width="16.375" customWidth="1"/>
+    <col min="48" max="48" width="12.375" customWidth="1"/>
+    <col min="49" max="49" width="11.5" style="5" customWidth="1"/>
+    <col min="50" max="50" width="15.875" style="1" customWidth="1"/>
+    <col min="51" max="51" width="11.625" style="5" customWidth="1"/>
+    <col min="52" max="52" width="15.875" style="1" customWidth="1"/>
+    <col min="53" max="53" width="13.5" style="5" customWidth="1"/>
+    <col min="55" max="55" width="11.75" customWidth="1"/>
+    <col min="56" max="56" width="12" customWidth="1"/>
+    <col min="57" max="57" width="11" style="2" customWidth="1"/>
+    <col min="58" max="58" width="9.125" customWidth="1"/>
+    <col min="59" max="59" width="21.5" customWidth="1"/>
+    <col min="60" max="60" width="10.25" customWidth="1"/>
+    <col min="61" max="61" width="9.375" customWidth="1"/>
+    <col min="62" max="62" width="12.75" customWidth="1"/>
+    <col min="63" max="64" width="12.75" style="1" customWidth="1"/>
+    <col min="65" max="65" width="13.75" customWidth="1"/>
+    <col min="66" max="66" width="13.375" customWidth="1"/>
+    <col min="67" max="67" width="11.75" customWidth="1"/>
+    <col min="68" max="68" width="9.875" customWidth="1"/>
+    <col min="69" max="69" width="10" customWidth="1"/>
+    <col min="70" max="70" width="11" customWidth="1"/>
+    <col min="71" max="71" width="9.375"/>
+    <col min="73" max="73" width="11.875" style="6" customWidth="1"/>
+    <col min="74" max="74" width="12.5" style="6" customWidth="1"/>
+    <col min="75" max="75" width="12.125" style="6" customWidth="1"/>
+    <col min="76" max="81" width="9" style="6"/>
+    <col min="82" max="82" width="9" style="5"/>
+    <col min="83" max="84" width="11.125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:83">
+    <row r="1" spans="1:84">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2234,7 +2244,7 @@
       <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="9" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="8" t="s">
@@ -2246,13 +2256,13 @@
       <c r="Q1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="R1" s="8" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="T1" s="10" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="7" t="s">
@@ -2261,22 +2271,22 @@
       <c r="V1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="11" t="s">
+      <c r="W1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="X1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Y1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="Z1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="12" t="s">
+      <c r="AA1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="10" t="s">
+      <c r="AB1" s="12" t="s">
         <v>27</v>
       </c>
       <c r="AC1" s="10" t="s">
@@ -2294,10 +2304,10 @@
       <c r="AG1" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="13" t="s">
+      <c r="AH1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="14" t="s">
+      <c r="AI1" s="13" t="s">
         <v>34</v>
       </c>
       <c r="AJ1" s="14" t="s">
@@ -2309,10 +2319,10 @@
       <c r="AL1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="15" t="s">
+      <c r="AM1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="11" t="s">
+      <c r="AN1" s="15" t="s">
         <v>39</v>
       </c>
       <c r="AO1" s="11" t="s">
@@ -2321,10 +2331,10 @@
       <c r="AP1" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="14" t="s">
+      <c r="AQ1" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="7" t="s">
+      <c r="AR1" s="14" t="s">
         <v>43</v>
       </c>
       <c r="AS1" s="7" t="s">
@@ -2336,22 +2346,22 @@
       <c r="AU1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="16" t="s">
+      <c r="AV1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="10" t="s">
+      <c r="AW1" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="16" t="s">
+      <c r="AX1" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="10" t="s">
+      <c r="AY1" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="16" t="s">
+      <c r="AZ1" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="8" t="s">
+      <c r="BA1" s="16" t="s">
         <v>52</v>
       </c>
       <c r="BB1" s="8" t="s">
@@ -2360,31 +2370,31 @@
       <c r="BC1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="11" t="s">
+      <c r="BD1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="8" t="s">
+      <c r="BE1" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="7" t="s">
+      <c r="BF1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="8" t="s">
+      <c r="BG1" s="7" t="s">
         <v>58</v>
       </c>
       <c r="BH1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="7" t="s">
+      <c r="BI1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="10" t="s">
+      <c r="BJ1" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="17" t="s">
+      <c r="BK1" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="7" t="s">
+      <c r="BL1" s="17" t="s">
         <v>63</v>
       </c>
       <c r="BM1" s="7" t="s">
@@ -2408,7 +2418,7 @@
       <c r="BS1" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="18" t="s">
+      <c r="BT1" s="7" t="s">
         <v>71</v>
       </c>
       <c r="BU1" s="18" t="s">
@@ -2435,14 +2445,17 @@
       <c r="CB1" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" s="14" t="s">
+      <c r="CC1" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="13" t="s">
+      <c r="CD1" s="14" t="s">
         <v>81</v>
       </c>
       <c r="CE1" s="13" t="s">
         <v>82</v>
+      </c>
+      <c r="CF1" s="13" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2450,54 +2463,54 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576 AG2:AG1048576 AY2:AY1048576 BK$1:BK$1048576 BV2:BW1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 AH2:AH1048576 AZ2:AZ1048576 BL$1:BL$1048576 BW2:BX1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 AC2:AD1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576 AD2:AE1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W$1:W$1048576 AP$1:AP$1048576 BD2:BD1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:X$1048576 AQ$1:AQ$1048576 BE2:BE1048576">
       <formula1>1</formula1>
       <formula2>2958464</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:X$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y$1:Y$1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA1048576 AE2:AE1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576 AF2:AF1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576 BZ2:BZ1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 CA2:CA1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576 BX2:BX1048576 BT2:BU1048576 CA2:CB1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG1048576 BY2:BY1048576 BU2:BV1048576 CB2:CC1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI$1:AI$1048576 AM$1:AM$1048576 AV2:AV1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ$1:AJ$1048576 AN$1:AN$1048576 AW2:AW1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ$1:AQ$1048576 AJ$1:AL$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR$1:AR$1048576 AK$1:AM$1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2:AW1048576 BY2:BY1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX1048576 BZ2:BZ1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY1048576">
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576 CC$1:CC$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA1048576 CD$1:CD$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN$1:AO$1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO$1:AP$1048576">
       <formula1>32874</formula1>
       <formula2>2958464</formula2>
     </dataValidation>
@@ -2506,7 +2519,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AX2:AX1048555" listDataValidation="1"/>
+    <ignoredError sqref="AY2:AY1048555" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="17985" windowHeight="4560"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>spu</t>
   </si>
@@ -978,6 +978,9 @@
       </rPr>
       <t>保险属性</t>
     </r>
+  </si>
+  <si>
+    <t>电池重量（g）</t>
   </si>
   <si>
     <r>
@@ -2134,7 +2137,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CF1"/>
+  <dimension ref="A1:CG1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
@@ -2188,23 +2191,23 @@
     <col min="60" max="60" width="10.25" customWidth="1"/>
     <col min="61" max="61" width="9.375" customWidth="1"/>
     <col min="62" max="62" width="12.75" customWidth="1"/>
-    <col min="63" max="64" width="12.75" style="1" customWidth="1"/>
-    <col min="65" max="65" width="13.75" customWidth="1"/>
-    <col min="66" max="66" width="13.375" customWidth="1"/>
-    <col min="67" max="67" width="11.75" customWidth="1"/>
-    <col min="68" max="68" width="9.875" customWidth="1"/>
-    <col min="69" max="69" width="10" customWidth="1"/>
-    <col min="70" max="70" width="11" customWidth="1"/>
-    <col min="71" max="71" width="9.375"/>
-    <col min="73" max="73" width="11.875" style="6" customWidth="1"/>
-    <col min="74" max="74" width="12.5" style="6" customWidth="1"/>
-    <col min="75" max="75" width="12.125" style="6" customWidth="1"/>
-    <col min="76" max="81" width="9" style="6"/>
-    <col min="82" max="82" width="9" style="5"/>
-    <col min="83" max="84" width="11.125" style="4" customWidth="1"/>
+    <col min="63" max="65" width="12.75" style="1" customWidth="1"/>
+    <col min="66" max="66" width="13.75" customWidth="1"/>
+    <col min="67" max="67" width="13.375" customWidth="1"/>
+    <col min="68" max="68" width="11.75" customWidth="1"/>
+    <col min="69" max="69" width="9.875" customWidth="1"/>
+    <col min="70" max="70" width="10" customWidth="1"/>
+    <col min="71" max="71" width="11" customWidth="1"/>
+    <col min="72" max="72" width="9.375"/>
+    <col min="74" max="74" width="11.875" style="6" customWidth="1"/>
+    <col min="75" max="75" width="12.5" style="6" customWidth="1"/>
+    <col min="76" max="76" width="12.125" style="6" customWidth="1"/>
+    <col min="77" max="82" width="9" style="6"/>
+    <col min="83" max="83" width="9" style="5"/>
+    <col min="84" max="85" width="11.125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:84">
+    <row r="1" spans="1:85">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2397,7 +2400,7 @@
       <c r="BL1" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="7" t="s">
+      <c r="BM1" s="17" t="s">
         <v>64</v>
       </c>
       <c r="BN1" s="7" t="s">
@@ -2421,7 +2424,7 @@
       <c r="BT1" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="18" t="s">
+      <c r="BU1" s="7" t="s">
         <v>72</v>
       </c>
       <c r="BV1" s="18" t="s">
@@ -2448,14 +2451,17 @@
       <c r="CC1" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="14" t="s">
+      <c r="CD1" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="13" t="s">
+      <c r="CE1" s="14" t="s">
         <v>82</v>
       </c>
       <c r="CF1" s="13" t="s">
         <v>83</v>
+      </c>
+      <c r="CG1" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2463,7 +2469,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 AH2:AH1048576 AZ2:AZ1048576 BL$1:BL$1048576 BW2:BX1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 AH2:AH1048576 AZ2:AZ1048576 BM$1:BM$1048576 BX2:BY1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
@@ -2482,11 +2488,11 @@
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 CA2:CA1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 CB2:CB1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG1048576 BY2:BY1048576 BU2:BV1048576 CB2:CC1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG1048576 BZ2:BZ1048576 BV2:BW1048576 CC2:CD1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
@@ -2498,7 +2504,7 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX1048576 BZ2:BZ1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX1048576 CA2:CA1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
@@ -2506,7 +2512,7 @@
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA1048576 CD$1:CD$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA1048576 CE$1:CE$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowWidth="17985" windowHeight="4560"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -238,7 +238,7 @@
     </r>
   </si>
   <si>
-    <t>研发团队</t>
+    <t>研发团队（产线）</t>
   </si>
   <si>
     <r>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -1040,22 +1040,22 @@
     <t>英文用途</t>
   </si>
   <si>
-    <t>产品尺寸(长)(cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(宽)(cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(高)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(长)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(宽)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(高)(cm)</t>
+    <t>产品尺寸(长)(mm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(宽)(mm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(高)(mm)</t>
+  </si>
+  <si>
+    <t>箱规(长)(mm)</t>
+  </si>
+  <si>
+    <t>箱规(宽)(mm)</t>
+  </si>
+  <si>
+    <t>箱规(高)(mm)</t>
   </si>
   <si>
     <t>毛重(g)</t>
@@ -1278,12 +1278,12 @@
       <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -1043,22 +1043,22 @@
     <t>英文用途</t>
   </si>
   <si>
-    <t>产品尺寸(长)(cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(宽)(cm)</t>
-  </si>
-  <si>
-    <t>产品尺寸(高)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(长)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(宽)(cm)</t>
-  </si>
-  <si>
-    <t>箱规(高)(cm)</t>
+    <t>产品尺寸(长)(mm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(宽)(mm)</t>
+  </si>
+  <si>
+    <t>产品尺寸(高)(mm)</t>
+  </si>
+  <si>
+    <t>箱规(长)(mm)</t>
+  </si>
+  <si>
+    <t>箱规(宽)(mm)</t>
+  </si>
+  <si>
+    <t>箱规(高)(mm)</t>
   </si>
   <si>
     <t>毛重(g)</t>
@@ -1283,16 +1283,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>spu</t>
   </si>
@@ -239,6 +239,20 @@
   </si>
   <si>
     <t>研发团队（产线）</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BU线</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2137,8 +2151,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CG1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:CH2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -2147,67 +2161,69 @@
     <col min="11" max="11" width="12.375" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="7.75" customWidth="1"/>
-    <col min="14" max="15" width="12.75" customWidth="1"/>
-    <col min="18" max="18" width="11.5" customWidth="1"/>
-    <col min="19" max="19" width="12.125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="14.375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="15.375" customWidth="1"/>
-    <col min="22" max="22" width="15.875" customWidth="1"/>
-    <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="12" style="2" customWidth="1"/>
-    <col min="25" max="25" width="16.625" customWidth="1"/>
-    <col min="26" max="26" width="6.75" customWidth="1"/>
-    <col min="27" max="27" width="9.75" customWidth="1"/>
-    <col min="28" max="28" width="15.125" style="3" customWidth="1"/>
-    <col min="29" max="29" width="15" style="1" customWidth="1"/>
-    <col min="30" max="30" width="14.875" style="1" customWidth="1"/>
-    <col min="31" max="31" width="8.75" style="1" customWidth="1"/>
-    <col min="32" max="32" width="15.25" style="1" customWidth="1"/>
-    <col min="33" max="33" width="16.75" style="1" customWidth="1"/>
-    <col min="34" max="34" width="14" style="1" customWidth="1"/>
-    <col min="35" max="35" width="11.5" style="4"/>
-    <col min="36" max="36" width="13" style="5" customWidth="1"/>
-    <col min="37" max="37" width="12.25" style="5" customWidth="1"/>
-    <col min="38" max="38" width="11.125" style="5" customWidth="1"/>
-    <col min="39" max="39" width="13.625" style="5" customWidth="1"/>
-    <col min="40" max="40" width="12.625" style="5" customWidth="1"/>
-    <col min="41" max="41" width="14.25" style="2" customWidth="1"/>
-    <col min="42" max="42" width="14.5" style="2" customWidth="1"/>
-    <col min="43" max="43" width="12" style="2" customWidth="1"/>
-    <col min="44" max="44" width="10.75" style="5" customWidth="1"/>
-    <col min="46" max="46" width="10.75" customWidth="1"/>
-    <col min="47" max="47" width="16.375" customWidth="1"/>
-    <col min="48" max="48" width="12.375" customWidth="1"/>
-    <col min="49" max="49" width="11.5" style="5" customWidth="1"/>
-    <col min="50" max="50" width="15.875" style="1" customWidth="1"/>
-    <col min="51" max="51" width="11.625" style="5" customWidth="1"/>
-    <col min="52" max="52" width="15.875" style="1" customWidth="1"/>
-    <col min="53" max="53" width="13.5" style="5" customWidth="1"/>
-    <col min="55" max="55" width="11.75" customWidth="1"/>
-    <col min="56" max="56" width="12" customWidth="1"/>
-    <col min="57" max="57" width="11" style="2" customWidth="1"/>
-    <col min="58" max="58" width="9.125" customWidth="1"/>
-    <col min="59" max="59" width="21.5" customWidth="1"/>
-    <col min="60" max="60" width="10.25" customWidth="1"/>
-    <col min="61" max="61" width="9.375" customWidth="1"/>
-    <col min="62" max="62" width="12.75" customWidth="1"/>
-    <col min="63" max="65" width="12.75" style="1" customWidth="1"/>
-    <col min="66" max="66" width="13.75" customWidth="1"/>
-    <col min="67" max="67" width="13.375" customWidth="1"/>
-    <col min="68" max="68" width="11.75" customWidth="1"/>
-    <col min="69" max="69" width="9.875" customWidth="1"/>
-    <col min="70" max="70" width="10" customWidth="1"/>
-    <col min="71" max="71" width="11" customWidth="1"/>
-    <col min="72" max="72" width="9.375"/>
-    <col min="74" max="74" width="11.875" style="6" customWidth="1"/>
-    <col min="75" max="75" width="12.5" style="6" customWidth="1"/>
-    <col min="76" max="76" width="12.125" style="6" customWidth="1"/>
-    <col min="77" max="82" width="9" style="6"/>
-    <col min="83" max="83" width="9" style="5"/>
-    <col min="84" max="85" width="11.125" style="4" customWidth="1"/>
+    <col min="14" max="14" width="12.75" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="16" max="16" width="12.75" customWidth="1"/>
+    <col min="19" max="19" width="11.5" customWidth="1"/>
+    <col min="20" max="20" width="12.125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="14.375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="15.375" customWidth="1"/>
+    <col min="23" max="23" width="15.875" customWidth="1"/>
+    <col min="24" max="24" width="11" customWidth="1"/>
+    <col min="25" max="25" width="12" style="2" customWidth="1"/>
+    <col min="26" max="26" width="16.625" customWidth="1"/>
+    <col min="27" max="27" width="6.75" customWidth="1"/>
+    <col min="28" max="28" width="9.75" customWidth="1"/>
+    <col min="29" max="29" width="15.125" style="3" customWidth="1"/>
+    <col min="30" max="30" width="15" style="1" customWidth="1"/>
+    <col min="31" max="31" width="14.875" style="1" customWidth="1"/>
+    <col min="32" max="32" width="8.75" style="1" customWidth="1"/>
+    <col min="33" max="33" width="15.25" style="1" customWidth="1"/>
+    <col min="34" max="34" width="16.75" style="1" customWidth="1"/>
+    <col min="35" max="35" width="14" style="1" customWidth="1"/>
+    <col min="36" max="36" width="11.5" style="4"/>
+    <col min="37" max="37" width="13" style="5" customWidth="1"/>
+    <col min="38" max="38" width="12.25" style="5" customWidth="1"/>
+    <col min="39" max="39" width="11.125" style="5" customWidth="1"/>
+    <col min="40" max="40" width="13.625" style="5" customWidth="1"/>
+    <col min="41" max="41" width="12.625" style="5" customWidth="1"/>
+    <col min="42" max="42" width="14.25" style="2" customWidth="1"/>
+    <col min="43" max="43" width="14.5" style="2" customWidth="1"/>
+    <col min="44" max="44" width="12" style="2" customWidth="1"/>
+    <col min="45" max="45" width="10.75" style="5" customWidth="1"/>
+    <col min="47" max="47" width="10.75" customWidth="1"/>
+    <col min="48" max="48" width="16.375" customWidth="1"/>
+    <col min="49" max="49" width="12.375" customWidth="1"/>
+    <col min="50" max="50" width="11.5" style="5" customWidth="1"/>
+    <col min="51" max="51" width="15.875" style="1" customWidth="1"/>
+    <col min="52" max="52" width="11.625" style="5" customWidth="1"/>
+    <col min="53" max="53" width="15.875" style="1" customWidth="1"/>
+    <col min="54" max="54" width="13.5" style="5" customWidth="1"/>
+    <col min="56" max="56" width="11.75" customWidth="1"/>
+    <col min="57" max="57" width="12" customWidth="1"/>
+    <col min="58" max="58" width="11" style="2" customWidth="1"/>
+    <col min="59" max="59" width="9.125" customWidth="1"/>
+    <col min="60" max="60" width="21.5" customWidth="1"/>
+    <col min="61" max="61" width="10.25" customWidth="1"/>
+    <col min="62" max="62" width="9.375" customWidth="1"/>
+    <col min="63" max="63" width="12.75" customWidth="1"/>
+    <col min="64" max="66" width="12.75" style="1" customWidth="1"/>
+    <col min="67" max="67" width="13.75" customWidth="1"/>
+    <col min="68" max="68" width="13.375" customWidth="1"/>
+    <col min="69" max="69" width="11.75" customWidth="1"/>
+    <col min="70" max="70" width="9.875" customWidth="1"/>
+    <col min="71" max="71" width="10" customWidth="1"/>
+    <col min="72" max="72" width="11" customWidth="1"/>
+    <col min="73" max="73" width="9.375"/>
+    <col min="75" max="75" width="11.875" style="6" customWidth="1"/>
+    <col min="76" max="76" width="12.5" style="6" customWidth="1"/>
+    <col min="77" max="77" width="12.125" style="6" customWidth="1"/>
+    <col min="78" max="83" width="9" style="6"/>
+    <col min="84" max="84" width="9" style="5"/>
+    <col min="85" max="86" width="11.125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:85">
+    <row r="1" spans="1:86">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2262,13 +2278,13 @@
       <c r="R1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="S1" s="8" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="7" t="s">
+      <c r="U1" s="10" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="7" t="s">
@@ -2277,22 +2293,22 @@
       <c r="W1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="11" t="s">
+      <c r="X1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="Y1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="Z1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AA1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="12" t="s">
+      <c r="AB1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="10" t="s">
+      <c r="AC1" s="12" t="s">
         <v>28</v>
       </c>
       <c r="AD1" s="10" t="s">
@@ -2310,10 +2326,10 @@
       <c r="AH1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="13" t="s">
+      <c r="AI1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="14" t="s">
+      <c r="AJ1" s="13" t="s">
         <v>35</v>
       </c>
       <c r="AK1" s="14" t="s">
@@ -2325,10 +2341,10 @@
       <c r="AM1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="15" t="s">
+      <c r="AN1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="11" t="s">
+      <c r="AO1" s="15" t="s">
         <v>40</v>
       </c>
       <c r="AP1" s="11" t="s">
@@ -2337,10 +2353,10 @@
       <c r="AQ1" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="14" t="s">
+      <c r="AR1" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="7" t="s">
+      <c r="AS1" s="14" t="s">
         <v>44</v>
       </c>
       <c r="AT1" s="7" t="s">
@@ -2352,22 +2368,22 @@
       <c r="AV1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="16" t="s">
+      <c r="AW1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="10" t="s">
+      <c r="AX1" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="16" t="s">
+      <c r="AY1" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="10" t="s">
+      <c r="AZ1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="16" t="s">
+      <c r="BA1" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="8" t="s">
+      <c r="BB1" s="16" t="s">
         <v>53</v>
       </c>
       <c r="BC1" s="8" t="s">
@@ -2376,34 +2392,34 @@
       <c r="BD1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="11" t="s">
+      <c r="BE1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="8" t="s">
+      <c r="BF1" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="7" t="s">
+      <c r="BG1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="8" t="s">
+      <c r="BH1" s="7" t="s">
         <v>59</v>
       </c>
       <c r="BI1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="7" t="s">
+      <c r="BJ1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="10" t="s">
+      <c r="BK1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="17" t="s">
+      <c r="BL1" s="10" t="s">
         <v>63</v>
       </c>
       <c r="BM1" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="7" t="s">
+      <c r="BN1" s="17" t="s">
         <v>65</v>
       </c>
       <c r="BO1" s="7" t="s">
@@ -2427,7 +2443,7 @@
       <c r="BU1" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="18" t="s">
+      <c r="BV1" s="7" t="s">
         <v>73</v>
       </c>
       <c r="BW1" s="18" t="s">
@@ -2454,69 +2470,75 @@
       <c r="CD1" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="14" t="s">
+      <c r="CE1" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" s="13" t="s">
+      <c r="CF1" s="14" t="s">
         <v>83</v>
       </c>
       <c r="CG1" s="13" t="s">
         <v>84</v>
       </c>
+      <c r="CH1" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:86">
+      <c r="O2" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="14">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576 AH2:AH1048576 AZ2:AZ1048576 BM$1:BM$1048576 BX2:BY1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576 AI2:AI1048576 BA2:BA1048576 BN$1:BN$1048576 BY2:BZ1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576 AD2:AE1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 AE2:AF1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X$1:X$1048576 AQ$1:AQ$1048576 BE2:BE1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y$1:Y$1048576 AR$1:AR$1048576 BF2:BF1048576">
       <formula1>1</formula1>
       <formula2>2958464</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y$1:Y$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z$1:Z$1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576 AF2:AF1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 AG2:AG1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 CB2:CB1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576 CC2:CC1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG1048576 BZ2:BZ1048576 BV2:BW1048576 CC2:CD1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH1048576 CA2:CA1048576 BW2:BX1048576 CD2:CE1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ$1:AJ$1048576 AN$1:AN$1048576 AW2:AW1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK$1:AK$1048576 AO$1:AO$1048576 AX2:AX1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR$1:AR$1048576 AK$1:AM$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS$1:AS$1048576 AL$1:AN$1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX1048576 CA2:CA1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY1048576 CB2:CB1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576">
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA1048576 CE$1:CE$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BB2:BB1048576 CF$1:CF$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO$1:AP$1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP$1:AQ$1048576">
       <formula1>32874</formula1>
       <formula2>2958464</formula2>
     </dataValidation>
@@ -2525,7 +2547,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AY2:AY1048555" listDataValidation="1"/>
+    <ignoredError sqref="AZ2:AZ1048555" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -242,6 +242,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1297,16 +1304,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1774,7 +1781,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1830,6 +1837,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2484,7 +2494,7 @@
       </c>
     </row>
     <row r="2" spans="1:86">
-      <c r="O2" s="7"/>
+      <c r="O2" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="14">

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>spu</t>
   </si>
@@ -428,6 +428,20 @@
         <scheme val="minor"/>
       </rPr>
       <t>单位</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>产品质保期</t>
     </r>
   </si>
   <si>
@@ -1302,12 +1316,12 @@
       <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2161,7 +2175,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CH2"/>
+  <dimension ref="A1:CI2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
@@ -2183,57 +2197,59 @@
     <col min="25" max="25" width="12" style="2" customWidth="1"/>
     <col min="26" max="26" width="16.625" customWidth="1"/>
     <col min="27" max="27" width="6.75" customWidth="1"/>
-    <col min="28" max="28" width="9.75" customWidth="1"/>
-    <col min="29" max="29" width="15.125" style="3" customWidth="1"/>
-    <col min="30" max="30" width="15" style="1" customWidth="1"/>
-    <col min="31" max="31" width="14.875" style="1" customWidth="1"/>
-    <col min="32" max="32" width="8.75" style="1" customWidth="1"/>
-    <col min="33" max="33" width="15.25" style="1" customWidth="1"/>
-    <col min="34" max="34" width="16.75" style="1" customWidth="1"/>
-    <col min="35" max="35" width="14" style="1" customWidth="1"/>
-    <col min="36" max="36" width="11.5" style="4"/>
-    <col min="37" max="37" width="13" style="5" customWidth="1"/>
-    <col min="38" max="38" width="12.25" style="5" customWidth="1"/>
-    <col min="39" max="39" width="11.125" style="5" customWidth="1"/>
-    <col min="40" max="40" width="13.625" style="5" customWidth="1"/>
-    <col min="41" max="41" width="12.625" style="5" customWidth="1"/>
-    <col min="42" max="42" width="14.25" style="2" customWidth="1"/>
-    <col min="43" max="43" width="14.5" style="2" customWidth="1"/>
-    <col min="44" max="44" width="12" style="2" customWidth="1"/>
-    <col min="45" max="45" width="10.75" style="5" customWidth="1"/>
-    <col min="47" max="47" width="10.75" customWidth="1"/>
-    <col min="48" max="48" width="16.375" customWidth="1"/>
-    <col min="49" max="49" width="12.375" customWidth="1"/>
-    <col min="50" max="50" width="11.5" style="5" customWidth="1"/>
-    <col min="51" max="51" width="15.875" style="1" customWidth="1"/>
-    <col min="52" max="52" width="11.625" style="5" customWidth="1"/>
-    <col min="53" max="53" width="15.875" style="1" customWidth="1"/>
-    <col min="54" max="54" width="13.5" style="5" customWidth="1"/>
-    <col min="56" max="56" width="11.75" customWidth="1"/>
-    <col min="57" max="57" width="12" customWidth="1"/>
-    <col min="58" max="58" width="11" style="2" customWidth="1"/>
-    <col min="59" max="59" width="9.125" customWidth="1"/>
-    <col min="60" max="60" width="21.5" customWidth="1"/>
-    <col min="61" max="61" width="10.25" customWidth="1"/>
-    <col min="62" max="62" width="9.375" customWidth="1"/>
-    <col min="63" max="63" width="12.75" customWidth="1"/>
-    <col min="64" max="66" width="12.75" style="1" customWidth="1"/>
-    <col min="67" max="67" width="13.75" customWidth="1"/>
-    <col min="68" max="68" width="13.375" customWidth="1"/>
-    <col min="69" max="69" width="11.75" customWidth="1"/>
-    <col min="70" max="70" width="9.875" customWidth="1"/>
-    <col min="71" max="71" width="10" customWidth="1"/>
-    <col min="72" max="72" width="11" customWidth="1"/>
-    <col min="73" max="73" width="9.375"/>
-    <col min="75" max="75" width="11.875" style="6" customWidth="1"/>
-    <col min="76" max="76" width="12.5" style="6" customWidth="1"/>
-    <col min="77" max="77" width="12.125" style="6" customWidth="1"/>
-    <col min="78" max="83" width="9" style="6"/>
-    <col min="84" max="84" width="9" style="5"/>
-    <col min="85" max="86" width="11.125" style="4" customWidth="1"/>
+    <col min="28" max="28" width="7.625" customWidth="1"/>
+    <col min="29" max="29" width="9.75" customWidth="1"/>
+    <col min="30" max="30" width="15.125" style="3" customWidth="1"/>
+    <col min="31" max="31" width="15" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.875" style="1" customWidth="1"/>
+    <col min="33" max="33" width="8.75" style="1" customWidth="1"/>
+    <col min="34" max="34" width="15.25" style="1" customWidth="1"/>
+    <col min="35" max="35" width="16.75" style="1" customWidth="1"/>
+    <col min="36" max="36" width="14" style="1" customWidth="1"/>
+    <col min="37" max="37" width="11.5" style="4"/>
+    <col min="38" max="38" width="13" style="5" customWidth="1"/>
+    <col min="39" max="39" width="12.25" style="5" customWidth="1"/>
+    <col min="40" max="40" width="11.125" style="5" customWidth="1"/>
+    <col min="41" max="41" width="13.625" style="5" customWidth="1"/>
+    <col min="42" max="42" width="12.625" style="5" customWidth="1"/>
+    <col min="43" max="43" width="14.25" style="2" customWidth="1"/>
+    <col min="44" max="44" width="14.5" style="2" customWidth="1"/>
+    <col min="45" max="45" width="12" style="2" customWidth="1"/>
+    <col min="46" max="46" width="10.75" style="5" customWidth="1"/>
+    <col min="48" max="48" width="10.75" customWidth="1"/>
+    <col min="49" max="49" width="16.375" customWidth="1"/>
+    <col min="50" max="50" width="12.375" customWidth="1"/>
+    <col min="51" max="51" width="11.5" style="5" customWidth="1"/>
+    <col min="52" max="52" width="15.875" style="1" customWidth="1"/>
+    <col min="53" max="53" width="11.625" style="5" customWidth="1"/>
+    <col min="54" max="54" width="15.875" style="1" customWidth="1"/>
+    <col min="55" max="55" width="13.5" style="5" customWidth="1"/>
+    <col min="57" max="57" width="11.75" customWidth="1"/>
+    <col min="58" max="58" width="12" customWidth="1"/>
+    <col min="59" max="59" width="11" style="2" customWidth="1"/>
+    <col min="60" max="60" width="9.125" customWidth="1"/>
+    <col min="61" max="61" width="21.5" customWidth="1"/>
+    <col min="62" max="62" width="10.25" customWidth="1"/>
+    <col min="63" max="63" width="9.375" customWidth="1"/>
+    <col min="64" max="64" width="12.75" customWidth="1"/>
+    <col min="65" max="67" width="12.75" style="1" customWidth="1"/>
+    <col min="68" max="68" width="13.75" customWidth="1"/>
+    <col min="69" max="69" width="13.375" customWidth="1"/>
+    <col min="70" max="70" width="11.75" customWidth="1"/>
+    <col min="71" max="71" width="9.875" customWidth="1"/>
+    <col min="72" max="72" width="10" customWidth="1"/>
+    <col min="73" max="73" width="11" customWidth="1"/>
+    <col min="74" max="74" width="9.375"/>
+    <col min="76" max="76" width="11.875" style="6" customWidth="1"/>
+    <col min="77" max="77" width="12.5" style="6" customWidth="1"/>
+    <col min="78" max="78" width="12.125" style="6" customWidth="1"/>
+    <col min="79" max="84" width="9" style="6"/>
+    <col min="85" max="85" width="9" style="5"/>
+    <col min="86" max="86" width="11.125" style="4" customWidth="1"/>
+    <col min="87" max="87" width="13.875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:86">
+    <row r="1" spans="1:87">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2315,13 +2331,13 @@
       <c r="AA1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="7" t="s">
+      <c r="AB1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="12" t="s">
+      <c r="AC1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="10" t="s">
+      <c r="AD1" s="12" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="10" t="s">
@@ -2339,10 +2355,10 @@
       <c r="AI1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="13" t="s">
+      <c r="AJ1" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="14" t="s">
+      <c r="AK1" s="13" t="s">
         <v>36</v>
       </c>
       <c r="AL1" s="14" t="s">
@@ -2354,10 +2370,10 @@
       <c r="AN1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="15" t="s">
+      <c r="AO1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="11" t="s">
+      <c r="AP1" s="15" t="s">
         <v>41</v>
       </c>
       <c r="AQ1" s="11" t="s">
@@ -2366,10 +2382,10 @@
       <c r="AR1" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="14" t="s">
+      <c r="AS1" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="7" t="s">
+      <c r="AT1" s="14" t="s">
         <v>45</v>
       </c>
       <c r="AU1" s="7" t="s">
@@ -2381,22 +2397,22 @@
       <c r="AW1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="16" t="s">
+      <c r="AX1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="10" t="s">
+      <c r="AY1" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="16" t="s">
+      <c r="AZ1" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="10" t="s">
+      <c r="BA1" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="16" t="s">
+      <c r="BB1" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="8" t="s">
+      <c r="BC1" s="16" t="s">
         <v>54</v>
       </c>
       <c r="BD1" s="8" t="s">
@@ -2405,34 +2421,34 @@
       <c r="BE1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="11" t="s">
+      <c r="BF1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="8" t="s">
+      <c r="BG1" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="7" t="s">
+      <c r="BH1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="8" t="s">
+      <c r="BI1" s="7" t="s">
         <v>60</v>
       </c>
       <c r="BJ1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="7" t="s">
+      <c r="BK1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="10" t="s">
+      <c r="BL1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="17" t="s">
+      <c r="BM1" s="10" t="s">
         <v>64</v>
       </c>
       <c r="BN1" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="7" t="s">
+      <c r="BO1" s="17" t="s">
         <v>66</v>
       </c>
       <c r="BP1" s="7" t="s">
@@ -2456,7 +2472,7 @@
       <c r="BV1" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" s="18" t="s">
+      <c r="BW1" s="7" t="s">
         <v>74</v>
       </c>
       <c r="BX1" s="18" t="s">
@@ -2483,17 +2499,20 @@
       <c r="CE1" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" s="14" t="s">
+      <c r="CF1" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="CG1" s="13" t="s">
+      <c r="CG1" s="14" t="s">
         <v>84</v>
       </c>
       <c r="CH1" s="13" t="s">
         <v>85</v>
       </c>
+      <c r="CI1" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
-    <row r="2" spans="1:86">
+    <row r="2" spans="1:87">
       <c r="O2" s="19"/>
     </row>
   </sheetData>
@@ -2501,54 +2520,54 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J$1:J$1048576">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576 AI2:AI1048576 BA2:BA1048576 BN$1:BN$1048576 BY2:BZ1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576 AJ2:AJ1048576 BB2:BB1048576 BO$1:BO$1048576 BZ2:CA1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 AE2:AF1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U1048576 AF2:AG1048576">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y$1:Y$1048576 AR$1:AR$1048576 BF2:BF1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y$1:Y$1048576 AS$1:AS$1048576 BG2:BG1048576">
       <formula1>1</formula1>
       <formula2>2958464</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z$1:Z$1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC1048576 AG2:AG1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576 AH2:AH1048576">
       <formula1>0</formula1>
       <formula2>99999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576 CC2:CC1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE1048576 CD2:CD1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH2:AH1048576 CA2:CA1048576 BW2:BX1048576 CD2:CE1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2:AI1048576 CB2:CB1048576 BX2:BY1048576 CE2:CF1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK$1:AK$1048576 AO$1:AO$1048576 AX2:AX1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL$1:AL$1048576 AP$1:AP$1048576 AY2:AY1048576">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS$1:AS$1048576 AL$1:AN$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT$1:AT$1048576 AM$1:AO$1048576">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY1048576 CB2:CB1048576">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576 CC2:CC1048576">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ2:AZ1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA1048576">
       <formula1>0</formula1>
       <formula2>99999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BB2:BB1048576 CF$1:CF$1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BC1048576 CG$1:CG$1048576">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP$1:AQ$1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ$1:AR$1048576">
       <formula1>32874</formula1>
       <formula2>2958464</formula2>
     </dataValidation>
@@ -2557,7 +2576,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="AZ2:AZ1048555" listDataValidation="1"/>
+    <ignoredError sqref="BA2:BA1048555" listDataValidation="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetailTemplate.xlsx
@@ -238,17 +238,28 @@
     </r>
   </si>
   <si>
-    <t>研发团队（产线）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>研发团队（产线）</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>*</t>
     </r>
     <r>
@@ -432,6 +443,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1316,18 +1334,18 @@
       <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2289,7 +2307,7 @@
       <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="8" t="s">
